--- a/apps/nuxt/i18n/i18n.xlsx
+++ b/apps/nuxt/i18n/i18n.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7920" uniqueCount="7195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7905" uniqueCount="7192">
   <si>
     <t>key</t>
   </si>
@@ -21526,19 +21526,12 @@
     <t>练习例句</t>
   </si>
   <si>
-    <t>enable_fsrs</t>
-  </si>
-  <si>
-    <t>启用遗忘曲线算法</t>
-  </si>
-  <si>
-    <t>enable_fsrs_desc</t>
-  </si>
-  <si>
-    <t>开启后，将使用遗忘曲线(FSRS)算法来决定需要复习的单词,而非固定单词数量; 刚启用时，没有复习词，学习一次之后才有复习词</t>
-  </si>
-  <si>
-    <t>开启后，将使用FSRS算法来决定需要复习的单词,而非固定单词数量</t>
+    <t>fsrs_desc</t>
+  </si>
+  <si>
+    <t>基于“艾宾浩斯遗忘曲线”设计，系统会根据你的记忆情况，自动安排最合适的复习时间。
+不再机械重复，让你用更少时间记住更多单词。
+记得越牢，复习间隔越长；容易忘的内容，会更频繁出现。</t>
   </si>
   <si>
     <t>fsrs_settings</t>
@@ -21638,14 +21631,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -22114,28 +22100,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -22144,129 +22133,129 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -22652,7 +22641,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O528"/>
+  <dimension ref="A1:O527"/>
   <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -46723,756 +46712,709 @@
         <v>7160</v>
       </c>
     </row>
-    <row r="513" spans="1:15">
+    <row r="513" ht="360" spans="1:15">
       <c r="A513" t="s">
         <v>7161</v>
       </c>
-      <c r="B513" t="s">
+      <c r="B513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="C513" t="s">
+      <c r="C513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="D513" t="s">
+      <c r="D513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="E513" t="s">
+      <c r="E513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="F513" t="s">
+      <c r="F513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="G513" t="s">
+      <c r="G513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="H513" t="s">
+      <c r="H513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="I513" t="s">
+      <c r="I513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="J513" t="s">
+      <c r="J513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="K513" t="s">
+      <c r="K513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="L513" t="s">
+      <c r="L513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="M513" t="s">
+      <c r="M513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="N513" t="s">
+      <c r="N513" s="1" t="s">
         <v>7162</v>
       </c>
-      <c r="O513" t="s">
+      <c r="O513" s="1" t="s">
         <v>7162</v>
       </c>
     </row>
     <row r="514" spans="1:15">
-      <c r="A514" t="s">
+      <c r="A514" s="2" t="s">
         <v>7163</v>
       </c>
-      <c r="B514" t="s">
+      <c r="B514" s="2" t="s">
         <v>7164</v>
       </c>
-      <c r="C514" t="s">
+      <c r="C514" s="2" t="s">
         <v>7164</v>
       </c>
-      <c r="D514" t="s">
+      <c r="D514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="E514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="F514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="G514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="H514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="I514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="J514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="K514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="L514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="M514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="N514" s="2" t="s">
+        <v>7164</v>
+      </c>
+      <c r="O514" s="2" t="s">
+        <v>7164</v>
+      </c>
+    </row>
+    <row r="515" spans="1:15">
+      <c r="A515" s="2" t="s">
         <v>7165</v>
       </c>
-      <c r="E514" t="s">
-        <v>7165</v>
-      </c>
-      <c r="F514" t="s">
-        <v>7165</v>
-      </c>
-      <c r="G514" t="s">
-        <v>7165</v>
-      </c>
-      <c r="H514" t="s">
-        <v>7165</v>
-      </c>
-      <c r="I514" t="s">
-        <v>7165</v>
-      </c>
-      <c r="J514" t="s">
-        <v>7165</v>
-      </c>
-      <c r="K514" t="s">
-        <v>7165</v>
-      </c>
-      <c r="L514" t="s">
-        <v>7165</v>
-      </c>
-      <c r="M514" t="s">
-        <v>7165</v>
-      </c>
-      <c r="N514" t="s">
-        <v>7165</v>
-      </c>
-      <c r="O514" t="s">
-        <v>7165</v>
-      </c>
-    </row>
-    <row r="515" spans="1:15">
-      <c r="A515" s="1" t="s">
+      <c r="B515" s="3" t="s">
         <v>7166</v>
       </c>
-      <c r="B515" s="1" t="s">
+      <c r="C515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="D515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="E515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="F515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="G515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="H515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="I515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="J515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="K515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="L515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="M515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="N515" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="O515" s="3" t="s">
+        <v>7166</v>
+      </c>
+    </row>
+    <row r="516" spans="1:15">
+      <c r="A516" s="4" t="s">
         <v>7167</v>
       </c>
-      <c r="C515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="D515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="E515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="F515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="G515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="H515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="I515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="J515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="K515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="L515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="M515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="N515" s="1" t="s">
-        <v>7167</v>
-      </c>
-      <c r="O515" s="1" t="s">
-        <v>7167</v>
-      </c>
-    </row>
-    <row r="516" spans="1:15">
-      <c r="A516" s="1" t="s">
+      <c r="B516" s="2" t="s">
         <v>7168</v>
       </c>
-      <c r="B516" s="2" t="s">
+      <c r="C516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="E516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="F516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="G516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="H516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="I516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="J516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="K516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="L516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="M516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="N516" s="2" t="s">
+        <v>7168</v>
+      </c>
+      <c r="O516" s="2" t="s">
+        <v>7168</v>
+      </c>
+    </row>
+    <row r="517" spans="1:15">
+      <c r="A517" s="2" t="s">
         <v>7169</v>
       </c>
-      <c r="C516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="D516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="E516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="F516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="G516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="H516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="I516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="J516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="K516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="L516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="M516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="N516" s="2" t="s">
-        <v>7169</v>
-      </c>
-      <c r="O516" s="2" t="s">
-        <v>7169</v>
-      </c>
-    </row>
-    <row r="517" spans="1:15">
-      <c r="A517" s="3" t="s">
+      <c r="B517" s="2" t="s">
         <v>7170</v>
       </c>
-      <c r="B517" s="1" t="s">
+      <c r="C517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="D517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="E517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="F517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="G517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="H517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="I517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="J517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="K517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="L517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="M517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="N517" s="2" t="s">
+        <v>7170</v>
+      </c>
+      <c r="O517" s="2" t="s">
+        <v>7170</v>
+      </c>
+    </row>
+    <row r="518" spans="1:15">
+      <c r="A518" s="2" t="s">
         <v>7171</v>
       </c>
-      <c r="C517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="E517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="F517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="G517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="H517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="I517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="J517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="K517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="L517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="M517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="N517" s="1" t="s">
-        <v>7171</v>
-      </c>
-      <c r="O517" s="1" t="s">
-        <v>7171</v>
-      </c>
-    </row>
-    <row r="518" spans="1:15">
-      <c r="A518" s="1" t="s">
+      <c r="B518" s="2" t="s">
         <v>7172</v>
       </c>
-      <c r="B518" s="1" t="s">
+      <c r="C518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="D518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="E518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="F518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="G518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="H518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="I518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="J518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="K518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="L518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="M518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="N518" s="2" t="s">
+        <v>7172</v>
+      </c>
+      <c r="O518" s="2" t="s">
+        <v>7172</v>
+      </c>
+    </row>
+    <row r="519" spans="1:15">
+      <c r="A519" s="2" t="s">
         <v>7173</v>
       </c>
-      <c r="C518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="D518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="E518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="F518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="G518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="H518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="I518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="J518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="K518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="L518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="M518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="N518" s="1" t="s">
-        <v>7173</v>
-      </c>
-      <c r="O518" s="1" t="s">
-        <v>7173</v>
-      </c>
-    </row>
-    <row r="519" spans="1:15">
-      <c r="A519" s="1" t="s">
+      <c r="B519" s="2" t="s">
         <v>7174</v>
       </c>
-      <c r="B519" s="1" t="s">
+      <c r="C519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="D519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="E519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="F519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="G519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="H519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="I519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="J519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="K519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="L519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="M519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="N519" s="2" t="s">
+        <v>7174</v>
+      </c>
+      <c r="O519" s="2" t="s">
+        <v>7174</v>
+      </c>
+    </row>
+    <row r="520" spans="1:15">
+      <c r="A520" s="2" t="s">
         <v>7175</v>
       </c>
-      <c r="C519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="D519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="E519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="F519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="G519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="H519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="I519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="J519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="K519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="L519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="M519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="N519" s="1" t="s">
-        <v>7175</v>
-      </c>
-      <c r="O519" s="1" t="s">
-        <v>7175</v>
-      </c>
-    </row>
-    <row r="520" spans="1:15">
-      <c r="A520" s="1" t="s">
+      <c r="B520" s="2" t="s">
         <v>7176</v>
       </c>
-      <c r="B520" s="1" t="s">
+      <c r="C520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="D520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="E520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="F520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="G520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="H520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="I520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="J520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="K520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="L520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="M520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="N520" s="2" t="s">
+        <v>7176</v>
+      </c>
+      <c r="O520" s="2" t="s">
+        <v>7176</v>
+      </c>
+    </row>
+    <row r="521" spans="1:15">
+      <c r="A521" s="2" t="s">
         <v>7177</v>
       </c>
-      <c r="C520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="D520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="E520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="F520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="G520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="H520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="I520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="J520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="K520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="L520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="M520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="N520" s="1" t="s">
-        <v>7177</v>
-      </c>
-      <c r="O520" s="1" t="s">
-        <v>7177</v>
-      </c>
-    </row>
-    <row r="521" spans="1:15">
-      <c r="A521" s="1" t="s">
+      <c r="B521" s="2" t="s">
         <v>7178</v>
       </c>
-      <c r="B521" s="1" t="s">
+      <c r="C521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="D521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="E521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="F521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="G521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="H521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="I521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="J521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="K521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="L521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="M521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="N521" s="2" t="s">
+        <v>7178</v>
+      </c>
+      <c r="O521" s="2" t="s">
+        <v>7178</v>
+      </c>
+    </row>
+    <row r="522" spans="1:15">
+      <c r="A522" s="2" t="s">
         <v>7179</v>
       </c>
-      <c r="C521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="D521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="E521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="F521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="G521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="H521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="I521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="J521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="K521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="L521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="M521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="N521" s="1" t="s">
-        <v>7179</v>
-      </c>
-      <c r="O521" s="1" t="s">
-        <v>7179</v>
-      </c>
-    </row>
-    <row r="522" spans="1:15">
-      <c r="A522" s="1" t="s">
+      <c r="B522" s="2" t="s">
         <v>7180</v>
       </c>
-      <c r="B522" s="1" t="s">
+      <c r="C522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="D522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="E522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="F522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="G522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="H522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="I522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="J522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="K522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="L522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="M522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="N522" s="2" t="s">
+        <v>7180</v>
+      </c>
+      <c r="O522" s="2" t="s">
+        <v>7180</v>
+      </c>
+    </row>
+    <row r="523" spans="1:15">
+      <c r="A523" s="5" t="s">
         <v>7181</v>
       </c>
-      <c r="C522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="D522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="E522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="F522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="G522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="H522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="I522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="J522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="K522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="L522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="M522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="N522" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="O522" s="1" t="s">
-        <v>7181</v>
-      </c>
-    </row>
-    <row r="523" spans="1:15">
-      <c r="A523" s="1" t="s">
+      <c r="B523" s="2" t="s">
         <v>7182</v>
       </c>
-      <c r="B523" s="1" t="s">
+      <c r="C523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="D523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="E523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="F523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="G523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="H523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="I523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="J523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="K523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="L523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="M523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="N523" s="2" t="s">
+        <v>7182</v>
+      </c>
+      <c r="O523" s="2" t="s">
+        <v>7182</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15">
+      <c r="A524" s="2" t="s">
         <v>7183</v>
       </c>
-      <c r="C523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="D523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="E523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="F523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="G523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="H523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="I523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="J523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="K523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="L523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="M523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="N523" s="1" t="s">
-        <v>7183</v>
-      </c>
-      <c r="O523" s="1" t="s">
-        <v>7183</v>
-      </c>
-    </row>
-    <row r="524" spans="1:15">
-      <c r="A524" s="4" t="s">
+      <c r="B524" s="2" t="s">
         <v>7184</v>
       </c>
-      <c r="B524" s="1" t="s">
+      <c r="C524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="D524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="E524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="F524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="G524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="H524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="I524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="J524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="K524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="L524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="M524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="N524" s="2" t="s">
+        <v>7184</v>
+      </c>
+      <c r="O524" s="2" t="s">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="525" spans="1:15">
+      <c r="A525" s="2" t="s">
         <v>7185</v>
       </c>
-      <c r="C524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="D524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="E524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="F524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="G524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="H524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="I524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="J524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="K524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="L524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="M524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="N524" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="O524" s="1" t="s">
-        <v>7185</v>
-      </c>
-    </row>
-    <row r="525" spans="1:15">
-      <c r="A525" s="1" t="s">
+      <c r="B525" s="2" t="s">
         <v>7186</v>
       </c>
-      <c r="B525" s="1" t="s">
+      <c r="C525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="D525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="E525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="F525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="G525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="H525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="I525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="J525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="K525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="L525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="M525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="N525" s="2" t="s">
+        <v>7186</v>
+      </c>
+      <c r="O525" s="2" t="s">
+        <v>7186</v>
+      </c>
+    </row>
+    <row r="526" spans="1:15">
+      <c r="A526" s="2" t="s">
         <v>7187</v>
       </c>
-      <c r="C525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="D525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="E525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="F525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="G525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="H525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="I525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="J525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="K525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="L525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="M525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="N525" s="1" t="s">
-        <v>7187</v>
-      </c>
-      <c r="O525" s="1" t="s">
-        <v>7187</v>
-      </c>
-    </row>
-    <row r="526" spans="1:15">
-      <c r="A526" s="1" t="s">
+      <c r="B526" s="2" t="s">
         <v>7188</v>
       </c>
-      <c r="B526" s="1" t="s">
+      <c r="C526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="D526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="E526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="F526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="G526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="H526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="I526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="J526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="K526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="L526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="M526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="N526" s="2" t="s">
+        <v>7188</v>
+      </c>
+      <c r="O526" s="2" t="s">
+        <v>7188</v>
+      </c>
+    </row>
+    <row r="527" spans="1:15">
+      <c r="A527" s="2" t="s">
         <v>7189</v>
       </c>
-      <c r="C526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="D526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="E526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="F526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="G526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="H526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="I526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="J526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="K526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="L526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="M526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="N526" s="1" t="s">
-        <v>7189</v>
-      </c>
-      <c r="O526" s="1" t="s">
-        <v>7189</v>
-      </c>
-    </row>
-    <row r="527" spans="1:15">
-      <c r="A527" s="1" t="s">
+      <c r="B527" s="2" t="s">
         <v>7190</v>
       </c>
-      <c r="B527" s="1" t="s">
+      <c r="C527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="C527" s="1" t="s">
+      <c r="D527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="D527" s="1" t="s">
+      <c r="E527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="E527" s="1" t="s">
+      <c r="F527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="F527" s="1" t="s">
+      <c r="G527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="G527" s="1" t="s">
+      <c r="H527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="H527" s="1" t="s">
+      <c r="I527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="I527" s="1" t="s">
+      <c r="J527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="J527" s="1" t="s">
+      <c r="K527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="K527" s="1" t="s">
+      <c r="L527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="L527" s="1" t="s">
+      <c r="M527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="M527" s="1" t="s">
+      <c r="N527" s="2" t="s">
         <v>7191</v>
       </c>
-      <c r="N527" s="1" t="s">
+      <c r="O527" s="2" t="s">
         <v>7191</v>
-      </c>
-      <c r="O527" s="1" t="s">
-        <v>7191</v>
-      </c>
-    </row>
-    <row r="528" spans="1:15">
-      <c r="A528" s="1" t="s">
-        <v>7192</v>
-      </c>
-      <c r="B528" s="1" t="s">
-        <v>7193</v>
-      </c>
-      <c r="C528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="D528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="E528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="F528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="G528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="H528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="I528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="J528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="K528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="L528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="M528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="N528" s="1" t="s">
-        <v>7194</v>
-      </c>
-      <c r="O528" s="1" t="s">
-        <v>7194</v>
       </c>
     </row>
   </sheetData>
@@ -47480,7 +47422,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A251 A119:O250 A118 A1:O117 C277 A277 A252:O276 A500 A501:O502 A503 A504:O510 C118:O118 A451:O499 C450:O450 A450 A279:O449" numberStoredAsText="1"/>
+    <ignoredError sqref="A279:O449 A450 C450:O450 A451:O499 C118:O118 A504:O510 A503 A501:O502 A500 A252:O276 A277 C277 A1:O117 A118 A119:O250 A251" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/apps/nuxt/i18n/i18n.xlsx
+++ b/apps/nuxt/i18n/i18n.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wysha_Object\wysha_Project\WebProjects\TypeWords\apps\nuxt\i18n\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DDB4A2-F2D5-40DB-8149-E64DA3037743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-16200" windowWidth="29010" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30720" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7950" uniqueCount="7163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7950" uniqueCount="7165">
   <si>
     <t>key</t>
   </si>
@@ -19724,6 +19718,12 @@
   </si>
   <si>
     <t>Важливе повідомлення</t>
+  </si>
+  <si>
+    <t>dont_show</t>
+  </si>
+  <si>
+    <t>不再显示</t>
   </si>
   <si>
     <t>function_desc</t>
@@ -21423,12 +21423,18 @@
     <t>遗忘曲线设置</t>
   </si>
   <si>
+    <t>不再机械重复，让你用更少时间记住更多单词。</t>
+  </si>
+  <si>
     <t>fsrs_limit_desc</t>
   </si>
   <si>
     <t>在学习过程中对每个单词错误次数进行评级，共有四个评级，Again,Hard,Good,Easy，遗忘曲线算法会使用评级来计算这个单词下一次需要复习的时间。</t>
   </si>
   <si>
+    <t>记得越牢，复习间隔越长；容易忘的内容，会更频繁出现。</t>
+  </si>
+  <si>
     <t>fsrs_easy_limit</t>
   </si>
   <si>
@@ -21504,59 +21510,47 @@
     <t>最大天数限制</t>
   </si>
   <si>
-    <t>dont_show</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不再显示</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>export_as_xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出为xlsx文件</t>
   </si>
   <si>
     <t>export_as_json</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>导出为xlsx文件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>导出为json文件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>xlsx_template_download</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>xlsx模板下载地址</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>import_xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>导入xlsx文件</t>
   </si>
   <si>
     <t>import_json</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>导入xlsx文件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>导入json文件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -21568,33 +21562,355 @@
       <sz val="11"/>
       <color rgb="FFCE9178"/>
       <name val="Consolas"/>
-      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -21602,31 +21918,321 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -21948,20 +22554,20 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O530"/>
-  <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="21.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22008,7 +22614,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -22055,7 +22661,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -22102,7 +22708,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -22149,7 +22755,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -22196,7 +22802,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -22243,7 +22849,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -22290,7 +22896,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -22337,7 +22943,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -22384,7 +22990,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -22431,7 +23037,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -22478,7 +23084,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>150</v>
       </c>
@@ -22525,7 +23131,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>165</v>
       </c>
@@ -22572,7 +23178,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>180</v>
       </c>
@@ -22619,7 +23225,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>195</v>
       </c>
@@ -22666,7 +23272,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>210</v>
       </c>
@@ -22713,7 +23319,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>225</v>
       </c>
@@ -22760,7 +23366,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>240</v>
       </c>
@@ -22807,7 +23413,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>255</v>
       </c>
@@ -22854,7 +23460,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>270</v>
       </c>
@@ -22901,7 +23507,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>285</v>
       </c>
@@ -22948,7 +23554,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>300</v>
       </c>
@@ -22995,7 +23601,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>314</v>
       </c>
@@ -23042,7 +23648,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>328</v>
       </c>
@@ -23089,7 +23695,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>342</v>
       </c>
@@ -23136,7 +23742,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>357</v>
       </c>
@@ -23183,7 +23789,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>372</v>
       </c>
@@ -23230,7 +23836,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>387</v>
       </c>
@@ -23277,7 +23883,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
         <v>402</v>
       </c>
@@ -23324,7 +23930,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>417</v>
       </c>
@@ -23371,7 +23977,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
         <v>432</v>
       </c>
@@ -23418,7 +24024,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
         <v>447</v>
       </c>
@@ -23465,7 +24071,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
         <v>462</v>
       </c>
@@ -23512,7 +24118,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
         <v>477</v>
       </c>
@@ -23559,7 +24165,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
         <v>492</v>
       </c>
@@ -23606,7 +24212,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
         <v>507</v>
       </c>
@@ -23653,7 +24259,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
         <v>510</v>
       </c>
@@ -23700,7 +24306,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
         <v>513</v>
       </c>
@@ -23747,7 +24353,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
         <v>528</v>
       </c>
@@ -23794,7 +24400,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
         <v>541</v>
       </c>
@@ -23841,7 +24447,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
         <v>556</v>
       </c>
@@ -23888,7 +24494,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
         <v>569</v>
       </c>
@@ -23935,7 +24541,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
         <v>582</v>
       </c>
@@ -23982,7 +24588,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
         <v>595</v>
       </c>
@@ -24029,7 +24635,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
         <v>610</v>
       </c>
@@ -24076,7 +24682,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
         <v>624</v>
       </c>
@@ -24123,7 +24729,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
         <v>638</v>
       </c>
@@ -24170,7 +24776,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
         <v>653</v>
       </c>
@@ -24217,7 +24823,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
         <v>667</v>
       </c>
@@ -24264,7 +24870,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
         <v>681</v>
       </c>
@@ -24311,7 +24917,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:15">
       <c r="A51" t="s">
         <v>694</v>
       </c>
@@ -24358,7 +24964,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
         <v>706</v>
       </c>
@@ -24405,7 +25011,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
         <v>719</v>
       </c>
@@ -24452,7 +25058,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15">
       <c r="A54" t="s">
         <v>732</v>
       </c>
@@ -24499,7 +25105,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:15">
       <c r="A55" t="s">
         <v>747</v>
       </c>
@@ -24546,7 +25152,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:15">
       <c r="A56" t="s">
         <v>760</v>
       </c>
@@ -24593,7 +25199,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:15">
       <c r="A57" t="s">
         <v>775</v>
       </c>
@@ -24640,7 +25246,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:15">
       <c r="A58" t="s">
         <v>790</v>
       </c>
@@ -24687,7 +25293,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:15">
       <c r="A59" t="s">
         <v>805</v>
       </c>
@@ -24734,7 +25340,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:15">
       <c r="A60" t="s">
         <v>820</v>
       </c>
@@ -24781,7 +25387,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:15">
       <c r="A61" t="s">
         <v>835</v>
       </c>
@@ -24828,7 +25434,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:15">
       <c r="A62" t="s">
         <v>850</v>
       </c>
@@ -24875,7 +25481,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:15">
       <c r="A63" t="s">
         <v>865</v>
       </c>
@@ -24922,7 +25528,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:15">
       <c r="A64" t="s">
         <v>880</v>
       </c>
@@ -24969,7 +25575,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:15">
       <c r="A65" t="s">
         <v>895</v>
       </c>
@@ -25016,7 +25622,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:15">
       <c r="A66" t="s">
         <v>910</v>
       </c>
@@ -25063,7 +25669,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:15">
       <c r="A67" t="s">
         <v>925</v>
       </c>
@@ -25110,7 +25716,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:15">
       <c r="A68" t="s">
         <v>940</v>
       </c>
@@ -25157,7 +25763,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:15">
       <c r="A69" t="s">
         <v>955</v>
       </c>
@@ -25204,7 +25810,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:15">
       <c r="A70" t="s">
         <v>970</v>
       </c>
@@ -25251,7 +25857,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:15">
       <c r="A71" t="s">
         <v>985</v>
       </c>
@@ -25298,7 +25904,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:15">
       <c r="A72" t="s">
         <v>1000</v>
       </c>
@@ -25345,7 +25951,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:15">
       <c r="A73" t="s">
         <v>1015</v>
       </c>
@@ -25392,7 +25998,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:15">
       <c r="A74" t="s">
         <v>1030</v>
       </c>
@@ -25439,7 +26045,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:15">
       <c r="A75" t="s">
         <v>1045</v>
       </c>
@@ -25486,7 +26092,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:15">
       <c r="A76" t="s">
         <v>1060</v>
       </c>
@@ -25533,7 +26139,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:15">
       <c r="A77" t="s">
         <v>1075</v>
       </c>
@@ -25580,7 +26186,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:15">
       <c r="A78" t="s">
         <v>1090</v>
       </c>
@@ -25627,7 +26233,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:15">
       <c r="A79" t="s">
         <v>1105</v>
       </c>
@@ -25674,7 +26280,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:15">
       <c r="A80" t="s">
         <v>1120</v>
       </c>
@@ -25721,7 +26327,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:15">
       <c r="A81" t="s">
         <v>1135</v>
       </c>
@@ -25768,7 +26374,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:15">
       <c r="A82" t="s">
         <v>1149</v>
       </c>
@@ -25815,7 +26421,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:15">
       <c r="A83" t="s">
         <v>1162</v>
       </c>
@@ -25862,7 +26468,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:15">
       <c r="A84" t="s">
         <v>1173</v>
       </c>
@@ -25909,7 +26515,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:15">
       <c r="A85" t="s">
         <v>1188</v>
       </c>
@@ -25956,7 +26562,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:15">
       <c r="A86" t="s">
         <v>1202</v>
       </c>
@@ -26003,7 +26609,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:15">
       <c r="A87" t="s">
         <v>1217</v>
       </c>
@@ -26050,7 +26656,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:15">
       <c r="A88" t="s">
         <v>1232</v>
       </c>
@@ -26097,7 +26703,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:15">
       <c r="A89" t="s">
         <v>1247</v>
       </c>
@@ -26144,7 +26750,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:15">
       <c r="A90" t="s">
         <v>1262</v>
       </c>
@@ -26191,7 +26797,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:15">
       <c r="A91" t="s">
         <v>1277</v>
       </c>
@@ -26238,7 +26844,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:15">
       <c r="A92" t="s">
         <v>1292</v>
       </c>
@@ -26285,7 +26891,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:15">
       <c r="A93" t="s">
         <v>1307</v>
       </c>
@@ -26332,7 +26938,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:15">
       <c r="A94" t="s">
         <v>1321</v>
       </c>
@@ -26379,7 +26985,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:15">
       <c r="A95" t="s">
         <v>1336</v>
       </c>
@@ -26426,7 +27032,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:15">
       <c r="A96" t="s">
         <v>1351</v>
       </c>
@@ -26473,7 +27079,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:15">
       <c r="A97" t="s">
         <v>1366</v>
       </c>
@@ -26520,7 +27126,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:15">
       <c r="A98" t="s">
         <v>1381</v>
       </c>
@@ -26567,7 +27173,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:15">
       <c r="A99" t="s">
         <v>1396</v>
       </c>
@@ -26614,7 +27220,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:15">
       <c r="A100" t="s">
         <v>1411</v>
       </c>
@@ -26661,7 +27267,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:15">
       <c r="A101" t="s">
         <v>1426</v>
       </c>
@@ -26708,7 +27314,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:15">
       <c r="A102" t="s">
         <v>1441</v>
       </c>
@@ -26755,7 +27361,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:15">
       <c r="A103" t="s">
         <v>1456</v>
       </c>
@@ -26802,7 +27408,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:15">
       <c r="A104" t="s">
         <v>1470</v>
       </c>
@@ -26849,7 +27455,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:15">
       <c r="A105" t="s">
         <v>1485</v>
       </c>
@@ -26896,7 +27502,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:15">
       <c r="A106" t="s">
         <v>1500</v>
       </c>
@@ -26943,7 +27549,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:15">
       <c r="A107" t="s">
         <v>1515</v>
       </c>
@@ -26990,7 +27596,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:15">
       <c r="A108" t="s">
         <v>1530</v>
       </c>
@@ -27037,7 +27643,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:15">
       <c r="A109" t="s">
         <v>1545</v>
       </c>
@@ -27084,7 +27690,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:15">
       <c r="A110" t="s">
         <v>1560</v>
       </c>
@@ -27131,7 +27737,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:15">
       <c r="A111" t="s">
         <v>1574</v>
       </c>
@@ -27178,7 +27784,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:15">
       <c r="A112" t="s">
         <v>1589</v>
       </c>
@@ -27225,7 +27831,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:15">
       <c r="A113" t="s">
         <v>1604</v>
       </c>
@@ -27272,7 +27878,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:15">
       <c r="A114" t="s">
         <v>1619</v>
       </c>
@@ -27319,7 +27925,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:15">
       <c r="A115" t="s">
         <v>1634</v>
       </c>
@@ -27366,7 +27972,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:15">
       <c r="A116" t="s">
         <v>1649</v>
       </c>
@@ -27413,7 +28019,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:15">
       <c r="A117" t="s">
         <v>1660</v>
       </c>
@@ -27460,7 +28066,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="118" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:15">
       <c r="A118" t="s">
         <v>1673</v>
       </c>
@@ -27507,7 +28113,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:15">
       <c r="A119" t="s">
         <v>1688</v>
       </c>
@@ -27554,7 +28160,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:15">
       <c r="A120" t="s">
         <v>1703</v>
       </c>
@@ -27601,7 +28207,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:15">
       <c r="A121" t="s">
         <v>1718</v>
       </c>
@@ -27648,7 +28254,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:15">
       <c r="A122" t="s">
         <v>1732</v>
       </c>
@@ -27695,7 +28301,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:15">
       <c r="A123" t="s">
         <v>1747</v>
       </c>
@@ -27742,7 +28348,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:15">
       <c r="A124" t="s">
         <v>1762</v>
       </c>
@@ -27789,7 +28395,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:15">
       <c r="A125" t="s">
         <v>1777</v>
       </c>
@@ -27836,7 +28442,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:15">
       <c r="A126" t="s">
         <v>1792</v>
       </c>
@@ -27883,7 +28489,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:15">
       <c r="A127" t="s">
         <v>1807</v>
       </c>
@@ -27930,7 +28536,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:15">
       <c r="A128" t="s">
         <v>1822</v>
       </c>
@@ -27977,7 +28583,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:15">
       <c r="A129" t="s">
         <v>1837</v>
       </c>
@@ -28024,7 +28630,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:15">
       <c r="A130" t="s">
         <v>1850</v>
       </c>
@@ -28071,7 +28677,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:15">
       <c r="A131" t="s">
         <v>1862</v>
       </c>
@@ -28118,7 +28724,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:15">
       <c r="A132" t="s">
         <v>1877</v>
       </c>
@@ -28165,7 +28771,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:15">
       <c r="A133" t="s">
         <v>1882</v>
       </c>
@@ -28212,7 +28818,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:15">
       <c r="A134" t="s">
         <v>1897</v>
       </c>
@@ -28259,7 +28865,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:15">
       <c r="A135" t="s">
         <v>1912</v>
       </c>
@@ -28306,7 +28912,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:15">
       <c r="A136" t="s">
         <v>1927</v>
       </c>
@@ -28353,7 +28959,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:15">
       <c r="A137" t="s">
         <v>1942</v>
       </c>
@@ -28400,7 +29006,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:15">
       <c r="A138" t="s">
         <v>1957</v>
       </c>
@@ -28447,7 +29053,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:15">
       <c r="A139" t="s">
         <v>1972</v>
       </c>
@@ -28494,7 +29100,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:15">
       <c r="A140" t="s">
         <v>1986</v>
       </c>
@@ -28541,7 +29147,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:15">
       <c r="A141" t="s">
         <v>2001</v>
       </c>
@@ -28588,7 +29194,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:15">
       <c r="A142" t="s">
         <v>2016</v>
       </c>
@@ -28635,7 +29241,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:15">
       <c r="A143" t="s">
         <v>2031</v>
       </c>
@@ -28682,7 +29288,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:15">
       <c r="A144" t="s">
         <v>2046</v>
       </c>
@@ -28729,7 +29335,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:15">
       <c r="A145" t="s">
         <v>2061</v>
       </c>
@@ -28776,7 +29382,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:15">
       <c r="A146" t="s">
         <v>2075</v>
       </c>
@@ -28823,7 +29429,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:15">
       <c r="A147" t="s">
         <v>2090</v>
       </c>
@@ -28870,7 +29476,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:15">
       <c r="A148" t="s">
         <v>2105</v>
       </c>
@@ -28917,7 +29523,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:15">
       <c r="A149" t="s">
         <v>2120</v>
       </c>
@@ -28964,7 +29570,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:15">
       <c r="A150" t="s">
         <v>2135</v>
       </c>
@@ -29011,7 +29617,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:15">
       <c r="A151" t="s">
         <v>2150</v>
       </c>
@@ -29058,7 +29664,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:15">
       <c r="A152" t="s">
         <v>2164</v>
       </c>
@@ -29105,7 +29711,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:15">
       <c r="A153" t="s">
         <v>2170</v>
       </c>
@@ -29152,7 +29758,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:15">
       <c r="A154" t="s">
         <v>2183</v>
       </c>
@@ -29199,7 +29805,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:15">
       <c r="A155" t="s">
         <v>2198</v>
       </c>
@@ -29246,7 +29852,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:15">
       <c r="A156" t="s">
         <v>2212</v>
       </c>
@@ -29293,7 +29899,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:15">
       <c r="A157" t="s">
         <v>2223</v>
       </c>
@@ -29340,7 +29946,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:15">
       <c r="A158" t="s">
         <v>2237</v>
       </c>
@@ -29387,7 +29993,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:15">
       <c r="A159" t="s">
         <v>2252</v>
       </c>
@@ -29434,7 +30040,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:15">
       <c r="A160" t="s">
         <v>2267</v>
       </c>
@@ -29481,7 +30087,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:15">
       <c r="A161" t="s">
         <v>2282</v>
       </c>
@@ -29528,7 +30134,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:15">
       <c r="A162" t="s">
         <v>2297</v>
       </c>
@@ -29575,7 +30181,7 @@
         <v>2311</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:15">
       <c r="A163" t="s">
         <v>2312</v>
       </c>
@@ -29622,7 +30228,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:15">
       <c r="A164" t="s">
         <v>2327</v>
       </c>
@@ -29669,7 +30275,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:15">
       <c r="A165" t="s">
         <v>2341</v>
       </c>
@@ -29716,7 +30322,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:15">
       <c r="A166" t="s">
         <v>2355</v>
       </c>
@@ -29763,7 +30369,7 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:15">
       <c r="A167" t="s">
         <v>2367</v>
       </c>
@@ -29810,7 +30416,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:15">
       <c r="A168" t="s">
         <v>2382</v>
       </c>
@@ -29857,7 +30463,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:15">
       <c r="A169" t="s">
         <v>2397</v>
       </c>
@@ -29904,7 +30510,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:15">
       <c r="A170" t="s">
         <v>2412</v>
       </c>
@@ -29951,7 +30557,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:15">
       <c r="A171" t="s">
         <v>2427</v>
       </c>
@@ -29998,7 +30604,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:15">
       <c r="A172" t="s">
         <v>2442</v>
       </c>
@@ -30045,7 +30651,7 @@
         <v>2445</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:15">
       <c r="A173" t="s">
         <v>2454</v>
       </c>
@@ -30092,7 +30698,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:15">
       <c r="A174" t="s">
         <v>2467</v>
       </c>
@@ -30139,7 +30745,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:15">
       <c r="A175" t="s">
         <v>2482</v>
       </c>
@@ -30186,7 +30792,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:15">
       <c r="A176" t="s">
         <v>2497</v>
       </c>
@@ -30233,7 +30839,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:15">
       <c r="A177" t="s">
         <v>2512</v>
       </c>
@@ -30280,7 +30886,7 @@
         <v>2526</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:15">
       <c r="A178" t="s">
         <v>2527</v>
       </c>
@@ -30327,7 +30933,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:15">
       <c r="A179" t="s">
         <v>2542</v>
       </c>
@@ -30374,7 +30980,7 @@
         <v>2545</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:15">
       <c r="A180" t="s">
         <v>2556</v>
       </c>
@@ -30421,7 +31027,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:15">
       <c r="A181" t="s">
         <v>2571</v>
       </c>
@@ -30468,7 +31074,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:15">
       <c r="A182" t="s">
         <v>2585</v>
       </c>
@@ -30515,7 +31121,7 @@
         <v>2586</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:15">
       <c r="A183" t="s">
         <v>2597</v>
       </c>
@@ -30562,7 +31168,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:15">
       <c r="A184" t="s">
         <v>2612</v>
       </c>
@@ -30609,7 +31215,7 @@
         <v>2626</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:15">
       <c r="A185" t="s">
         <v>2627</v>
       </c>
@@ -30656,7 +31262,7 @@
         <v>2641</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:15">
       <c r="A186" t="s">
         <v>2642</v>
       </c>
@@ -30703,7 +31309,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:15">
       <c r="A187" t="s">
         <v>2657</v>
       </c>
@@ -30750,7 +31356,7 @@
         <v>2671</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:15">
       <c r="A188" t="s">
         <v>2672</v>
       </c>
@@ -30797,7 +31403,7 @@
         <v>2686</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:15">
       <c r="A189" t="s">
         <v>2687</v>
       </c>
@@ -30844,7 +31450,7 @@
         <v>2701</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:15">
       <c r="A190" t="s">
         <v>2702</v>
       </c>
@@ -30891,7 +31497,7 @@
         <v>2716</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:15">
       <c r="A191" t="s">
         <v>2717</v>
       </c>
@@ -30938,7 +31544,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:15">
       <c r="A192" t="s">
         <v>2732</v>
       </c>
@@ -30985,7 +31591,7 @@
         <v>2745</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:15">
       <c r="A193" t="s">
         <v>2746</v>
       </c>
@@ -31032,7 +31638,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:15">
       <c r="A194" t="s">
         <v>2759</v>
       </c>
@@ -31079,7 +31685,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:15">
       <c r="A195" t="s">
         <v>2771</v>
       </c>
@@ -31126,7 +31732,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:15">
       <c r="A196" t="s">
         <v>2785</v>
       </c>
@@ -31173,7 +31779,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:15">
       <c r="A197" t="s">
         <v>2799</v>
       </c>
@@ -31220,7 +31826,7 @@
         <v>2812</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:15">
       <c r="A198" t="s">
         <v>2813</v>
       </c>
@@ -31267,7 +31873,7 @@
         <v>2827</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:15">
       <c r="A199" t="s">
         <v>2828</v>
       </c>
@@ -31314,7 +31920,7 @@
         <v>2829</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:15">
       <c r="A200" t="s">
         <v>2832</v>
       </c>
@@ -31361,7 +31967,7 @@
         <v>2833</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:15">
       <c r="A201" t="s">
         <v>2846</v>
       </c>
@@ -31408,7 +32014,7 @@
         <v>2860</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:15">
       <c r="A202" t="s">
         <v>2861</v>
       </c>
@@ -31455,7 +32061,7 @@
         <v>2862</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:15">
       <c r="A203" t="s">
         <v>2875</v>
       </c>
@@ -31502,7 +32108,7 @@
         <v>2889</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:15">
       <c r="A204" t="s">
         <v>2890</v>
       </c>
@@ -31549,7 +32155,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:15">
       <c r="A205" t="s">
         <v>2905</v>
       </c>
@@ -31596,7 +32202,7 @@
         <v>2919</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:15">
       <c r="A206" t="s">
         <v>2920</v>
       </c>
@@ -31643,7 +32249,7 @@
         <v>2934</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:15">
       <c r="A207" t="s">
         <v>2935</v>
       </c>
@@ -31690,7 +32296,7 @@
         <v>2949</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:15">
       <c r="A208" t="s">
         <v>2950</v>
       </c>
@@ -31737,7 +32343,7 @@
         <v>2951</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:15">
       <c r="A209" t="s">
         <v>2961</v>
       </c>
@@ -31784,7 +32390,7 @@
         <v>2962</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:15">
       <c r="A210" t="s">
         <v>2975</v>
       </c>
@@ -31831,7 +32437,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:15">
       <c r="A211" t="s">
         <v>2989</v>
       </c>
@@ -31878,7 +32484,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:15">
       <c r="A212" t="s">
         <v>3004</v>
       </c>
@@ -31925,7 +32531,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:15">
       <c r="A213" t="s">
         <v>3017</v>
       </c>
@@ -31972,7 +32578,7 @@
         <v>3020</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:15">
       <c r="A214" t="s">
         <v>3021</v>
       </c>
@@ -32019,7 +32625,7 @@
         <v>3035</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:15">
       <c r="A215" t="s">
         <v>3036</v>
       </c>
@@ -32066,7 +32672,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:15">
       <c r="A216" t="s">
         <v>3040</v>
       </c>
@@ -32113,7 +32719,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:15">
       <c r="A217" t="s">
         <v>3055</v>
       </c>
@@ -32160,7 +32766,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:15">
       <c r="A218" t="s">
         <v>3065</v>
       </c>
@@ -32207,7 +32813,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:15">
       <c r="A219" t="s">
         <v>3080</v>
       </c>
@@ -32254,7 +32860,7 @@
         <v>3093</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:15">
       <c r="A220" t="s">
         <v>3094</v>
       </c>
@@ -32301,7 +32907,7 @@
         <v>3108</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:15">
       <c r="A221" t="s">
         <v>3109</v>
       </c>
@@ -32348,7 +32954,7 @@
         <v>3123</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:15">
       <c r="A222" t="s">
         <v>3124</v>
       </c>
@@ -32395,7 +33001,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:15">
       <c r="A223" t="s">
         <v>3137</v>
       </c>
@@ -32442,7 +33048,7 @@
         <v>3151</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:15">
       <c r="A224" t="s">
         <v>3152</v>
       </c>
@@ -32489,7 +33095,7 @@
         <v>3153</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:15">
       <c r="A225" t="s">
         <v>3165</v>
       </c>
@@ -32536,7 +33142,7 @@
         <v>3179</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:15">
       <c r="A226" t="s">
         <v>3180</v>
       </c>
@@ -32583,7 +33189,7 @@
         <v>3194</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:15">
       <c r="A227" t="s">
         <v>3195</v>
       </c>
@@ -32630,7 +33236,7 @@
         <v>3209</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:15">
       <c r="A228" t="s">
         <v>3210</v>
       </c>
@@ -32677,7 +33283,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:15">
       <c r="A229" t="s">
         <v>3224</v>
       </c>
@@ -32724,7 +33330,7 @@
         <v>3238</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:15">
       <c r="A230" t="s">
         <v>3239</v>
       </c>
@@ -32771,7 +33377,7 @@
         <v>3253</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:15">
       <c r="A231" t="s">
         <v>3254</v>
       </c>
@@ -32818,7 +33424,7 @@
         <v>3268</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:15">
       <c r="A232" t="s">
         <v>3269</v>
       </c>
@@ -32865,7 +33471,7 @@
         <v>3283</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:15">
       <c r="A233" t="s">
         <v>3284</v>
       </c>
@@ -32912,7 +33518,7 @@
         <v>3298</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:15">
       <c r="A234" t="s">
         <v>3299</v>
       </c>
@@ -32959,7 +33565,7 @@
         <v>3313</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:15">
       <c r="A235" t="s">
         <v>3314</v>
       </c>
@@ -33006,7 +33612,7 @@
         <v>3328</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:15">
       <c r="A236" t="s">
         <v>3329</v>
       </c>
@@ -33053,7 +33659,7 @@
         <v>3343</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:15">
       <c r="A237" t="s">
         <v>3344</v>
       </c>
@@ -33100,7 +33706,7 @@
         <v>3345</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:15">
       <c r="A238" t="s">
         <v>3358</v>
       </c>
@@ -33147,7 +33753,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:15">
       <c r="A239" t="s">
         <v>3373</v>
       </c>
@@ -33194,7 +33800,7 @@
         <v>3387</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:15">
       <c r="A240" t="s">
         <v>3388</v>
       </c>
@@ -33241,7 +33847,7 @@
         <v>3402</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:15">
       <c r="A241" t="s">
         <v>3403</v>
       </c>
@@ -33288,7 +33894,7 @@
         <v>3404</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:15">
       <c r="A242" t="s">
         <v>3416</v>
       </c>
@@ -33335,7 +33941,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:15">
       <c r="A243" t="s">
         <v>3430</v>
       </c>
@@ -33382,7 +33988,7 @@
         <v>3444</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:15">
       <c r="A244" t="s">
         <v>3445</v>
       </c>
@@ -33429,7 +34035,7 @@
         <v>3459</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:15">
       <c r="A245" t="s">
         <v>3460</v>
       </c>
@@ -33476,7 +34082,7 @@
         <v>3461</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:15">
       <c r="A246" t="s">
         <v>3470</v>
       </c>
@@ -33523,7 +34129,7 @@
         <v>3484</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:15">
       <c r="A247" t="s">
         <v>3485</v>
       </c>
@@ -33570,7 +34176,7 @@
         <v>3499</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:15">
       <c r="A248" t="s">
         <v>3500</v>
       </c>
@@ -33617,7 +34223,7 @@
         <v>3514</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:15">
       <c r="A249" t="s">
         <v>3515</v>
       </c>
@@ -33664,7 +34270,7 @@
         <v>3529</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:15">
       <c r="A250" t="s">
         <v>3530</v>
       </c>
@@ -33711,7 +34317,7 @@
         <v>3544</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:15">
       <c r="A251" t="s">
         <v>3545</v>
       </c>
@@ -33758,7 +34364,7 @@
         <v>3559</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:15">
       <c r="A252" t="s">
         <v>3560</v>
       </c>
@@ -33805,7 +34411,7 @@
         <v>3574</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:15">
       <c r="A253" t="s">
         <v>3575</v>
       </c>
@@ -33852,7 +34458,7 @@
         <v>3589</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:15">
       <c r="A254" t="s">
         <v>3590</v>
       </c>
@@ -33899,7 +34505,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:15">
       <c r="A255" t="s">
         <v>3604</v>
       </c>
@@ -33946,7 +34552,7 @@
         <v>3618</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:15">
       <c r="A256" t="s">
         <v>3619</v>
       </c>
@@ -33993,7 +34599,7 @@
         <v>3633</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:15">
       <c r="A257" t="s">
         <v>3634</v>
       </c>
@@ -34040,7 +34646,7 @@
         <v>3648</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:15">
       <c r="A258" t="s">
         <v>3649</v>
       </c>
@@ -34087,7 +34693,7 @@
         <v>3663</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:15">
       <c r="A259" t="s">
         <v>3664</v>
       </c>
@@ -34134,7 +34740,7 @@
         <v>3678</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:15">
       <c r="A260" t="s">
         <v>3679</v>
       </c>
@@ -34181,7 +34787,7 @@
         <v>3693</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:15">
       <c r="A261" t="s">
         <v>3694</v>
       </c>
@@ -34228,7 +34834,7 @@
         <v>3695</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:15">
       <c r="A262" t="s">
         <v>3703</v>
       </c>
@@ -34275,7 +34881,7 @@
         <v>3717</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:15">
       <c r="A263" t="s">
         <v>3718</v>
       </c>
@@ -34322,7 +34928,7 @@
         <v>3719</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:15">
       <c r="A264" t="s">
         <v>3732</v>
       </c>
@@ -34369,7 +34975,7 @@
         <v>3733</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:15">
       <c r="A265" t="s">
         <v>3746</v>
       </c>
@@ -34416,7 +35022,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:15">
       <c r="A266" t="s">
         <v>3761</v>
       </c>
@@ -34463,7 +35069,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:15">
       <c r="A267" t="s">
         <v>3776</v>
       </c>
@@ -34510,7 +35116,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:15">
       <c r="A268" t="s">
         <v>3777</v>
       </c>
@@ -34557,7 +35163,7 @@
         <v>3791</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:15">
       <c r="A269" t="s">
         <v>3792</v>
       </c>
@@ -34604,7 +35210,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:15">
       <c r="A270" t="s">
         <v>3807</v>
       </c>
@@ -34651,7 +35257,7 @@
         <v>3808</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:15">
       <c r="A271" t="s">
         <v>3817</v>
       </c>
@@ -34698,7 +35304,7 @@
         <v>3818</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:15">
       <c r="A272" t="s">
         <v>3830</v>
       </c>
@@ -34745,7 +35351,7 @@
         <v>3831</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:15">
       <c r="A273" t="s">
         <v>3844</v>
       </c>
@@ -34792,7 +35398,7 @@
         <v>3845</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:15">
       <c r="A274" t="s">
         <v>3858</v>
       </c>
@@ -34839,7 +35445,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:15">
       <c r="A275" t="s">
         <v>3872</v>
       </c>
@@ -34886,7 +35492,7 @@
         <v>3875</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:15">
       <c r="A276" t="s">
         <v>3876</v>
       </c>
@@ -34933,7 +35539,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:15">
       <c r="A277" t="s">
         <v>3889</v>
       </c>
@@ -34980,7 +35586,7 @@
         <v>3903</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:15">
       <c r="A278" t="s">
         <v>3904</v>
       </c>
@@ -35027,7 +35633,7 @@
         <v>3918</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:15">
       <c r="A279" t="s">
         <v>3919</v>
       </c>
@@ -35074,7 +35680,7 @@
         <v>3933</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:15">
       <c r="A280" t="s">
         <v>3934</v>
       </c>
@@ -35121,7 +35727,7 @@
         <v>3948</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:15">
       <c r="A281" t="s">
         <v>3949</v>
       </c>
@@ -35168,7 +35774,7 @@
         <v>3963</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:15">
       <c r="A282" t="s">
         <v>3964</v>
       </c>
@@ -35215,7 +35821,7 @@
         <v>3978</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:15">
       <c r="A283" t="s">
         <v>3979</v>
       </c>
@@ -35262,7 +35868,7 @@
         <v>3993</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:15">
       <c r="A284" t="s">
         <v>3994</v>
       </c>
@@ -35309,7 +35915,7 @@
         <v>4008</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:15">
       <c r="A285" t="s">
         <v>4009</v>
       </c>
@@ -35356,7 +35962,7 @@
         <v>4023</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:15">
       <c r="A286" t="s">
         <v>4024</v>
       </c>
@@ -35403,7 +36009,7 @@
         <v>4025</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:15">
       <c r="A287" t="s">
         <v>4038</v>
       </c>
@@ -35450,7 +36056,7 @@
         <v>4052</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:15">
       <c r="A288" t="s">
         <v>4053</v>
       </c>
@@ -35497,7 +36103,7 @@
         <v>4054</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:15">
       <c r="A289" t="s">
         <v>4067</v>
       </c>
@@ -35544,7 +36150,7 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:15">
       <c r="A290" t="s">
         <v>4081</v>
       </c>
@@ -35591,7 +36197,7 @@
         <v>4088</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:15">
       <c r="A291" t="s">
         <v>4089</v>
       </c>
@@ -35638,7 +36244,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:15">
       <c r="A292" t="s">
         <v>4104</v>
       </c>
@@ -35685,7 +36291,7 @@
         <v>4118</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:15">
       <c r="A293" t="s">
         <v>4119</v>
       </c>
@@ -35732,7 +36338,7 @@
         <v>4120</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:15">
       <c r="A294" t="s">
         <v>4133</v>
       </c>
@@ -35779,7 +36385,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:15">
       <c r="A295" t="s">
         <v>4148</v>
       </c>
@@ -35826,7 +36432,7 @@
         <v>4162</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:15">
       <c r="A296" t="s">
         <v>4163</v>
       </c>
@@ -35873,7 +36479,7 @@
         <v>4177</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:15">
       <c r="A297" t="s">
         <v>4178</v>
       </c>
@@ -35920,7 +36526,7 @@
         <v>4192</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:15">
       <c r="A298" t="s">
         <v>4193</v>
       </c>
@@ -35967,7 +36573,7 @@
         <v>4207</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:15">
       <c r="A299" t="s">
         <v>4208</v>
       </c>
@@ -36014,7 +36620,7 @@
         <v>4222</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:15">
       <c r="A300" t="s">
         <v>4223</v>
       </c>
@@ -36061,7 +36667,7 @@
         <v>4237</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:15">
       <c r="A301" t="s">
         <v>4238</v>
       </c>
@@ -36108,7 +36714,7 @@
         <v>4250</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:15">
       <c r="A302" t="s">
         <v>4251</v>
       </c>
@@ -36155,7 +36761,7 @@
         <v>4252</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:15">
       <c r="A303" t="s">
         <v>4263</v>
       </c>
@@ -36202,7 +36808,7 @@
         <v>4277</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:15">
       <c r="A304" t="s">
         <v>4278</v>
       </c>
@@ -36249,7 +36855,7 @@
         <v>4279</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:15">
       <c r="A305" t="s">
         <v>4292</v>
       </c>
@@ -36296,7 +36902,7 @@
         <v>4306</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:15">
       <c r="A306" t="s">
         <v>4307</v>
       </c>
@@ -36343,7 +36949,7 @@
         <v>4321</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:15">
       <c r="A307" t="s">
         <v>4322</v>
       </c>
@@ -36390,7 +36996,7 @@
         <v>4336</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:15">
       <c r="A308" t="s">
         <v>4337</v>
       </c>
@@ -36437,7 +37043,7 @@
         <v>4351</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:15">
       <c r="A309" t="s">
         <v>4352</v>
       </c>
@@ -36484,7 +37090,7 @@
         <v>4366</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:15">
       <c r="A310" t="s">
         <v>4367</v>
       </c>
@@ -36531,7 +37137,7 @@
         <v>4381</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:15">
       <c r="A311" t="s">
         <v>4382</v>
       </c>
@@ -36578,7 +37184,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:15">
       <c r="A312" t="s">
         <v>4397</v>
       </c>
@@ -36625,7 +37231,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:15">
       <c r="A313" t="s">
         <v>4412</v>
       </c>
@@ -36672,7 +37278,7 @@
         <v>4426</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:15">
       <c r="A314" t="s">
         <v>4427</v>
       </c>
@@ -36719,7 +37325,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:15">
       <c r="A315" t="s">
         <v>4442</v>
       </c>
@@ -36766,7 +37372,7 @@
         <v>4443</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:15">
       <c r="A316" t="s">
         <v>4456</v>
       </c>
@@ -36813,7 +37419,7 @@
         <v>4457</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:15">
       <c r="A317" t="s">
         <v>4470</v>
       </c>
@@ -36860,7 +37466,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:15">
       <c r="A318" t="s">
         <v>4485</v>
       </c>
@@ -36907,7 +37513,7 @@
         <v>4499</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:15">
       <c r="A319" t="s">
         <v>4500</v>
       </c>
@@ -36954,7 +37560,7 @@
         <v>4501</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:15">
       <c r="A320" t="s">
         <v>4514</v>
       </c>
@@ -37001,7 +37607,7 @@
         <v>4515</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:15">
       <c r="A321" t="s">
         <v>4528</v>
       </c>
@@ -37048,7 +37654,7 @@
         <v>4529</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:15">
       <c r="A322" t="s">
         <v>4542</v>
       </c>
@@ -37095,7 +37701,7 @@
         <v>4543</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:15">
       <c r="A323" t="s">
         <v>4556</v>
       </c>
@@ -37142,7 +37748,7 @@
         <v>4570</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:15">
       <c r="A324" t="s">
         <v>4571</v>
       </c>
@@ -37189,7 +37795,7 @@
         <v>4585</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:15">
       <c r="A325" t="s">
         <v>4586</v>
       </c>
@@ -37236,7 +37842,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:15">
       <c r="A326" t="s">
         <v>4601</v>
       </c>
@@ -37283,7 +37889,7 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:15">
       <c r="A327" t="s">
         <v>4616</v>
       </c>
@@ -37330,7 +37936,7 @@
         <v>4630</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:15">
       <c r="A328" t="s">
         <v>4631</v>
       </c>
@@ -37377,7 +37983,7 @@
         <v>4645</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:15">
       <c r="A329" t="s">
         <v>4646</v>
       </c>
@@ -37424,7 +38030,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:15">
       <c r="A330" t="s">
         <v>4660</v>
       </c>
@@ -37471,7 +38077,7 @@
         <v>4661</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:15">
       <c r="A331" t="s">
         <v>4674</v>
       </c>
@@ -37518,7 +38124,7 @@
         <v>4688</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:15">
       <c r="A332" t="s">
         <v>4689</v>
       </c>
@@ -37565,7 +38171,7 @@
         <v>4703</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:15">
       <c r="A333" t="s">
         <v>4704</v>
       </c>
@@ -37612,7 +38218,7 @@
         <v>4717</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:15">
       <c r="A334" t="s">
         <v>4718</v>
       </c>
@@ -37659,7 +38265,7 @@
         <v>4719</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:15">
       <c r="A335" t="s">
         <v>4731</v>
       </c>
@@ -37706,7 +38312,7 @@
         <v>4745</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:15">
       <c r="A336" t="s">
         <v>4746</v>
       </c>
@@ -37753,7 +38359,7 @@
         <v>4759</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:15">
       <c r="A337" t="s">
         <v>4760</v>
       </c>
@@ -37800,7 +38406,7 @@
         <v>4763</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:15">
       <c r="A338" t="s">
         <v>4772</v>
       </c>
@@ -37847,7 +38453,7 @@
         <v>4786</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:15">
       <c r="A339" t="s">
         <v>4787</v>
       </c>
@@ -37894,7 +38500,7 @@
         <v>4801</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="340" spans="1:15">
       <c r="A340" t="s">
         <v>4802</v>
       </c>
@@ -37941,7 +38547,7 @@
         <v>4803</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:15">
       <c r="A341" t="s">
         <v>4812</v>
       </c>
@@ -37988,7 +38594,7 @@
         <v>4813</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:15">
       <c r="A342" t="s">
         <v>4826</v>
       </c>
@@ -38035,7 +38641,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:15">
       <c r="A343" t="s">
         <v>4840</v>
       </c>
@@ -38082,7 +38688,7 @@
         <v>4841</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:15">
       <c r="A344" t="s">
         <v>4854</v>
       </c>
@@ -38129,7 +38735,7 @@
         <v>4867</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:15">
       <c r="A345" t="s">
         <v>4868</v>
       </c>
@@ -38176,7 +38782,7 @@
         <v>4869</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:15">
       <c r="A346" t="s">
         <v>4878</v>
       </c>
@@ -38223,7 +38829,7 @@
         <v>4892</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:15">
       <c r="A347" t="s">
         <v>4893</v>
       </c>
@@ -38270,7 +38876,7 @@
         <v>4907</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:15">
       <c r="A348" t="s">
         <v>4908</v>
       </c>
@@ -38317,7 +38923,7 @@
         <v>4922</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:15">
       <c r="A349" t="s">
         <v>4923</v>
       </c>
@@ -38364,7 +38970,7 @@
         <v>4924</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:15">
       <c r="A350" t="s">
         <v>4937</v>
       </c>
@@ -38411,7 +39017,7 @@
         <v>4950</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:15">
       <c r="A351" t="s">
         <v>4951</v>
       </c>
@@ -38458,7 +39064,7 @@
         <v>4965</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:15">
       <c r="A352" t="s">
         <v>4966</v>
       </c>
@@ -38505,7 +39111,7 @@
         <v>4980</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:15">
       <c r="A353" t="s">
         <v>4981</v>
       </c>
@@ -38552,7 +39158,7 @@
         <v>4995</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:15">
       <c r="A354" t="s">
         <v>4996</v>
       </c>
@@ -38599,7 +39205,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:15">
       <c r="A355" t="s">
         <v>5011</v>
       </c>
@@ -38646,7 +39252,7 @@
         <v>5012</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:15">
       <c r="A356" t="s">
         <v>5025</v>
       </c>
@@ -38693,7 +39299,7 @@
         <v>5026</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:15">
       <c r="A357" t="s">
         <v>5037</v>
       </c>
@@ -38740,7 +39346,7 @@
         <v>5049</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:15">
       <c r="A358" t="s">
         <v>5050</v>
       </c>
@@ -38787,7 +39393,7 @@
         <v>5064</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:15">
       <c r="A359" t="s">
         <v>5065</v>
       </c>
@@ -38834,7 +39440,7 @@
         <v>5066</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:15">
       <c r="A360" t="s">
         <v>5079</v>
       </c>
@@ -38881,7 +39487,7 @@
         <v>5093</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:15">
       <c r="A361" t="s">
         <v>5094</v>
       </c>
@@ -38928,7 +39534,7 @@
         <v>5108</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:15">
       <c r="A362" t="s">
         <v>5109</v>
       </c>
@@ -38975,7 +39581,7 @@
         <v>5110</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:15">
       <c r="A363" t="s">
         <v>5123</v>
       </c>
@@ -39022,7 +39628,7 @@
         <v>5137</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:15">
       <c r="A364" t="s">
         <v>5138</v>
       </c>
@@ -39069,7 +39675,7 @@
         <v>5139</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:15">
       <c r="A365" t="s">
         <v>5152</v>
       </c>
@@ -39116,7 +39722,7 @@
         <v>5166</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="366" spans="1:15">
       <c r="A366" t="s">
         <v>5167</v>
       </c>
@@ -39163,7 +39769,7 @@
         <v>5168</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:15">
       <c r="A367" t="s">
         <v>5181</v>
       </c>
@@ -39210,7 +39816,7 @@
         <v>5182</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:15">
       <c r="A368" t="s">
         <v>5195</v>
       </c>
@@ -39257,7 +39863,7 @@
         <v>5196</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:15">
       <c r="A369" t="s">
         <v>5209</v>
       </c>
@@ -39304,7 +39910,7 @@
         <v>5210</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:15">
       <c r="A370" t="s">
         <v>5221</v>
       </c>
@@ -39351,7 +39957,7 @@
         <v>5234</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:15">
       <c r="A371" t="s">
         <v>5235</v>
       </c>
@@ -39398,7 +40004,7 @@
         <v>5249</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="372" spans="1:15">
       <c r="A372" t="s">
         <v>5250</v>
       </c>
@@ -39445,7 +40051,7 @@
         <v>5251</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:15">
       <c r="A373" t="s">
         <v>5264</v>
       </c>
@@ -39492,7 +40098,7 @@
         <v>5278</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:15">
       <c r="A374" t="s">
         <v>5279</v>
       </c>
@@ -39539,7 +40145,7 @@
         <v>5293</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:15">
       <c r="A375" t="s">
         <v>5294</v>
       </c>
@@ -39586,7 +40192,7 @@
         <v>5308</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:15">
       <c r="A376" t="s">
         <v>5309</v>
       </c>
@@ -39633,7 +40239,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:15">
       <c r="A377" t="s">
         <v>5311</v>
       </c>
@@ -39680,7 +40286,7 @@
         <v>5325</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:15">
       <c r="A378" t="s">
         <v>5326</v>
       </c>
@@ -39727,7 +40333,7 @@
         <v>5329</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:15">
       <c r="A379" t="s">
         <v>5338</v>
       </c>
@@ -39774,7 +40380,7 @@
         <v>5352</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:15">
       <c r="A380" t="s">
         <v>5353</v>
       </c>
@@ -39821,7 +40427,7 @@
         <v>5363</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:15">
       <c r="A381" t="s">
         <v>5364</v>
       </c>
@@ -39868,7 +40474,7 @@
         <v>5378</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:15">
       <c r="A382" t="s">
         <v>5379</v>
       </c>
@@ -39915,7 +40521,7 @@
         <v>5380</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:15">
       <c r="A383" t="s">
         <v>5391</v>
       </c>
@@ -39962,7 +40568,7 @@
         <v>5405</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:15">
       <c r="A384" t="s">
         <v>5406</v>
       </c>
@@ -40009,7 +40615,7 @@
         <v>5420</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:15">
       <c r="A385" t="s">
         <v>5421</v>
       </c>
@@ -40056,7 +40662,7 @@
         <v>5422</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:15">
       <c r="A386" t="s">
         <v>5434</v>
       </c>
@@ -40103,7 +40709,7 @@
         <v>5447</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:15">
       <c r="A387" t="s">
         <v>5448</v>
       </c>
@@ -40150,7 +40756,7 @@
         <v>5462</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:15">
       <c r="A388" t="s">
         <v>5463</v>
       </c>
@@ -40197,7 +40803,7 @@
         <v>5477</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:15">
       <c r="A389" t="s">
         <v>5478</v>
       </c>
@@ -40244,7 +40850,7 @@
         <v>5479</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:15">
       <c r="A390" t="s">
         <v>5492</v>
       </c>
@@ -40291,7 +40897,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:15">
       <c r="A391" t="s">
         <v>5502</v>
       </c>
@@ -40338,7 +40944,7 @@
         <v>5516</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="392" spans="1:15">
       <c r="A392" t="s">
         <v>5517</v>
       </c>
@@ -40385,7 +40991,7 @@
         <v>5531</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:15">
       <c r="A393" t="s">
         <v>5532</v>
       </c>
@@ -40432,7 +41038,7 @@
         <v>5533</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:15">
       <c r="A394" t="s">
         <v>5546</v>
       </c>
@@ -40479,7 +41085,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="395" spans="1:15">
       <c r="A395" t="s">
         <v>5561</v>
       </c>
@@ -40526,7 +41132,7 @@
         <v>5575</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="396" spans="1:15">
       <c r="A396" t="s">
         <v>5576</v>
       </c>
@@ -40573,7 +41179,7 @@
         <v>5590</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="397" spans="1:15">
       <c r="A397" t="s">
         <v>5591</v>
       </c>
@@ -40620,7 +41226,7 @@
         <v>5605</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:15">
       <c r="A398" t="s">
         <v>5606</v>
       </c>
@@ -40667,7 +41273,7 @@
         <v>5607</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="399" spans="1:15">
       <c r="A399" t="s">
         <v>5620</v>
       </c>
@@ -40714,7 +41320,7 @@
         <v>5634</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:15">
       <c r="A400" t="s">
         <v>5635</v>
       </c>
@@ -40761,7 +41367,7 @@
         <v>5636</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="401" spans="1:15">
       <c r="A401" t="s">
         <v>5647</v>
       </c>
@@ -40808,7 +41414,7 @@
         <v>5648</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:15">
       <c r="A402" t="s">
         <v>5660</v>
       </c>
@@ -40855,7 +41461,7 @@
         <v>5672</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:15">
       <c r="A403" t="s">
         <v>5673</v>
       </c>
@@ -40902,7 +41508,7 @@
         <v>5687</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:15">
       <c r="A404" t="s">
         <v>5688</v>
       </c>
@@ -40949,7 +41555,7 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:15">
       <c r="A405" t="s">
         <v>5703</v>
       </c>
@@ -40996,7 +41602,7 @@
         <v>5717</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="406" spans="1:15">
       <c r="A406" t="s">
         <v>5718</v>
       </c>
@@ -41043,7 +41649,7 @@
         <v>5719</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:15">
       <c r="A407" t="s">
         <v>5732</v>
       </c>
@@ -41090,7 +41696,7 @@
         <v>5733</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:15">
       <c r="A408" t="s">
         <v>5745</v>
       </c>
@@ -41137,7 +41743,7 @@
         <v>5759</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:15">
       <c r="A409" t="s">
         <v>5760</v>
       </c>
@@ -41184,7 +41790,7 @@
         <v>5774</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="410" spans="1:15">
       <c r="A410" t="s">
         <v>5775</v>
       </c>
@@ -41231,7 +41837,7 @@
         <v>5789</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="411" spans="1:15">
       <c r="A411" t="s">
         <v>5790</v>
       </c>
@@ -41278,7 +41884,7 @@
         <v>5804</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="412" spans="1:15">
       <c r="A412" t="s">
         <v>5805</v>
       </c>
@@ -41325,7 +41931,7 @@
         <v>5818</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:15">
       <c r="A413" t="s">
         <v>5819</v>
       </c>
@@ -41372,7 +41978,7 @@
         <v>5833</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="414" spans="1:15">
       <c r="A414" t="s">
         <v>5834</v>
       </c>
@@ -41419,7 +42025,7 @@
         <v>5847</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:15">
       <c r="A415" t="s">
         <v>5848</v>
       </c>
@@ -41466,7 +42072,7 @@
         <v>5862</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="416" spans="1:15">
       <c r="A416" t="s">
         <v>5863</v>
       </c>
@@ -41513,7 +42119,7 @@
         <v>5864</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:15">
       <c r="A417" t="s">
         <v>5877</v>
       </c>
@@ -41560,7 +42166,7 @@
         <v>5878</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:15">
       <c r="A418" t="s">
         <v>5891</v>
       </c>
@@ -41607,7 +42213,7 @@
         <v>5905</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:15">
       <c r="A419" t="s">
         <v>5906</v>
       </c>
@@ -41654,7 +42260,7 @@
         <v>5920</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="420" spans="1:15">
       <c r="A420" t="s">
         <v>5921</v>
       </c>
@@ -41701,7 +42307,7 @@
         <v>5935</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="421" spans="1:15">
       <c r="A421" t="s">
         <v>5936</v>
       </c>
@@ -41748,7 +42354,7 @@
         <v>5950</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="422" spans="1:15">
       <c r="A422" t="s">
         <v>5951</v>
       </c>
@@ -41795,7 +42401,7 @@
         <v>5965</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="423" spans="1:15">
       <c r="A423" t="s">
         <v>5966</v>
       </c>
@@ -41842,7 +42448,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="424" spans="1:15">
       <c r="A424" t="s">
         <v>5981</v>
       </c>
@@ -41889,7 +42495,7 @@
         <v>5982</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="425" spans="1:15">
       <c r="A425" t="s">
         <v>5995</v>
       </c>
@@ -41936,7 +42542,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="426" spans="1:15">
       <c r="A426" t="s">
         <v>6004</v>
       </c>
@@ -41983,7 +42589,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="427" spans="1:15">
       <c r="A427" t="s">
         <v>6011</v>
       </c>
@@ -42030,7 +42636,7 @@
         <v>6012</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="428" spans="1:15">
       <c r="A428" t="s">
         <v>6025</v>
       </c>
@@ -42077,7 +42683,7 @@
         <v>6039</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:15">
       <c r="A429" t="s">
         <v>6040</v>
       </c>
@@ -42124,7 +42730,7 @@
         <v>6041</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:15">
       <c r="A430" t="s">
         <v>6053</v>
       </c>
@@ -42171,7 +42777,7 @@
         <v>6067</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="431" spans="1:15">
       <c r="A431" t="s">
         <v>6068</v>
       </c>
@@ -42218,7 +42824,7 @@
         <v>6082</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="432" spans="1:15">
       <c r="A432" t="s">
         <v>6083</v>
       </c>
@@ -42265,7 +42871,7 @@
         <v>6097</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="433" spans="1:15">
       <c r="A433" t="s">
         <v>6098</v>
       </c>
@@ -42312,7 +42918,7 @@
         <v>6112</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:15">
       <c r="A434" t="s">
         <v>6113</v>
       </c>
@@ -42359,7 +42965,7 @@
         <v>4025</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="435" spans="1:15">
       <c r="A435" t="s">
         <v>6126</v>
       </c>
@@ -42406,7 +43012,7 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="436" spans="1:15">
       <c r="A436" t="s">
         <v>6132</v>
       </c>
@@ -42453,7 +43059,7 @@
         <v>3963</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="437" spans="1:15">
       <c r="A437" t="s">
         <v>6140</v>
       </c>
@@ -42500,7 +43106,7 @@
         <v>4118</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="438" spans="1:15">
       <c r="A438" t="s">
         <v>6152</v>
       </c>
@@ -42547,7 +43153,7 @@
         <v>6165</v>
       </c>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="439" spans="1:15">
       <c r="A439" t="s">
         <v>6166</v>
       </c>
@@ -42594,7 +43200,7 @@
         <v>4120</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="440" spans="1:15">
       <c r="A440" t="s">
         <v>6179</v>
       </c>
@@ -42641,7 +43247,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="441" spans="1:15">
       <c r="A441" t="s">
         <v>6184</v>
       </c>
@@ -42688,7 +43294,7 @@
         <v>6198</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="442" spans="1:15">
       <c r="A442" t="s">
         <v>6199</v>
       </c>
@@ -42735,7 +43341,7 @@
         <v>6213</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="443" spans="1:15">
       <c r="A443" t="s">
         <v>6214</v>
       </c>
@@ -42782,7 +43388,7 @@
         <v>6228</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="444" spans="1:15">
       <c r="A444" t="s">
         <v>6229</v>
       </c>
@@ -42829,7 +43435,7 @@
         <v>6243</v>
       </c>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="445" spans="1:15">
       <c r="A445" t="s">
         <v>6244</v>
       </c>
@@ -42876,7 +43482,7 @@
         <v>6257</v>
       </c>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="446" spans="1:15">
       <c r="A446" t="s">
         <v>6258</v>
       </c>
@@ -42923,7 +43529,7 @@
         <v>6271</v>
       </c>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="447" spans="1:15">
       <c r="A447" t="s">
         <v>6272</v>
       </c>
@@ -42970,7 +43576,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="448" spans="1:15">
       <c r="A448" t="s">
         <v>6278</v>
       </c>
@@ -43017,7 +43623,7 @@
         <v>6285</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="449" spans="1:15">
       <c r="A449" t="s">
         <v>6286</v>
       </c>
@@ -43064,7 +43670,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="450" spans="1:15">
       <c r="A450" t="s">
         <v>6301</v>
       </c>
@@ -43111,7 +43717,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="451" spans="1:15">
       <c r="A451" t="s">
         <v>6316</v>
       </c>
@@ -43158,7 +43764,7 @@
         <v>6317</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="452" spans="1:15">
       <c r="A452" t="s">
         <v>6330</v>
       </c>
@@ -43205,7 +43811,7 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="453" spans="1:15">
       <c r="A453" t="s">
         <v>6343</v>
       </c>
@@ -43252,7 +43858,7 @@
         <v>6344</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="454" spans="1:15">
       <c r="A454" t="s">
         <v>6355</v>
       </c>
@@ -43299,7 +43905,7 @@
         <v>6358</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="455" spans="1:15">
       <c r="A455" t="s">
         <v>6369</v>
       </c>
@@ -43346,7 +43952,7 @@
         <v>6383</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="456" spans="1:15">
       <c r="A456" t="s">
         <v>6384</v>
       </c>
@@ -43393,7 +43999,7 @@
         <v>6398</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="457" spans="1:15">
       <c r="A457" t="s">
         <v>6399</v>
       </c>
@@ -43440,7 +44046,7 @@
         <v>6413</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="458" spans="1:15">
       <c r="A458" t="s">
         <v>6414</v>
       </c>
@@ -43487,7 +44093,7 @@
         <v>6428</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="459" spans="1:15">
       <c r="A459" t="s">
         <v>6429</v>
       </c>
@@ -43534,7 +44140,7 @@
         <v>6443</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="460" spans="1:15">
       <c r="A460" t="s">
         <v>6444</v>
       </c>
@@ -43581,7 +44187,7 @@
         <v>6458</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="461" spans="1:15">
       <c r="A461" t="s">
         <v>6459</v>
       </c>
@@ -43628,7 +44234,7 @@
         <v>6472</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="462" spans="1:15">
       <c r="A462" t="s">
         <v>6473</v>
       </c>
@@ -43675,7 +44281,7 @@
         <v>6486</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="463" spans="1:15">
       <c r="A463" t="s">
         <v>6487</v>
       </c>
@@ -43722,7 +44328,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="464" spans="1:15">
       <c r="A464" t="s">
         <v>6502</v>
       </c>
@@ -43769,7 +44375,7 @@
         <v>6516</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="465" spans="1:15">
       <c r="A465" t="s">
         <v>6517</v>
       </c>
@@ -43816,7 +44422,7 @@
         <v>6530</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="466" spans="1:15">
       <c r="A466" t="s">
         <v>6531</v>
       </c>
@@ -43863,7 +44469,7 @@
         <v>6545</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="467" spans="1:15">
       <c r="A467" t="s">
         <v>6546</v>
       </c>
@@ -43910,103 +44516,103 @@
         <v>6547</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A468" s="3" t="s">
-        <v>7151</v>
-      </c>
-      <c r="B468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="C468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="D468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="E468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="F468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="G468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="H468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="I468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="J468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="K468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="L468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="M468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="N468" s="3" t="s">
-        <v>7152</v>
-      </c>
-      <c r="O468" s="3" t="s">
-        <v>7152</v>
-      </c>
-    </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="468" spans="1:15">
+      <c r="A468" t="s">
+        <v>6559</v>
+      </c>
+      <c r="B468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="C468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="D468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="E468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="F468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="G468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="H468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="I468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="J468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="K468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="L468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="M468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="N468" t="s">
+        <v>6560</v>
+      </c>
+      <c r="O468" t="s">
+        <v>6560</v>
+      </c>
+    </row>
+    <row r="469" spans="1:15">
       <c r="A469" t="s">
-        <v>6559</v>
+        <v>6561</v>
       </c>
       <c r="B469" t="s">
-        <v>6560</v>
+        <v>6562</v>
       </c>
       <c r="C469" t="s">
-        <v>6561</v>
+        <v>6563</v>
       </c>
       <c r="D469" t="s">
-        <v>6562</v>
+        <v>6564</v>
       </c>
       <c r="E469" t="s">
-        <v>6563</v>
+        <v>6565</v>
       </c>
       <c r="F469" t="s">
-        <v>6564</v>
+        <v>6566</v>
       </c>
       <c r="G469" t="s">
         <v>724</v>
       </c>
       <c r="H469" t="s">
-        <v>6565</v>
+        <v>6567</v>
       </c>
       <c r="I469" t="s">
-        <v>6566</v>
+        <v>6568</v>
       </c>
       <c r="J469" t="s">
-        <v>6567</v>
+        <v>6569</v>
       </c>
       <c r="K469" t="s">
-        <v>6568</v>
+        <v>6570</v>
       </c>
       <c r="L469" t="s">
-        <v>6569</v>
+        <v>6571</v>
       </c>
       <c r="M469" t="s">
-        <v>6570</v>
+        <v>6572</v>
       </c>
       <c r="N469" t="s">
-        <v>6571</v>
+        <v>6573</v>
       </c>
       <c r="O469" t="s">
-        <v>6560</v>
-      </c>
-    </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6562</v>
+      </c>
+    </row>
+    <row r="470" spans="1:15">
       <c r="A470" t="s">
-        <v>6572</v>
+        <v>6574</v>
       </c>
       <c r="B470" t="s">
         <v>2368</v>
@@ -44021,7 +44627,7 @@
         <v>2371</v>
       </c>
       <c r="F470" t="s">
-        <v>6573</v>
+        <v>6575</v>
       </c>
       <c r="G470" t="s">
         <v>2373</v>
@@ -44030,136 +44636,136 @@
         <v>2374</v>
       </c>
       <c r="I470" t="s">
-        <v>6574</v>
+        <v>6576</v>
       </c>
       <c r="J470" t="s">
         <v>2376</v>
       </c>
       <c r="K470" t="s">
-        <v>6575</v>
+        <v>6577</v>
       </c>
       <c r="L470" t="s">
         <v>2378</v>
       </c>
       <c r="M470" t="s">
-        <v>6576</v>
+        <v>6578</v>
       </c>
       <c r="N470" t="s">
         <v>2380</v>
       </c>
       <c r="O470" t="s">
-        <v>6577</v>
-      </c>
-    </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6579</v>
+      </c>
+    </row>
+    <row r="471" spans="1:15">
       <c r="A471" t="s">
-        <v>6578</v>
+        <v>6580</v>
       </c>
       <c r="B471" t="s">
-        <v>6579</v>
+        <v>6581</v>
       </c>
       <c r="C471" t="s">
-        <v>6580</v>
+        <v>6582</v>
       </c>
       <c r="D471" t="s">
-        <v>6581</v>
+        <v>6583</v>
       </c>
       <c r="E471" t="s">
-        <v>6582</v>
+        <v>6584</v>
       </c>
       <c r="F471" t="s">
-        <v>6583</v>
+        <v>6585</v>
       </c>
       <c r="G471" t="s">
-        <v>6584</v>
+        <v>6586</v>
       </c>
       <c r="H471" t="s">
-        <v>6585</v>
+        <v>6587</v>
       </c>
       <c r="I471" t="s">
-        <v>6586</v>
+        <v>6588</v>
       </c>
       <c r="J471" t="s">
-        <v>6587</v>
+        <v>6589</v>
       </c>
       <c r="K471" t="s">
-        <v>6588</v>
+        <v>6590</v>
       </c>
       <c r="L471" t="s">
-        <v>6589</v>
+        <v>6591</v>
       </c>
       <c r="M471" t="s">
-        <v>6590</v>
+        <v>6592</v>
       </c>
       <c r="N471" t="s">
-        <v>6591</v>
+        <v>6593</v>
       </c>
       <c r="O471" t="s">
-        <v>6592</v>
-      </c>
-    </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6594</v>
+      </c>
+    </row>
+    <row r="472" spans="1:15">
       <c r="A472" t="s">
-        <v>6593</v>
+        <v>6595</v>
       </c>
       <c r="B472" t="s">
-        <v>6594</v>
+        <v>6596</v>
       </c>
       <c r="C472" t="s">
-        <v>6595</v>
+        <v>6597</v>
       </c>
       <c r="D472" t="s">
-        <v>6596</v>
+        <v>6598</v>
       </c>
       <c r="E472" t="s">
-        <v>6597</v>
+        <v>6599</v>
       </c>
       <c r="F472" t="s">
-        <v>6598</v>
+        <v>6600</v>
       </c>
       <c r="G472" t="s">
-        <v>6599</v>
+        <v>6601</v>
       </c>
       <c r="H472" t="s">
-        <v>6600</v>
+        <v>6602</v>
       </c>
       <c r="I472" t="s">
-        <v>6601</v>
+        <v>6603</v>
       </c>
       <c r="J472" t="s">
-        <v>6602</v>
+        <v>6604</v>
       </c>
       <c r="K472" t="s">
-        <v>6603</v>
+        <v>6605</v>
       </c>
       <c r="L472" t="s">
-        <v>6604</v>
+        <v>6606</v>
       </c>
       <c r="M472" t="s">
-        <v>6605</v>
+        <v>6607</v>
       </c>
       <c r="N472" t="s">
-        <v>6606</v>
+        <v>6608</v>
       </c>
       <c r="O472" t="s">
-        <v>6607</v>
-      </c>
-    </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6609</v>
+      </c>
+    </row>
+    <row r="473" spans="1:15">
       <c r="A473" t="s">
-        <v>6608</v>
+        <v>6610</v>
       </c>
       <c r="B473" t="s">
         <v>2383</v>
       </c>
       <c r="C473" t="s">
-        <v>6609</v>
+        <v>6611</v>
       </c>
       <c r="D473" t="s">
         <v>2385</v>
       </c>
       <c r="E473" t="s">
-        <v>6610</v>
+        <v>6612</v>
       </c>
       <c r="F473" t="s">
         <v>2387</v>
@@ -44171,2712 +44777,2712 @@
         <v>2389</v>
       </c>
       <c r="I473" t="s">
-        <v>6611</v>
+        <v>6613</v>
       </c>
       <c r="J473" t="s">
-        <v>6612</v>
+        <v>6614</v>
       </c>
       <c r="K473" t="s">
-        <v>6613</v>
+        <v>6615</v>
       </c>
       <c r="L473" t="s">
-        <v>6614</v>
+        <v>6616</v>
       </c>
       <c r="M473" t="s">
-        <v>6615</v>
+        <v>6617</v>
       </c>
       <c r="N473" t="s">
-        <v>6616</v>
+        <v>6618</v>
       </c>
       <c r="O473" t="s">
-        <v>6617</v>
-      </c>
-    </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6619</v>
+      </c>
+    </row>
+    <row r="474" spans="1:15">
       <c r="A474" t="s">
-        <v>6618</v>
+        <v>6620</v>
       </c>
       <c r="B474" t="s">
         <v>2398</v>
       </c>
       <c r="C474" t="s">
-        <v>6619</v>
+        <v>6621</v>
       </c>
       <c r="D474" t="s">
-        <v>6620</v>
+        <v>6622</v>
       </c>
       <c r="E474" t="s">
-        <v>6621</v>
+        <v>6623</v>
       </c>
       <c r="F474" t="s">
-        <v>6622</v>
+        <v>6624</v>
       </c>
       <c r="G474" t="s">
-        <v>6623</v>
+        <v>6625</v>
       </c>
       <c r="H474" t="s">
-        <v>6624</v>
+        <v>6626</v>
       </c>
       <c r="I474" t="s">
-        <v>6625</v>
+        <v>6627</v>
       </c>
       <c r="J474" t="s">
-        <v>6626</v>
+        <v>6628</v>
       </c>
       <c r="K474" t="s">
-        <v>6627</v>
+        <v>6629</v>
       </c>
       <c r="L474" t="s">
-        <v>6628</v>
+        <v>6630</v>
       </c>
       <c r="M474" t="s">
-        <v>6629</v>
+        <v>6631</v>
       </c>
       <c r="N474" t="s">
-        <v>6630</v>
+        <v>6632</v>
       </c>
       <c r="O474" t="s">
-        <v>6631</v>
-      </c>
-    </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6633</v>
+      </c>
+    </row>
+    <row r="475" spans="1:15">
       <c r="A475" t="s">
-        <v>6632</v>
+        <v>6634</v>
       </c>
       <c r="B475" t="s">
-        <v>6633</v>
+        <v>6635</v>
       </c>
       <c r="C475" t="s">
-        <v>6634</v>
+        <v>6636</v>
       </c>
       <c r="D475" t="s">
-        <v>6635</v>
+        <v>6637</v>
       </c>
       <c r="E475" t="s">
-        <v>6636</v>
+        <v>6638</v>
       </c>
       <c r="F475" t="s">
-        <v>6637</v>
+        <v>6639</v>
       </c>
       <c r="G475" t="s">
-        <v>6638</v>
+        <v>6640</v>
       </c>
       <c r="H475" t="s">
-        <v>6639</v>
+        <v>6641</v>
       </c>
       <c r="I475" t="s">
-        <v>6640</v>
+        <v>6642</v>
       </c>
       <c r="J475" t="s">
-        <v>6641</v>
+        <v>6643</v>
       </c>
       <c r="K475" t="s">
-        <v>6642</v>
+        <v>6644</v>
       </c>
       <c r="L475" t="s">
-        <v>6643</v>
+        <v>6645</v>
       </c>
       <c r="M475" t="s">
-        <v>6644</v>
+        <v>6646</v>
       </c>
       <c r="N475" t="s">
-        <v>6645</v>
+        <v>6647</v>
       </c>
       <c r="O475" t="s">
-        <v>6646</v>
-      </c>
-    </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6648</v>
+      </c>
+    </row>
+    <row r="476" spans="1:15">
       <c r="A476" t="s">
-        <v>6647</v>
+        <v>6649</v>
       </c>
       <c r="B476" t="s">
-        <v>6648</v>
+        <v>6650</v>
       </c>
       <c r="C476" t="s">
-        <v>6649</v>
+        <v>6651</v>
       </c>
       <c r="D476" t="s">
-        <v>6650</v>
+        <v>6652</v>
       </c>
       <c r="E476" t="s">
-        <v>6651</v>
+        <v>6653</v>
       </c>
       <c r="F476" t="s">
-        <v>6652</v>
+        <v>6654</v>
       </c>
       <c r="G476" t="s">
-        <v>6653</v>
+        <v>6655</v>
       </c>
       <c r="H476" t="s">
-        <v>6654</v>
+        <v>6656</v>
       </c>
       <c r="I476" t="s">
-        <v>6655</v>
+        <v>6657</v>
       </c>
       <c r="J476" t="s">
-        <v>6656</v>
+        <v>6658</v>
       </c>
       <c r="K476" t="s">
-        <v>6657</v>
+        <v>6659</v>
       </c>
       <c r="L476" t="s">
-        <v>6658</v>
+        <v>6660</v>
       </c>
       <c r="M476" t="s">
-        <v>6659</v>
+        <v>6661</v>
       </c>
       <c r="N476" t="s">
-        <v>6660</v>
+        <v>6662</v>
       </c>
       <c r="O476" t="s">
-        <v>6661</v>
-      </c>
-    </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6663</v>
+      </c>
+    </row>
+    <row r="477" spans="1:15">
       <c r="A477" t="s">
-        <v>6662</v>
+        <v>6664</v>
       </c>
       <c r="B477" t="s">
-        <v>6663</v>
+        <v>6665</v>
       </c>
       <c r="C477" t="s">
-        <v>6664</v>
+        <v>6666</v>
       </c>
       <c r="D477" t="s">
-        <v>6665</v>
+        <v>6667</v>
       </c>
       <c r="E477" t="s">
-        <v>6666</v>
+        <v>6668</v>
       </c>
       <c r="F477" t="s">
-        <v>6667</v>
+        <v>6669</v>
       </c>
       <c r="G477" t="s">
-        <v>6668</v>
+        <v>6670</v>
       </c>
       <c r="H477" t="s">
-        <v>6669</v>
+        <v>6671</v>
       </c>
       <c r="I477" t="s">
-        <v>6670</v>
+        <v>6672</v>
       </c>
       <c r="J477" t="s">
-        <v>6671</v>
+        <v>6673</v>
       </c>
       <c r="K477" t="s">
-        <v>6672</v>
+        <v>6674</v>
       </c>
       <c r="L477" t="s">
-        <v>6673</v>
+        <v>6675</v>
       </c>
       <c r="M477" t="s">
-        <v>6674</v>
+        <v>6676</v>
       </c>
       <c r="N477" t="s">
-        <v>6675</v>
+        <v>6677</v>
       </c>
       <c r="O477" t="s">
-        <v>6676</v>
-      </c>
-    </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6678</v>
+      </c>
+    </row>
+    <row r="478" spans="1:15">
       <c r="A478" t="s">
-        <v>6677</v>
+        <v>6679</v>
       </c>
       <c r="B478" t="s">
-        <v>6678</v>
+        <v>6680</v>
       </c>
       <c r="C478" t="s">
-        <v>6679</v>
+        <v>6681</v>
       </c>
       <c r="D478" t="s">
-        <v>6680</v>
+        <v>6682</v>
       </c>
       <c r="E478" t="s">
-        <v>6681</v>
+        <v>6683</v>
       </c>
       <c r="F478" t="s">
-        <v>6682</v>
+        <v>6684</v>
       </c>
       <c r="G478" t="s">
-        <v>6683</v>
+        <v>6685</v>
       </c>
       <c r="H478" t="s">
-        <v>6684</v>
+        <v>6686</v>
       </c>
       <c r="I478" t="s">
-        <v>6685</v>
+        <v>6687</v>
       </c>
       <c r="J478" t="s">
-        <v>6686</v>
+        <v>6688</v>
       </c>
       <c r="K478" t="s">
-        <v>6687</v>
+        <v>6689</v>
       </c>
       <c r="L478" t="s">
-        <v>6688</v>
+        <v>6690</v>
       </c>
       <c r="M478" t="s">
-        <v>6689</v>
+        <v>6691</v>
       </c>
       <c r="N478" t="s">
-        <v>6690</v>
+        <v>6692</v>
       </c>
       <c r="O478" t="s">
-        <v>6691</v>
-      </c>
-    </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6693</v>
+      </c>
+    </row>
+    <row r="479" spans="1:15">
       <c r="A479" t="s">
-        <v>6692</v>
+        <v>6694</v>
       </c>
       <c r="B479" t="s">
-        <v>6693</v>
+        <v>6695</v>
       </c>
       <c r="C479" t="s">
-        <v>6694</v>
+        <v>6696</v>
       </c>
       <c r="D479" t="s">
-        <v>6695</v>
+        <v>6697</v>
       </c>
       <c r="E479" t="s">
-        <v>6696</v>
+        <v>6698</v>
       </c>
       <c r="F479" t="s">
-        <v>6697</v>
+        <v>6699</v>
       </c>
       <c r="G479" t="s">
-        <v>6698</v>
+        <v>6700</v>
       </c>
       <c r="H479" t="s">
-        <v>6699</v>
+        <v>6701</v>
       </c>
       <c r="I479" t="s">
-        <v>6700</v>
+        <v>6702</v>
       </c>
       <c r="J479" t="s">
-        <v>6701</v>
+        <v>6703</v>
       </c>
       <c r="K479" t="s">
-        <v>6702</v>
+        <v>6704</v>
       </c>
       <c r="L479" t="s">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="M479" t="s">
-        <v>6704</v>
+        <v>6706</v>
       </c>
       <c r="N479" t="s">
-        <v>6705</v>
+        <v>6707</v>
       </c>
       <c r="O479" t="s">
-        <v>6706</v>
-      </c>
-    </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6708</v>
+      </c>
+    </row>
+    <row r="480" spans="1:15">
       <c r="A480" t="s">
-        <v>6707</v>
+        <v>6709</v>
       </c>
       <c r="B480" t="s">
-        <v>6708</v>
+        <v>6710</v>
       </c>
       <c r="C480" t="s">
-        <v>6709</v>
+        <v>6711</v>
       </c>
       <c r="D480" t="s">
-        <v>6710</v>
+        <v>6712</v>
       </c>
       <c r="E480" t="s">
-        <v>6711</v>
+        <v>6713</v>
       </c>
       <c r="F480" t="s">
-        <v>6712</v>
+        <v>6714</v>
       </c>
       <c r="G480" t="s">
-        <v>6713</v>
+        <v>6715</v>
       </c>
       <c r="H480" t="s">
-        <v>6714</v>
+        <v>6716</v>
       </c>
       <c r="I480" t="s">
-        <v>6715</v>
+        <v>6717</v>
       </c>
       <c r="J480" t="s">
-        <v>6716</v>
+        <v>6718</v>
       </c>
       <c r="K480" t="s">
-        <v>6717</v>
+        <v>6719</v>
       </c>
       <c r="L480" t="s">
-        <v>6718</v>
+        <v>6720</v>
       </c>
       <c r="M480" t="s">
-        <v>6719</v>
+        <v>6721</v>
       </c>
       <c r="N480" t="s">
-        <v>6720</v>
+        <v>6722</v>
       </c>
       <c r="O480" t="s">
-        <v>6721</v>
-      </c>
-    </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6723</v>
+      </c>
+    </row>
+    <row r="481" spans="1:15">
       <c r="A481" t="s">
-        <v>6722</v>
+        <v>6724</v>
       </c>
       <c r="B481" t="s">
-        <v>6723</v>
+        <v>6725</v>
       </c>
       <c r="C481" t="s">
-        <v>6724</v>
+        <v>6726</v>
       </c>
       <c r="D481" t="s">
-        <v>6725</v>
+        <v>6727</v>
       </c>
       <c r="E481" t="s">
-        <v>6726</v>
+        <v>6728</v>
       </c>
       <c r="F481" t="s">
-        <v>6727</v>
+        <v>6729</v>
       </c>
       <c r="G481" t="s">
-        <v>6728</v>
+        <v>6730</v>
       </c>
       <c r="H481" t="s">
-        <v>6729</v>
+        <v>6731</v>
       </c>
       <c r="I481" t="s">
-        <v>6730</v>
+        <v>6732</v>
       </c>
       <c r="J481" t="s">
-        <v>6731</v>
+        <v>6733</v>
       </c>
       <c r="K481" t="s">
-        <v>6732</v>
+        <v>6734</v>
       </c>
       <c r="L481" t="s">
-        <v>6733</v>
+        <v>6735</v>
       </c>
       <c r="M481" t="s">
-        <v>6734</v>
+        <v>6736</v>
       </c>
       <c r="N481" t="s">
-        <v>6735</v>
+        <v>6737</v>
       </c>
       <c r="O481" t="s">
-        <v>6736</v>
-      </c>
-    </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6738</v>
+      </c>
+    </row>
+    <row r="482" spans="1:15">
       <c r="A482" t="s">
-        <v>6737</v>
+        <v>6739</v>
       </c>
       <c r="B482" t="s">
-        <v>6738</v>
+        <v>6740</v>
       </c>
       <c r="C482" t="s">
-        <v>6739</v>
+        <v>6741</v>
       </c>
       <c r="D482" t="s">
-        <v>6740</v>
+        <v>6742</v>
       </c>
       <c r="E482" t="s">
-        <v>6741</v>
+        <v>6743</v>
       </c>
       <c r="F482" t="s">
-        <v>6742</v>
+        <v>6744</v>
       </c>
       <c r="G482" t="s">
-        <v>6743</v>
+        <v>6745</v>
       </c>
       <c r="H482" t="s">
-        <v>6744</v>
+        <v>6746</v>
       </c>
       <c r="I482" t="s">
-        <v>6745</v>
+        <v>6747</v>
       </c>
       <c r="J482" t="s">
-        <v>6746</v>
+        <v>6748</v>
       </c>
       <c r="K482" t="s">
-        <v>6747</v>
+        <v>6749</v>
       </c>
       <c r="L482" t="s">
-        <v>6748</v>
+        <v>6750</v>
       </c>
       <c r="M482" t="s">
-        <v>6749</v>
+        <v>6751</v>
       </c>
       <c r="N482" t="s">
-        <v>6750</v>
+        <v>6752</v>
       </c>
       <c r="O482" t="s">
-        <v>6751</v>
-      </c>
-    </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6753</v>
+      </c>
+    </row>
+    <row r="483" spans="1:15">
       <c r="A483" t="s">
-        <v>6752</v>
+        <v>6754</v>
       </c>
       <c r="B483" t="s">
-        <v>6753</v>
+        <v>6755</v>
       </c>
       <c r="C483" t="s">
-        <v>6754</v>
+        <v>6756</v>
       </c>
       <c r="D483" t="s">
-        <v>6755</v>
+        <v>6757</v>
       </c>
       <c r="E483" t="s">
-        <v>6756</v>
+        <v>6758</v>
       </c>
       <c r="F483" t="s">
-        <v>6757</v>
+        <v>6759</v>
       </c>
       <c r="G483" t="s">
-        <v>6758</v>
+        <v>6760</v>
       </c>
       <c r="H483" t="s">
-        <v>6759</v>
+        <v>6761</v>
       </c>
       <c r="I483" t="s">
-        <v>6760</v>
+        <v>6762</v>
       </c>
       <c r="J483" t="s">
-        <v>6761</v>
+        <v>6763</v>
       </c>
       <c r="K483" t="s">
-        <v>6762</v>
+        <v>6764</v>
       </c>
       <c r="L483" t="s">
-        <v>6763</v>
+        <v>6765</v>
       </c>
       <c r="M483" t="s">
-        <v>6764</v>
+        <v>6766</v>
       </c>
       <c r="N483" t="s">
-        <v>6765</v>
+        <v>6767</v>
       </c>
       <c r="O483" t="s">
-        <v>6766</v>
-      </c>
-    </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6768</v>
+      </c>
+    </row>
+    <row r="484" spans="1:15">
       <c r="A484" t="s">
-        <v>6767</v>
+        <v>6769</v>
       </c>
       <c r="B484" t="s">
-        <v>6768</v>
+        <v>6770</v>
       </c>
       <c r="C484" t="s">
-        <v>6769</v>
+        <v>6771</v>
       </c>
       <c r="D484" t="s">
-        <v>6770</v>
+        <v>6772</v>
       </c>
       <c r="E484" t="s">
-        <v>6771</v>
+        <v>6773</v>
       </c>
       <c r="F484" t="s">
-        <v>6772</v>
+        <v>6774</v>
       </c>
       <c r="G484" t="s">
-        <v>6773</v>
+        <v>6775</v>
       </c>
       <c r="H484" t="s">
-        <v>6774</v>
+        <v>6776</v>
       </c>
       <c r="I484" t="s">
-        <v>6775</v>
+        <v>6777</v>
       </c>
       <c r="J484" t="s">
-        <v>6776</v>
+        <v>6778</v>
       </c>
       <c r="K484" t="s">
-        <v>6777</v>
+        <v>6779</v>
       </c>
       <c r="L484" t="s">
-        <v>6778</v>
+        <v>6780</v>
       </c>
       <c r="M484" t="s">
-        <v>6779</v>
+        <v>6781</v>
       </c>
       <c r="N484" t="s">
-        <v>6780</v>
+        <v>6782</v>
       </c>
       <c r="O484" t="s">
-        <v>6781</v>
-      </c>
-    </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6783</v>
+      </c>
+    </row>
+    <row r="485" spans="1:15">
       <c r="A485" t="s">
-        <v>6782</v>
+        <v>6784</v>
       </c>
       <c r="B485" t="s">
-        <v>6783</v>
+        <v>6785</v>
       </c>
       <c r="C485" t="s">
-        <v>6784</v>
+        <v>6786</v>
       </c>
       <c r="D485" t="s">
-        <v>6785</v>
+        <v>6787</v>
       </c>
       <c r="E485" t="s">
-        <v>6786</v>
+        <v>6788</v>
       </c>
       <c r="F485" t="s">
-        <v>6787</v>
+        <v>6789</v>
       </c>
       <c r="G485" t="s">
-        <v>6788</v>
+        <v>6790</v>
       </c>
       <c r="H485" t="s">
-        <v>6789</v>
+        <v>6791</v>
       </c>
       <c r="I485" t="s">
-        <v>6790</v>
+        <v>6792</v>
       </c>
       <c r="J485" t="s">
-        <v>6791</v>
+        <v>6793</v>
       </c>
       <c r="K485" t="s">
-        <v>6792</v>
+        <v>6794</v>
       </c>
       <c r="L485" t="s">
-        <v>6793</v>
+        <v>6795</v>
       </c>
       <c r="M485" t="s">
-        <v>6794</v>
+        <v>6796</v>
       </c>
       <c r="N485" t="s">
-        <v>6795</v>
+        <v>6797</v>
       </c>
       <c r="O485" t="s">
-        <v>6796</v>
-      </c>
-    </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6798</v>
+      </c>
+    </row>
+    <row r="486" spans="1:15">
       <c r="A486" t="s">
-        <v>6797</v>
+        <v>6799</v>
       </c>
       <c r="B486" t="s">
-        <v>6798</v>
+        <v>6800</v>
       </c>
       <c r="C486" t="s">
-        <v>6799</v>
+        <v>6801</v>
       </c>
       <c r="D486" t="s">
-        <v>6800</v>
+        <v>6802</v>
       </c>
       <c r="E486" t="s">
-        <v>6801</v>
+        <v>6803</v>
       </c>
       <c r="F486" t="s">
-        <v>6802</v>
+        <v>6804</v>
       </c>
       <c r="G486" t="s">
-        <v>6803</v>
+        <v>6805</v>
       </c>
       <c r="H486" t="s">
-        <v>6804</v>
+        <v>6806</v>
       </c>
       <c r="I486" t="s">
-        <v>6805</v>
+        <v>6807</v>
       </c>
       <c r="J486" t="s">
-        <v>6806</v>
+        <v>6808</v>
       </c>
       <c r="K486" t="s">
-        <v>6807</v>
+        <v>6809</v>
       </c>
       <c r="L486" t="s">
-        <v>6808</v>
+        <v>6810</v>
       </c>
       <c r="M486" t="s">
-        <v>6809</v>
+        <v>6811</v>
       </c>
       <c r="N486" t="s">
-        <v>6810</v>
+        <v>6812</v>
       </c>
       <c r="O486" t="s">
-        <v>6811</v>
-      </c>
-    </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6813</v>
+      </c>
+    </row>
+    <row r="487" spans="1:15">
       <c r="A487" t="s">
-        <v>6812</v>
+        <v>6814</v>
       </c>
       <c r="B487" t="s">
-        <v>6813</v>
+        <v>6815</v>
       </c>
       <c r="C487" t="s">
-        <v>6814</v>
+        <v>6816</v>
       </c>
       <c r="D487" t="s">
-        <v>6815</v>
+        <v>6817</v>
       </c>
       <c r="E487" t="s">
-        <v>6816</v>
+        <v>6818</v>
       </c>
       <c r="F487" t="s">
-        <v>6817</v>
+        <v>6819</v>
       </c>
       <c r="G487" t="s">
-        <v>6818</v>
+        <v>6820</v>
       </c>
       <c r="H487" t="s">
-        <v>6819</v>
+        <v>6821</v>
       </c>
       <c r="I487" t="s">
-        <v>6820</v>
+        <v>6822</v>
       </c>
       <c r="J487" t="s">
-        <v>6821</v>
+        <v>6823</v>
       </c>
       <c r="K487" t="s">
-        <v>6822</v>
+        <v>6824</v>
       </c>
       <c r="L487" t="s">
-        <v>6823</v>
+        <v>6825</v>
       </c>
       <c r="M487" t="s">
-        <v>6824</v>
+        <v>6826</v>
       </c>
       <c r="N487" t="s">
-        <v>6825</v>
+        <v>6827</v>
       </c>
       <c r="O487" t="s">
-        <v>6826</v>
-      </c>
-    </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6828</v>
+      </c>
+    </row>
+    <row r="488" spans="1:15">
       <c r="A488" t="s">
-        <v>6827</v>
+        <v>6829</v>
       </c>
       <c r="B488" t="s">
-        <v>6828</v>
+        <v>6830</v>
       </c>
       <c r="C488" t="s">
-        <v>6829</v>
+        <v>6831</v>
       </c>
       <c r="D488" t="s">
-        <v>6830</v>
+        <v>6832</v>
       </c>
       <c r="E488" t="s">
-        <v>6831</v>
+        <v>6833</v>
       </c>
       <c r="F488" t="s">
-        <v>6832</v>
+        <v>6834</v>
       </c>
       <c r="G488" t="s">
-        <v>6833</v>
+        <v>6835</v>
       </c>
       <c r="H488" t="s">
-        <v>6834</v>
+        <v>6836</v>
       </c>
       <c r="I488" t="s">
-        <v>6835</v>
+        <v>6837</v>
       </c>
       <c r="J488" t="s">
-        <v>6836</v>
+        <v>6838</v>
       </c>
       <c r="K488" t="s">
-        <v>6837</v>
+        <v>6839</v>
       </c>
       <c r="L488" t="s">
-        <v>6838</v>
+        <v>6840</v>
       </c>
       <c r="M488" t="s">
-        <v>6839</v>
+        <v>6841</v>
       </c>
       <c r="N488" t="s">
-        <v>6840</v>
+        <v>6842</v>
       </c>
       <c r="O488" t="s">
-        <v>6841</v>
-      </c>
-    </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6843</v>
+      </c>
+    </row>
+    <row r="489" spans="1:15">
       <c r="A489" t="s">
-        <v>6842</v>
+        <v>6844</v>
       </c>
       <c r="B489" t="s">
-        <v>6843</v>
+        <v>6845</v>
       </c>
       <c r="C489" t="s">
-        <v>6844</v>
+        <v>6846</v>
       </c>
       <c r="D489" t="s">
-        <v>6845</v>
+        <v>6847</v>
       </c>
       <c r="E489" t="s">
-        <v>6846</v>
+        <v>6848</v>
       </c>
       <c r="F489" t="s">
-        <v>6847</v>
+        <v>6849</v>
       </c>
       <c r="G489" t="s">
-        <v>6848</v>
+        <v>6850</v>
       </c>
       <c r="H489" t="s">
-        <v>6849</v>
+        <v>6851</v>
       </c>
       <c r="I489" t="s">
-        <v>6850</v>
+        <v>6852</v>
       </c>
       <c r="J489" t="s">
-        <v>6851</v>
+        <v>6853</v>
       </c>
       <c r="K489" t="s">
-        <v>6852</v>
+        <v>6854</v>
       </c>
       <c r="L489" t="s">
-        <v>6853</v>
+        <v>6855</v>
       </c>
       <c r="M489" t="s">
-        <v>6854</v>
+        <v>6856</v>
       </c>
       <c r="N489" t="s">
-        <v>6855</v>
+        <v>6857</v>
       </c>
       <c r="O489" t="s">
-        <v>6856</v>
-      </c>
-    </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6858</v>
+      </c>
+    </row>
+    <row r="490" spans="1:15">
       <c r="A490" t="s">
-        <v>6857</v>
+        <v>6859</v>
       </c>
       <c r="B490" t="s">
-        <v>6858</v>
+        <v>6860</v>
       </c>
       <c r="C490" t="s">
-        <v>6859</v>
+        <v>6861</v>
       </c>
       <c r="D490" t="s">
-        <v>6860</v>
+        <v>6862</v>
       </c>
       <c r="E490" t="s">
-        <v>6861</v>
+        <v>6863</v>
       </c>
       <c r="F490" t="s">
-        <v>6862</v>
+        <v>6864</v>
       </c>
       <c r="G490" t="s">
-        <v>6863</v>
+        <v>6865</v>
       </c>
       <c r="H490" t="s">
-        <v>6864</v>
+        <v>6866</v>
       </c>
       <c r="I490" t="s">
-        <v>6865</v>
+        <v>6867</v>
       </c>
       <c r="J490" t="s">
-        <v>6866</v>
+        <v>6868</v>
       </c>
       <c r="K490" t="s">
-        <v>6867</v>
+        <v>6869</v>
       </c>
       <c r="L490" t="s">
-        <v>6868</v>
+        <v>6870</v>
       </c>
       <c r="M490" t="s">
-        <v>6869</v>
+        <v>6871</v>
       </c>
       <c r="N490" t="s">
-        <v>6870</v>
+        <v>6872</v>
       </c>
       <c r="O490" t="s">
-        <v>6871</v>
-      </c>
-    </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6873</v>
+      </c>
+    </row>
+    <row r="491" spans="1:15">
       <c r="A491" t="s">
-        <v>6872</v>
+        <v>6874</v>
       </c>
       <c r="B491" t="s">
-        <v>6873</v>
+        <v>6875</v>
       </c>
       <c r="C491" t="s">
-        <v>6874</v>
+        <v>6876</v>
       </c>
       <c r="D491" t="s">
-        <v>6875</v>
+        <v>6877</v>
       </c>
       <c r="E491" t="s">
-        <v>6876</v>
+        <v>6878</v>
       </c>
       <c r="F491" t="s">
-        <v>6877</v>
+        <v>6879</v>
       </c>
       <c r="G491" t="s">
-        <v>6878</v>
+        <v>6880</v>
       </c>
       <c r="H491" t="s">
-        <v>6879</v>
+        <v>6881</v>
       </c>
       <c r="I491" t="s">
-        <v>6880</v>
+        <v>6882</v>
       </c>
       <c r="J491" t="s">
-        <v>6881</v>
+        <v>6883</v>
       </c>
       <c r="K491" t="s">
-        <v>6882</v>
+        <v>6884</v>
       </c>
       <c r="L491" t="s">
-        <v>6883</v>
+        <v>6885</v>
       </c>
       <c r="M491" t="s">
-        <v>6884</v>
+        <v>6886</v>
       </c>
       <c r="N491" t="s">
-        <v>6885</v>
+        <v>6887</v>
       </c>
       <c r="O491" t="s">
-        <v>6886</v>
-      </c>
-    </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6888</v>
+      </c>
+    </row>
+    <row r="492" spans="1:15">
       <c r="A492" t="s">
-        <v>6887</v>
+        <v>6889</v>
       </c>
       <c r="B492" t="s">
-        <v>6888</v>
+        <v>6890</v>
       </c>
       <c r="C492" t="s">
-        <v>6889</v>
+        <v>6891</v>
       </c>
       <c r="D492" t="s">
-        <v>6890</v>
+        <v>6892</v>
       </c>
       <c r="E492" t="s">
-        <v>6891</v>
+        <v>6893</v>
       </c>
       <c r="F492" t="s">
-        <v>6892</v>
+        <v>6894</v>
       </c>
       <c r="G492" t="s">
-        <v>6893</v>
+        <v>6895</v>
       </c>
       <c r="H492" t="s">
-        <v>6894</v>
+        <v>6896</v>
       </c>
       <c r="I492" t="s">
-        <v>6895</v>
+        <v>6897</v>
       </c>
       <c r="J492" t="s">
-        <v>6896</v>
+        <v>6898</v>
       </c>
       <c r="K492" t="s">
-        <v>6897</v>
+        <v>6899</v>
       </c>
       <c r="L492" t="s">
-        <v>6898</v>
+        <v>6900</v>
       </c>
       <c r="M492" t="s">
-        <v>6899</v>
+        <v>6901</v>
       </c>
       <c r="N492" t="s">
-        <v>6900</v>
+        <v>6902</v>
       </c>
       <c r="O492" t="s">
-        <v>6901</v>
-      </c>
-    </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6903</v>
+      </c>
+    </row>
+    <row r="493" spans="1:15">
       <c r="A493" t="s">
-        <v>6902</v>
+        <v>6904</v>
       </c>
       <c r="B493" t="s">
-        <v>6903</v>
+        <v>6905</v>
       </c>
       <c r="C493" t="s">
-        <v>6904</v>
+        <v>6906</v>
       </c>
       <c r="D493" t="s">
-        <v>6905</v>
+        <v>6907</v>
       </c>
       <c r="E493" t="s">
-        <v>6906</v>
+        <v>6908</v>
       </c>
       <c r="F493" t="s">
-        <v>6907</v>
+        <v>6909</v>
       </c>
       <c r="G493" t="s">
-        <v>6908</v>
+        <v>6910</v>
       </c>
       <c r="H493" t="s">
-        <v>6909</v>
+        <v>6911</v>
       </c>
       <c r="I493" t="s">
-        <v>6910</v>
+        <v>6912</v>
       </c>
       <c r="J493" t="s">
-        <v>6911</v>
+        <v>6913</v>
       </c>
       <c r="K493" t="s">
-        <v>6912</v>
+        <v>6914</v>
       </c>
       <c r="L493" t="s">
-        <v>6913</v>
+        <v>6915</v>
       </c>
       <c r="M493" t="s">
-        <v>6914</v>
+        <v>6916</v>
       </c>
       <c r="N493" t="s">
-        <v>6915</v>
+        <v>6917</v>
       </c>
       <c r="O493" t="s">
-        <v>6916</v>
-      </c>
-    </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6918</v>
+      </c>
+    </row>
+    <row r="494" spans="1:15">
       <c r="A494" t="s">
-        <v>6917</v>
+        <v>6919</v>
       </c>
       <c r="B494" t="s">
-        <v>6918</v>
+        <v>6920</v>
       </c>
       <c r="C494" t="s">
-        <v>6919</v>
+        <v>6921</v>
       </c>
       <c r="D494" t="s">
-        <v>6920</v>
+        <v>6922</v>
       </c>
       <c r="E494" t="s">
-        <v>6921</v>
+        <v>6923</v>
       </c>
       <c r="F494" t="s">
-        <v>6922</v>
+        <v>6924</v>
       </c>
       <c r="G494" t="s">
-        <v>6923</v>
+        <v>6925</v>
       </c>
       <c r="H494" t="s">
-        <v>6924</v>
+        <v>6926</v>
       </c>
       <c r="I494" t="s">
-        <v>6925</v>
+        <v>6927</v>
       </c>
       <c r="J494" t="s">
-        <v>6926</v>
+        <v>6928</v>
       </c>
       <c r="K494" t="s">
-        <v>6927</v>
+        <v>6929</v>
       </c>
       <c r="L494" t="s">
-        <v>6928</v>
+        <v>6930</v>
       </c>
       <c r="M494" t="s">
-        <v>6929</v>
+        <v>6931</v>
       </c>
       <c r="N494" t="s">
-        <v>6930</v>
+        <v>6932</v>
       </c>
       <c r="O494" t="s">
-        <v>6931</v>
-      </c>
-    </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6933</v>
+      </c>
+    </row>
+    <row r="495" spans="1:15">
       <c r="A495" t="s">
-        <v>6932</v>
+        <v>6934</v>
       </c>
       <c r="B495" t="s">
-        <v>6933</v>
+        <v>6935</v>
       </c>
       <c r="C495" t="s">
-        <v>6934</v>
+        <v>6936</v>
       </c>
       <c r="D495" t="s">
-        <v>6935</v>
+        <v>6937</v>
       </c>
       <c r="E495" t="s">
-        <v>6936</v>
+        <v>6938</v>
       </c>
       <c r="F495" t="s">
-        <v>6937</v>
+        <v>6939</v>
       </c>
       <c r="G495" t="s">
-        <v>6938</v>
+        <v>6940</v>
       </c>
       <c r="H495" t="s">
-        <v>6939</v>
+        <v>6941</v>
       </c>
       <c r="I495" t="s">
-        <v>6940</v>
+        <v>6942</v>
       </c>
       <c r="J495" t="s">
-        <v>6941</v>
+        <v>6943</v>
       </c>
       <c r="K495" t="s">
-        <v>6942</v>
+        <v>6944</v>
       </c>
       <c r="L495" t="s">
-        <v>6943</v>
+        <v>6945</v>
       </c>
       <c r="M495" t="s">
-        <v>6944</v>
+        <v>6946</v>
       </c>
       <c r="N495" t="s">
-        <v>6945</v>
+        <v>6947</v>
       </c>
       <c r="O495" t="s">
-        <v>6946</v>
-      </c>
-    </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6948</v>
+      </c>
+    </row>
+    <row r="496" spans="1:15">
       <c r="A496" t="s">
-        <v>6947</v>
+        <v>6949</v>
       </c>
       <c r="B496" t="s">
-        <v>6948</v>
+        <v>6950</v>
       </c>
       <c r="C496" t="s">
-        <v>6949</v>
+        <v>6951</v>
       </c>
       <c r="D496" t="s">
-        <v>6950</v>
+        <v>6952</v>
       </c>
       <c r="E496" t="s">
-        <v>6951</v>
+        <v>6953</v>
       </c>
       <c r="F496" t="s">
-        <v>6952</v>
+        <v>6954</v>
       </c>
       <c r="G496" t="s">
-        <v>6953</v>
+        <v>6955</v>
       </c>
       <c r="H496" t="s">
-        <v>6954</v>
+        <v>6956</v>
       </c>
       <c r="I496" t="s">
-        <v>6955</v>
+        <v>6957</v>
       </c>
       <c r="J496" t="s">
-        <v>6956</v>
+        <v>6958</v>
       </c>
       <c r="K496" t="s">
-        <v>6957</v>
+        <v>6959</v>
       </c>
       <c r="L496" t="s">
-        <v>6958</v>
+        <v>6960</v>
       </c>
       <c r="M496" t="s">
-        <v>6959</v>
+        <v>6961</v>
       </c>
       <c r="N496" t="s">
-        <v>6960</v>
+        <v>6962</v>
       </c>
       <c r="O496" t="s">
-        <v>6961</v>
-      </c>
-    </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6963</v>
+      </c>
+    </row>
+    <row r="497" spans="1:15">
       <c r="A497" t="s">
-        <v>6962</v>
+        <v>6964</v>
       </c>
       <c r="B497" t="s">
-        <v>6963</v>
+        <v>6965</v>
       </c>
       <c r="C497" t="s">
-        <v>6964</v>
+        <v>6966</v>
       </c>
       <c r="D497" t="s">
+        <v>6967</v>
+      </c>
+      <c r="E497" t="s">
+        <v>6968</v>
+      </c>
+      <c r="F497" t="s">
+        <v>6969</v>
+      </c>
+      <c r="G497" t="s">
+        <v>6970</v>
+      </c>
+      <c r="H497" t="s">
+        <v>6971</v>
+      </c>
+      <c r="I497" t="s">
+        <v>6972</v>
+      </c>
+      <c r="J497" t="s">
+        <v>6973</v>
+      </c>
+      <c r="K497" t="s">
+        <v>6974</v>
+      </c>
+      <c r="L497" t="s">
+        <v>6975</v>
+      </c>
+      <c r="M497" t="s">
+        <v>6976</v>
+      </c>
+      <c r="N497" t="s">
+        <v>6977</v>
+      </c>
+      <c r="O497" t="s">
         <v>6965</v>
       </c>
-      <c r="E497" t="s">
-        <v>6966</v>
-      </c>
-      <c r="F497" t="s">
-        <v>6967</v>
-      </c>
-      <c r="G497" t="s">
-        <v>6968</v>
-      </c>
-      <c r="H497" t="s">
-        <v>6969</v>
-      </c>
-      <c r="I497" t="s">
-        <v>6970</v>
-      </c>
-      <c r="J497" t="s">
-        <v>6971</v>
-      </c>
-      <c r="K497" t="s">
-        <v>6972</v>
-      </c>
-      <c r="L497" t="s">
-        <v>6973</v>
-      </c>
-      <c r="M497" t="s">
-        <v>6974</v>
-      </c>
-      <c r="N497" t="s">
-        <v>6975</v>
-      </c>
-      <c r="O497" t="s">
-        <v>6963</v>
-      </c>
-    </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.15">
+    </row>
+    <row r="498" spans="1:15">
       <c r="A498" t="s">
-        <v>6976</v>
+        <v>6978</v>
       </c>
       <c r="B498" t="s">
-        <v>6977</v>
+        <v>6979</v>
       </c>
       <c r="C498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="D498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="E498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="F498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="G498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="H498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="I498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="J498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="K498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="L498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="M498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="N498" t="s">
-        <v>6978</v>
+        <v>6980</v>
       </c>
       <c r="O498" t="s">
-        <v>6978</v>
-      </c>
-    </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6980</v>
+      </c>
+    </row>
+    <row r="499" spans="1:15">
       <c r="A499" t="s">
-        <v>6979</v>
+        <v>6981</v>
       </c>
       <c r="B499" t="s">
-        <v>6980</v>
+        <v>6982</v>
       </c>
       <c r="C499" t="s">
-        <v>6981</v>
+        <v>6983</v>
       </c>
       <c r="D499" t="s">
-        <v>6982</v>
+        <v>6984</v>
       </c>
       <c r="E499" t="s">
-        <v>6983</v>
+        <v>6985</v>
       </c>
       <c r="F499" t="s">
-        <v>6984</v>
+        <v>6986</v>
       </c>
       <c r="G499" t="s">
-        <v>6985</v>
+        <v>6987</v>
       </c>
       <c r="H499" t="s">
-        <v>6986</v>
+        <v>6988</v>
       </c>
       <c r="I499" t="s">
-        <v>6987</v>
+        <v>6989</v>
       </c>
       <c r="J499" t="s">
-        <v>6988</v>
+        <v>6990</v>
       </c>
       <c r="K499" t="s">
-        <v>6989</v>
+        <v>6991</v>
       </c>
       <c r="L499" t="s">
-        <v>6990</v>
+        <v>6992</v>
       </c>
       <c r="M499" t="s">
-        <v>6991</v>
+        <v>6993</v>
       </c>
       <c r="N499" t="s">
-        <v>6992</v>
+        <v>6994</v>
       </c>
       <c r="O499" t="s">
-        <v>6993</v>
-      </c>
-    </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.15">
+        <v>6995</v>
+      </c>
+    </row>
+    <row r="500" spans="1:15">
       <c r="A500" t="s">
-        <v>6994</v>
+        <v>6996</v>
       </c>
       <c r="B500" t="s">
-        <v>6995</v>
+        <v>6997</v>
       </c>
       <c r="C500" t="s">
-        <v>6996</v>
+        <v>6998</v>
       </c>
       <c r="D500" t="s">
-        <v>6997</v>
+        <v>6999</v>
       </c>
       <c r="E500" t="s">
-        <v>6998</v>
+        <v>7000</v>
       </c>
       <c r="F500" t="s">
-        <v>6999</v>
+        <v>7001</v>
       </c>
       <c r="G500" t="s">
-        <v>7000</v>
+        <v>7002</v>
       </c>
       <c r="H500" t="s">
-        <v>7001</v>
+        <v>7003</v>
       </c>
       <c r="I500" t="s">
-        <v>7002</v>
+        <v>7004</v>
       </c>
       <c r="J500" t="s">
-        <v>7003</v>
+        <v>7005</v>
       </c>
       <c r="K500" t="s">
-        <v>7004</v>
+        <v>7006</v>
       </c>
       <c r="L500" t="s">
-        <v>7005</v>
+        <v>7007</v>
       </c>
       <c r="M500" t="s">
-        <v>7006</v>
+        <v>7008</v>
       </c>
       <c r="N500" t="s">
-        <v>7007</v>
+        <v>7009</v>
       </c>
       <c r="O500" t="s">
-        <v>7008</v>
-      </c>
-    </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7010</v>
+      </c>
+    </row>
+    <row r="501" spans="1:15">
       <c r="A501" t="s">
-        <v>7009</v>
+        <v>7011</v>
       </c>
       <c r="B501" t="s">
-        <v>7010</v>
+        <v>7012</v>
       </c>
       <c r="C501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="D501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="E501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="F501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="G501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="H501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="I501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="J501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="K501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="L501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="M501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="N501" t="s">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="O501" t="s">
-        <v>7011</v>
-      </c>
-    </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7013</v>
+      </c>
+    </row>
+    <row r="502" spans="1:15">
       <c r="A502" t="s">
-        <v>7012</v>
+        <v>7014</v>
       </c>
       <c r="B502" t="s">
-        <v>7013</v>
+        <v>7015</v>
       </c>
       <c r="C502" t="s">
-        <v>7014</v>
+        <v>7016</v>
       </c>
       <c r="D502" t="s">
+        <v>7017</v>
+      </c>
+      <c r="E502" t="s">
+        <v>7018</v>
+      </c>
+      <c r="F502" t="s">
+        <v>7019</v>
+      </c>
+      <c r="G502" t="s">
+        <v>7020</v>
+      </c>
+      <c r="H502" t="s">
+        <v>7021</v>
+      </c>
+      <c r="I502" t="s">
+        <v>7022</v>
+      </c>
+      <c r="J502" t="s">
+        <v>7023</v>
+      </c>
+      <c r="K502" t="s">
+        <v>7024</v>
+      </c>
+      <c r="L502" t="s">
+        <v>7025</v>
+      </c>
+      <c r="M502" t="s">
+        <v>7026</v>
+      </c>
+      <c r="N502" t="s">
+        <v>7027</v>
+      </c>
+      <c r="O502" t="s">
         <v>7015</v>
       </c>
-      <c r="E502" t="s">
-        <v>7016</v>
-      </c>
-      <c r="F502" t="s">
-        <v>7017</v>
-      </c>
-      <c r="G502" t="s">
-        <v>7018</v>
-      </c>
-      <c r="H502" t="s">
-        <v>7019</v>
-      </c>
-      <c r="I502" t="s">
-        <v>7020</v>
-      </c>
-      <c r="J502" t="s">
-        <v>7021</v>
-      </c>
-      <c r="K502" t="s">
-        <v>7022</v>
-      </c>
-      <c r="L502" t="s">
-        <v>7023</v>
-      </c>
-      <c r="M502" t="s">
-        <v>7024</v>
-      </c>
-      <c r="N502" t="s">
-        <v>7025</v>
-      </c>
-      <c r="O502" t="s">
-        <v>7013</v>
-      </c>
-    </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.15">
+    </row>
+    <row r="503" spans="1:15">
       <c r="A503" t="s">
-        <v>7026</v>
+        <v>7028</v>
       </c>
       <c r="B503" t="s">
-        <v>7027</v>
+        <v>7029</v>
       </c>
       <c r="C503" t="s">
-        <v>7028</v>
+        <v>7030</v>
       </c>
       <c r="D503" t="s">
-        <v>7029</v>
+        <v>7031</v>
       </c>
       <c r="E503" t="s">
-        <v>7030</v>
+        <v>7032</v>
       </c>
       <c r="F503" t="s">
-        <v>7031</v>
+        <v>7033</v>
       </c>
       <c r="G503" t="s">
-        <v>7032</v>
+        <v>7034</v>
       </c>
       <c r="H503" t="s">
-        <v>7033</v>
+        <v>7035</v>
       </c>
       <c r="I503" t="s">
-        <v>7034</v>
+        <v>7036</v>
       </c>
       <c r="J503" t="s">
-        <v>7035</v>
+        <v>7037</v>
       </c>
       <c r="K503" t="s">
-        <v>7036</v>
+        <v>7038</v>
       </c>
       <c r="L503" t="s">
-        <v>7037</v>
+        <v>7039</v>
       </c>
       <c r="M503" t="s">
-        <v>7038</v>
+        <v>7040</v>
       </c>
       <c r="N503" t="s">
-        <v>7039</v>
+        <v>7041</v>
       </c>
       <c r="O503" t="s">
-        <v>7040</v>
-      </c>
-    </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7042</v>
+      </c>
+    </row>
+    <row r="504" spans="1:15">
       <c r="A504" t="s">
-        <v>7041</v>
+        <v>7043</v>
       </c>
       <c r="B504" t="s">
-        <v>7042</v>
+        <v>7044</v>
       </c>
       <c r="C504" t="s">
-        <v>7043</v>
+        <v>7045</v>
       </c>
       <c r="D504" t="s">
-        <v>7044</v>
+        <v>7046</v>
       </c>
       <c r="E504" t="s">
-        <v>7045</v>
+        <v>7047</v>
       </c>
       <c r="F504" t="s">
-        <v>7046</v>
+        <v>7048</v>
       </c>
       <c r="G504" t="s">
-        <v>7047</v>
+        <v>7049</v>
       </c>
       <c r="H504" t="s">
-        <v>7048</v>
+        <v>7050</v>
       </c>
       <c r="I504" t="s">
-        <v>7049</v>
+        <v>7051</v>
       </c>
       <c r="J504" t="s">
-        <v>7050</v>
+        <v>7052</v>
       </c>
       <c r="K504" t="s">
-        <v>7051</v>
+        <v>7053</v>
       </c>
       <c r="L504" t="s">
-        <v>7052</v>
+        <v>7054</v>
       </c>
       <c r="M504" t="s">
-        <v>7053</v>
+        <v>7055</v>
       </c>
       <c r="N504" t="s">
-        <v>7054</v>
+        <v>7056</v>
       </c>
       <c r="O504" t="s">
-        <v>7055</v>
-      </c>
-    </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7057</v>
+      </c>
+    </row>
+    <row r="505" spans="1:15">
       <c r="A505" t="s">
-        <v>7056</v>
+        <v>7058</v>
       </c>
       <c r="B505" t="s">
-        <v>7057</v>
+        <v>7059</v>
       </c>
       <c r="C505" t="s">
-        <v>7058</v>
+        <v>7060</v>
       </c>
       <c r="D505" t="s">
-        <v>7059</v>
+        <v>7061</v>
       </c>
       <c r="E505" t="s">
-        <v>7060</v>
+        <v>7062</v>
       </c>
       <c r="F505" t="s">
-        <v>7061</v>
+        <v>7063</v>
       </c>
       <c r="G505" t="s">
-        <v>7062</v>
+        <v>7064</v>
       </c>
       <c r="H505" t="s">
-        <v>7063</v>
+        <v>7065</v>
       </c>
       <c r="I505" t="s">
-        <v>7064</v>
+        <v>7066</v>
       </c>
       <c r="J505" t="s">
-        <v>7065</v>
+        <v>7067</v>
       </c>
       <c r="K505" t="s">
-        <v>7066</v>
+        <v>7068</v>
       </c>
       <c r="L505" t="s">
-        <v>7067</v>
+        <v>7069</v>
       </c>
       <c r="M505" t="s">
-        <v>7068</v>
+        <v>7070</v>
       </c>
       <c r="N505" t="s">
-        <v>7069</v>
+        <v>7071</v>
       </c>
       <c r="O505" t="s">
-        <v>7070</v>
-      </c>
-    </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7072</v>
+      </c>
+    </row>
+    <row r="506" spans="1:15">
       <c r="A506" t="s">
-        <v>7071</v>
+        <v>7073</v>
       </c>
       <c r="B506" t="s">
-        <v>7072</v>
+        <v>7074</v>
       </c>
       <c r="C506" t="s">
-        <v>7073</v>
+        <v>7075</v>
       </c>
       <c r="D506" t="s">
-        <v>7074</v>
+        <v>7076</v>
       </c>
       <c r="E506" t="s">
-        <v>7075</v>
+        <v>7077</v>
       </c>
       <c r="F506" t="s">
-        <v>7076</v>
+        <v>7078</v>
       </c>
       <c r="G506" t="s">
-        <v>7077</v>
+        <v>7079</v>
       </c>
       <c r="H506" t="s">
-        <v>7078</v>
+        <v>7080</v>
       </c>
       <c r="I506" t="s">
-        <v>7079</v>
+        <v>7081</v>
       </c>
       <c r="J506" t="s">
-        <v>7080</v>
+        <v>7082</v>
       </c>
       <c r="K506" t="s">
-        <v>7081</v>
+        <v>7083</v>
       </c>
       <c r="L506" t="s">
-        <v>7082</v>
+        <v>7084</v>
       </c>
       <c r="M506" t="s">
-        <v>7083</v>
+        <v>7085</v>
       </c>
       <c r="N506" t="s">
-        <v>7084</v>
+        <v>7086</v>
       </c>
       <c r="O506" t="s">
-        <v>7085</v>
-      </c>
-    </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7087</v>
+      </c>
+    </row>
+    <row r="507" spans="1:15">
       <c r="A507" t="s">
-        <v>7086</v>
+        <v>7088</v>
       </c>
       <c r="B507" t="s">
-        <v>7087</v>
+        <v>7089</v>
       </c>
       <c r="C507" t="s">
-        <v>7088</v>
+        <v>7090</v>
       </c>
       <c r="D507" t="s">
-        <v>7089</v>
+        <v>7091</v>
       </c>
       <c r="E507" t="s">
-        <v>7090</v>
+        <v>7092</v>
       </c>
       <c r="F507" t="s">
-        <v>7091</v>
+        <v>7093</v>
       </c>
       <c r="G507" t="s">
-        <v>7092</v>
+        <v>7094</v>
       </c>
       <c r="H507" t="s">
-        <v>7093</v>
+        <v>7095</v>
       </c>
       <c r="I507" t="s">
-        <v>7094</v>
+        <v>7096</v>
       </c>
       <c r="J507" t="s">
-        <v>7095</v>
+        <v>7097</v>
       </c>
       <c r="K507" t="s">
-        <v>7096</v>
+        <v>7098</v>
       </c>
       <c r="L507" t="s">
-        <v>7097</v>
+        <v>7099</v>
       </c>
       <c r="M507" t="s">
-        <v>7098</v>
+        <v>7100</v>
       </c>
       <c r="N507" t="s">
-        <v>7099</v>
+        <v>7101</v>
       </c>
       <c r="O507" t="s">
-        <v>7100</v>
-      </c>
-    </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7102</v>
+      </c>
+    </row>
+    <row r="508" spans="1:15">
       <c r="A508" t="s">
-        <v>7101</v>
+        <v>7103</v>
       </c>
       <c r="B508" t="s">
-        <v>7102</v>
+        <v>7104</v>
       </c>
       <c r="C508" t="s">
-        <v>7103</v>
+        <v>7105</v>
       </c>
       <c r="D508" t="s">
+        <v>7106</v>
+      </c>
+      <c r="E508" t="s">
+        <v>7107</v>
+      </c>
+      <c r="F508" t="s">
+        <v>7108</v>
+      </c>
+      <c r="G508" t="s">
+        <v>7109</v>
+      </c>
+      <c r="H508" t="s">
+        <v>7110</v>
+      </c>
+      <c r="I508" t="s">
+        <v>7111</v>
+      </c>
+      <c r="J508" t="s">
+        <v>7112</v>
+      </c>
+      <c r="K508" t="s">
+        <v>7113</v>
+      </c>
+      <c r="L508" t="s">
+        <v>7114</v>
+      </c>
+      <c r="M508" t="s">
+        <v>7115</v>
+      </c>
+      <c r="N508" t="s">
+        <v>7116</v>
+      </c>
+      <c r="O508" t="s">
         <v>7104</v>
       </c>
-      <c r="E508" t="s">
-        <v>7105</v>
-      </c>
-      <c r="F508" t="s">
-        <v>7106</v>
-      </c>
-      <c r="G508" t="s">
-        <v>7107</v>
-      </c>
-      <c r="H508" t="s">
-        <v>7108</v>
-      </c>
-      <c r="I508" t="s">
-        <v>7109</v>
-      </c>
-      <c r="J508" t="s">
-        <v>7110</v>
-      </c>
-      <c r="K508" t="s">
-        <v>7111</v>
-      </c>
-      <c r="L508" t="s">
-        <v>7112</v>
-      </c>
-      <c r="M508" t="s">
-        <v>7113</v>
-      </c>
-      <c r="N508" t="s">
-        <v>7114</v>
-      </c>
-      <c r="O508" t="s">
-        <v>7102</v>
-      </c>
-    </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.15">
+    </row>
+    <row r="509" spans="1:15">
       <c r="A509" t="s">
-        <v>7115</v>
+        <v>7117</v>
       </c>
       <c r="B509" t="s">
-        <v>7116</v>
+        <v>7118</v>
       </c>
       <c r="C509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="D509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="E509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="F509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="G509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="H509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="I509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="J509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="K509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="L509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="M509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="N509" t="s">
-        <v>7117</v>
+        <v>7119</v>
       </c>
       <c r="O509" t="s">
-        <v>7116</v>
-      </c>
-    </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7118</v>
+      </c>
+    </row>
+    <row r="510" spans="1:15">
       <c r="A510" t="s">
-        <v>7118</v>
+        <v>7120</v>
       </c>
       <c r="B510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="C510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="D510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="E510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="F510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="G510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="H510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="I510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="J510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="K510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="L510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="M510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="N510" t="s">
-        <v>7119</v>
+        <v>7121</v>
       </c>
       <c r="O510" t="s">
-        <v>7119</v>
-      </c>
-    </row>
-    <row r="511" spans="1:15" ht="342" x14ac:dyDescent="0.15">
+        <v>7121</v>
+      </c>
+    </row>
+    <row r="511" ht="374.4" spans="1:15">
       <c r="A511" t="s">
-        <v>7120</v>
+        <v>7122</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="F511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="G511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="H511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="I511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="J511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="K511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="L511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="M511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="N511" s="1" t="s">
-        <v>7121</v>
+        <v>7123</v>
       </c>
       <c r="O511" s="1" t="s">
-        <v>7121</v>
-      </c>
-    </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A512" t="s">
-        <v>7122</v>
-      </c>
-      <c r="B512" t="s">
         <v>7123</v>
       </c>
-      <c r="C512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="D512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="E512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="F512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="G512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="H512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="I512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="J512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="K512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="L512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="M512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="N512" t="s">
-        <v>7123</v>
-      </c>
-      <c r="O512" t="s">
-        <v>7123</v>
-      </c>
-    </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A513" t="s">
+    </row>
+    <row r="512" spans="1:15">
+      <c r="A512" s="2" t="s">
         <v>7124</v>
       </c>
-      <c r="B513" t="s">
+      <c r="B512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="C513" t="s">
+      <c r="C512" s="2" t="s">
+        <v>7126</v>
+      </c>
+      <c r="D512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="D513" t="s">
+      <c r="E512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="E513" t="s">
+      <c r="F512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="F513" t="s">
+      <c r="G512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="G513" t="s">
+      <c r="H512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="H513" t="s">
+      <c r="I512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="I513" t="s">
+      <c r="J512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="J513" t="s">
+      <c r="K512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="K513" t="s">
+      <c r="L512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="L513" t="s">
+      <c r="M512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="M513" t="s">
+      <c r="N512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="N513" t="s">
+      <c r="O512" s="2" t="s">
         <v>7125</v>
       </c>
-      <c r="O513" t="s">
-        <v>7125</v>
-      </c>
-    </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A514" s="1" t="s">
-        <v>7126</v>
-      </c>
-      <c r="B514" t="s">
+    </row>
+    <row r="513" spans="1:15">
+      <c r="A513" s="2" t="s">
         <v>7127</v>
       </c>
-      <c r="C514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="D514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="E514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="F514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="G514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="H514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="I514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="J514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="K514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="L514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="M514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="N514" t="s">
-        <v>7127</v>
-      </c>
-      <c r="O514" t="s">
-        <v>7127</v>
-      </c>
-    </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A515" t="s">
+      <c r="B513" s="3" t="s">
         <v>7128</v>
       </c>
-      <c r="B515" t="s">
+      <c r="C513" s="3" t="s">
         <v>7129</v>
       </c>
-      <c r="C515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="D515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="E515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="F515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="G515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="H515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="I515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="J515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="K515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="L515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="M515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="N515" t="s">
-        <v>7129</v>
-      </c>
-      <c r="O515" t="s">
-        <v>7129</v>
-      </c>
-    </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A516" t="s">
+      <c r="D513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="E513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="F513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="G513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="H513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="I513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="J513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="K513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="L513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="M513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="N513" s="3" t="s">
+        <v>7128</v>
+      </c>
+      <c r="O513" s="3" t="s">
+        <v>7128</v>
+      </c>
+    </row>
+    <row r="514" spans="1:15">
+      <c r="A514" s="4" t="s">
         <v>7130</v>
       </c>
-      <c r="B516" t="s">
+      <c r="B514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="C516" t="s">
+      <c r="C514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="D516" t="s">
+      <c r="D514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="E516" t="s">
+      <c r="E514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="F516" t="s">
+      <c r="F514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="G516" t="s">
+      <c r="G514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="H516" t="s">
+      <c r="H514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="I516" t="s">
+      <c r="I514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="J516" t="s">
+      <c r="J514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="K516" t="s">
+      <c r="K514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="L516" t="s">
+      <c r="L514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="M516" t="s">
+      <c r="M514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="N516" t="s">
+      <c r="N514" s="2" t="s">
         <v>7131</v>
       </c>
-      <c r="O516" t="s">
+      <c r="O514" s="2" t="s">
         <v>7131</v>
       </c>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A517" t="s">
+    <row r="515" spans="1:15">
+      <c r="A515" s="2" t="s">
         <v>7132</v>
       </c>
-      <c r="B517" t="s">
+      <c r="B515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="C517" t="s">
+      <c r="C515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="D517" t="s">
+      <c r="D515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="E517" t="s">
+      <c r="E515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="F517" t="s">
+      <c r="F515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="G517" t="s">
+      <c r="G515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="H517" t="s">
+      <c r="H515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="I517" t="s">
+      <c r="I515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="J517" t="s">
+      <c r="J515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="K517" t="s">
+      <c r="K515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="L517" t="s">
+      <c r="L515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="M517" t="s">
+      <c r="M515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="N517" t="s">
+      <c r="N515" s="2" t="s">
         <v>7133</v>
       </c>
-      <c r="O517" t="s">
+      <c r="O515" s="2" t="s">
         <v>7133</v>
       </c>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A518" t="s">
+    <row r="516" spans="1:15">
+      <c r="A516" s="2" t="s">
         <v>7134</v>
       </c>
-      <c r="B518" t="s">
+      <c r="B516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="C518" t="s">
+      <c r="C516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="D518" t="s">
+      <c r="D516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="E518" t="s">
+      <c r="E516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="F518" t="s">
+      <c r="F516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="G518" t="s">
+      <c r="G516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="H518" t="s">
+      <c r="H516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="I518" t="s">
+      <c r="I516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="J518" t="s">
+      <c r="J516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="K518" t="s">
+      <c r="K516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="L518" t="s">
+      <c r="L516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="M518" t="s">
+      <c r="M516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="N518" t="s">
+      <c r="N516" s="2" t="s">
         <v>7135</v>
       </c>
-      <c r="O518" t="s">
+      <c r="O516" s="2" t="s">
         <v>7135</v>
       </c>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A519" t="s">
+    <row r="517" spans="1:15">
+      <c r="A517" s="2" t="s">
         <v>7136</v>
       </c>
-      <c r="B519" t="s">
+      <c r="B517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="C519" t="s">
+      <c r="C517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="D519" t="s">
+      <c r="D517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="E519" t="s">
+      <c r="E517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="F519" t="s">
+      <c r="F517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="G519" t="s">
+      <c r="G517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="H519" t="s">
+      <c r="H517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="I519" t="s">
+      <c r="I517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="J519" t="s">
+      <c r="J517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="K519" t="s">
+      <c r="K517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="L519" t="s">
+      <c r="L517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="M519" t="s">
+      <c r="M517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="N519" t="s">
+      <c r="N517" s="2" t="s">
         <v>7137</v>
       </c>
-      <c r="O519" t="s">
+      <c r="O517" s="2" t="s">
         <v>7137</v>
       </c>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A520" t="s">
+    <row r="518" spans="1:15">
+      <c r="A518" s="2" t="s">
         <v>7138</v>
       </c>
-      <c r="B520" t="s">
+      <c r="B518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="C520" t="s">
+      <c r="C518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="D520" t="s">
+      <c r="D518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="E520" t="s">
+      <c r="E518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="F520" t="s">
+      <c r="F518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="G520" t="s">
+      <c r="G518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="H520" t="s">
+      <c r="H518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="I520" t="s">
+      <c r="I518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="J520" t="s">
+      <c r="J518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="K520" t="s">
+      <c r="K518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="L520" t="s">
+      <c r="L518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="M520" t="s">
+      <c r="M518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="N520" t="s">
+      <c r="N518" s="2" t="s">
         <v>7139</v>
       </c>
-      <c r="O520" t="s">
+      <c r="O518" s="2" t="s">
         <v>7139</v>
       </c>
     </row>
-    <row r="521" spans="1:15" ht="15" x14ac:dyDescent="0.15">
-      <c r="A521" s="2" t="s">
+    <row r="519" spans="1:15">
+      <c r="A519" s="2" t="s">
         <v>7140</v>
       </c>
-      <c r="B521" t="s">
+      <c r="B519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="C521" t="s">
+      <c r="C519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="D521" t="s">
+      <c r="D519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="E521" t="s">
+      <c r="E519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="F521" t="s">
+      <c r="F519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="G521" t="s">
+      <c r="G519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="H521" t="s">
+      <c r="H519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="I521" t="s">
+      <c r="I519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="J521" t="s">
+      <c r="J519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="K521" t="s">
+      <c r="K519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="L521" t="s">
+      <c r="L519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="M521" t="s">
+      <c r="M519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="N521" t="s">
+      <c r="N519" s="2" t="s">
         <v>7141</v>
       </c>
-      <c r="O521" t="s">
+      <c r="O519" s="2" t="s">
         <v>7141</v>
       </c>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A522" t="s">
+    <row r="520" spans="1:15">
+      <c r="A520" s="2" t="s">
         <v>7142</v>
       </c>
-      <c r="B522" t="s">
+      <c r="B520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="C522" t="s">
+      <c r="C520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="D522" t="s">
+      <c r="D520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="E522" t="s">
+      <c r="E520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="F522" t="s">
+      <c r="F520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="G522" t="s">
+      <c r="G520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="H522" t="s">
+      <c r="H520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="I522" t="s">
+      <c r="I520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="J522" t="s">
+      <c r="J520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="K522" t="s">
+      <c r="K520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="L522" t="s">
+      <c r="L520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="M522" t="s">
+      <c r="M520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="N522" t="s">
+      <c r="N520" s="2" t="s">
         <v>7143</v>
       </c>
-      <c r="O522" t="s">
+      <c r="O520" s="2" t="s">
         <v>7143</v>
       </c>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A523" t="s">
+    <row r="521" spans="1:15">
+      <c r="A521" s="5" t="s">
         <v>7144</v>
       </c>
-      <c r="B523" t="s">
+      <c r="B521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="C523" t="s">
+      <c r="C521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="D523" t="s">
+      <c r="D521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="E523" t="s">
+      <c r="E521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="F523" t="s">
+      <c r="F521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="G523" t="s">
+      <c r="G521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="H523" t="s">
+      <c r="H521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="I523" t="s">
+      <c r="I521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="J523" t="s">
+      <c r="J521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="K523" t="s">
+      <c r="K521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="L523" t="s">
+      <c r="L521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="M523" t="s">
+      <c r="M521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="N523" t="s">
+      <c r="N521" s="2" t="s">
         <v>7145</v>
       </c>
-      <c r="O523" t="s">
+      <c r="O521" s="2" t="s">
         <v>7145</v>
       </c>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A524" t="s">
+    <row r="522" spans="1:15">
+      <c r="A522" s="2" t="s">
         <v>7146</v>
       </c>
-      <c r="B524" t="s">
+      <c r="B522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="C524" t="s">
+      <c r="C522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="D524" t="s">
+      <c r="D522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="E524" t="s">
+      <c r="E522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="F524" t="s">
+      <c r="F522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="G524" t="s">
+      <c r="G522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="H524" t="s">
+      <c r="H522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="I524" t="s">
+      <c r="I522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="J524" t="s">
+      <c r="J522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="K524" t="s">
+      <c r="K522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="L524" t="s">
+      <c r="L522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="M524" t="s">
+      <c r="M522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="N524" t="s">
+      <c r="N522" s="2" t="s">
         <v>7147</v>
       </c>
-      <c r="O524" t="s">
+      <c r="O522" s="2" t="s">
         <v>7147</v>
       </c>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A525" t="s">
+    <row r="523" spans="1:15">
+      <c r="A523" s="2" t="s">
         <v>7148</v>
       </c>
-      <c r="B525" t="s">
+      <c r="B523" s="2" t="s">
         <v>7149</v>
       </c>
-      <c r="C525" t="s">
+      <c r="C523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="D523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="E523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="F523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="G523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="H523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="I523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="J523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="K523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="L523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="M523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="N523" s="2" t="s">
+        <v>7149</v>
+      </c>
+      <c r="O523" s="2" t="s">
+        <v>7149</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15">
+      <c r="A524" s="2" t="s">
         <v>7150</v>
       </c>
-      <c r="D525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="E525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="F525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="G525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="H525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="I525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="J525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="K525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="L525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="M525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="N525" t="s">
-        <v>7150</v>
-      </c>
-      <c r="O525" t="s">
-        <v>7150</v>
-      </c>
-    </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A526" s="3" t="s">
+      <c r="B524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="C524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="D524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="E524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="F524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="G524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="H524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="I524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="J524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="K524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="L524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="M524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="N524" s="2" t="s">
+        <v>7151</v>
+      </c>
+      <c r="O524" s="2" t="s">
+        <v>7151</v>
+      </c>
+    </row>
+    <row r="525" spans="1:15">
+      <c r="A525" s="2" t="s">
+        <v>7152</v>
+      </c>
+      <c r="B525" s="2" t="s">
         <v>7153</v>
       </c>
-      <c r="B526" s="3" t="s">
+      <c r="C525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="D525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="E525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="F525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="G525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="H525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="I525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="J525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="K525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="L525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="M525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="N525" s="2" t="s">
+        <v>7154</v>
+      </c>
+      <c r="O525" s="2" t="s">
+        <v>7154</v>
+      </c>
+    </row>
+    <row r="526" spans="1:15">
+      <c r="A526" t="s">
         <v>7155</v>
       </c>
-      <c r="C526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="D526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="E526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="F526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="G526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="H526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="I526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="J526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="K526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="L526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="M526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="N526" s="3" t="s">
-        <v>7155</v>
-      </c>
-      <c r="O526" s="3" t="s">
-        <v>7155</v>
-      </c>
-    </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A527" s="3" t="s">
-        <v>7154</v>
-      </c>
-      <c r="B527" s="3" t="s">
+      <c r="B526" t="s">
         <v>7156</v>
       </c>
-      <c r="C527" s="3" t="s">
+      <c r="C526" t="s">
         <v>7156</v>
       </c>
-      <c r="D527" s="3" t="s">
+      <c r="D526" t="s">
         <v>7156</v>
       </c>
-      <c r="E527" s="3" t="s">
+      <c r="E526" t="s">
         <v>7156</v>
       </c>
-      <c r="F527" s="3" t="s">
+      <c r="F526" t="s">
         <v>7156</v>
       </c>
-      <c r="G527" s="3" t="s">
+      <c r="G526" t="s">
         <v>7156</v>
       </c>
-      <c r="H527" s="3" t="s">
+      <c r="H526" t="s">
         <v>7156</v>
       </c>
-      <c r="I527" s="3" t="s">
+      <c r="I526" t="s">
         <v>7156</v>
       </c>
-      <c r="J527" s="3" t="s">
+      <c r="J526" t="s">
         <v>7156</v>
       </c>
-      <c r="K527" s="3" t="s">
+      <c r="K526" t="s">
         <v>7156</v>
       </c>
-      <c r="L527" s="3" t="s">
+      <c r="L526" t="s">
         <v>7156</v>
       </c>
-      <c r="M527" s="3" t="s">
+      <c r="M526" t="s">
         <v>7156</v>
       </c>
-      <c r="N527" s="3" t="s">
+      <c r="N526" t="s">
         <v>7156</v>
       </c>
-      <c r="O527" s="3" t="s">
+      <c r="O526" t="s">
         <v>7156</v>
       </c>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A528" s="3" t="s">
+    <row r="527" spans="1:15">
+      <c r="A527" t="s">
         <v>7157</v>
       </c>
-      <c r="B528" s="3" t="s">
+      <c r="B527" t="s">
         <v>7158</v>
       </c>
-      <c r="C528" s="3" t="s">
+      <c r="C527" t="s">
         <v>7158</v>
       </c>
-      <c r="D528" s="3" t="s">
+      <c r="D527" t="s">
         <v>7158</v>
       </c>
-      <c r="E528" s="3" t="s">
+      <c r="E527" t="s">
         <v>7158</v>
       </c>
-      <c r="F528" s="3" t="s">
+      <c r="F527" t="s">
         <v>7158</v>
       </c>
-      <c r="G528" s="3" t="s">
+      <c r="G527" t="s">
         <v>7158</v>
       </c>
-      <c r="H528" s="3" t="s">
+      <c r="H527" t="s">
         <v>7158</v>
       </c>
-      <c r="I528" s="3" t="s">
+      <c r="I527" t="s">
         <v>7158</v>
       </c>
-      <c r="J528" s="3" t="s">
+      <c r="J527" t="s">
         <v>7158</v>
       </c>
-      <c r="K528" s="3" t="s">
+      <c r="K527" t="s">
         <v>7158</v>
       </c>
-      <c r="L528" s="3" t="s">
+      <c r="L527" t="s">
         <v>7158</v>
       </c>
-      <c r="M528" s="3" t="s">
+      <c r="M527" t="s">
         <v>7158</v>
       </c>
-      <c r="N528" s="3" t="s">
+      <c r="N527" t="s">
         <v>7158</v>
       </c>
-      <c r="O528" s="3" t="s">
+      <c r="O527" t="s">
         <v>7158</v>
       </c>
     </row>
-    <row r="529" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A529" s="3" t="s">
+    <row r="528" spans="1:15">
+      <c r="A528" t="s">
         <v>7159</v>
       </c>
-      <c r="B529" s="3" t="s">
+      <c r="B528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="C528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="D528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="E528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="F528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="G528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="H528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="I528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="J528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="K528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="L528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="M528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="N528" t="s">
+        <v>7160</v>
+      </c>
+      <c r="O528" t="s">
+        <v>7160</v>
+      </c>
+    </row>
+    <row r="529" spans="1:15">
+      <c r="A529" t="s">
         <v>7161</v>
       </c>
-      <c r="C529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="D529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="E529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="F529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="G529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="H529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="I529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="J529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="K529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="L529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="M529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="N529" s="3" t="s">
-        <v>7161</v>
-      </c>
-      <c r="O529" s="3" t="s">
-        <v>7161</v>
-      </c>
-    </row>
-    <row r="530" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A530" s="3" t="s">
-        <v>7160</v>
-      </c>
-      <c r="B530" s="3" t="s">
+      <c r="B529" t="s">
         <v>7162</v>
       </c>
-      <c r="C530" s="3" t="s">
+      <c r="C529" t="s">
         <v>7162</v>
       </c>
-      <c r="D530" s="3" t="s">
+      <c r="D529" t="s">
         <v>7162</v>
       </c>
-      <c r="E530" s="3" t="s">
+      <c r="E529" t="s">
         <v>7162</v>
       </c>
-      <c r="F530" s="3" t="s">
+      <c r="F529" t="s">
         <v>7162</v>
       </c>
-      <c r="G530" s="3" t="s">
+      <c r="G529" t="s">
         <v>7162</v>
       </c>
-      <c r="H530" s="3" t="s">
+      <c r="H529" t="s">
         <v>7162</v>
       </c>
-      <c r="I530" s="3" t="s">
+      <c r="I529" t="s">
         <v>7162</v>
       </c>
-      <c r="J530" s="3" t="s">
+      <c r="J529" t="s">
         <v>7162</v>
       </c>
-      <c r="K530" s="3" t="s">
+      <c r="K529" t="s">
         <v>7162</v>
       </c>
-      <c r="L530" s="3" t="s">
+      <c r="L529" t="s">
         <v>7162</v>
       </c>
-      <c r="M530" s="3" t="s">
+      <c r="M529" t="s">
         <v>7162</v>
       </c>
-      <c r="N530" s="3" t="s">
+      <c r="N529" t="s">
         <v>7162</v>
       </c>
-      <c r="O530" s="3" t="s">
+      <c r="O529" t="s">
         <v>7162</v>
       </c>
     </row>
+    <row r="530" spans="1:15">
+      <c r="A530" t="s">
+        <v>7163</v>
+      </c>
+      <c r="B530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="C530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="D530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="E530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="F530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="G530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="H530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="I530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="J530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="K530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="L530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="M530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="N530" t="s">
+        <v>7164</v>
+      </c>
+      <c r="O530" t="s">
+        <v>7164</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A277:O447 A448 C448:O448 A449:O467 C118:O118 A502:O508 A501 A499:O500 A498 A250:O274 A275 C275 A1:O117 A118 A119:O248 A249 A469:O497" numberStoredAsText="1"/>
+    <ignoredError sqref="A249 A119:O248 A118 A1:O117 C275 A275 A250:O274 A498 A499:O500 A501 A502:O508 C118:O118 A469:O497 A449:O467 C448:O448 A448 A277:O447" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/apps/nuxt/i18n/i18n.xlsx
+++ b/apps/nuxt/i18n/i18n.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wysha_Object\wysha_Project\WebProjects\TypeWords\apps\nuxt\i18n\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8F066C-180A-4467-A967-03BB43DCE702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500"/>
+    <workbookView xWindow="360" yWindow="3390" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7950" uniqueCount="7165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7995" uniqueCount="7171">
   <si>
     <t>key</t>
   </si>
@@ -21538,19 +21544,36 @@
   </si>
   <si>
     <t>导入json文件</t>
+  </si>
+  <si>
+    <t>self_assessment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自我评估</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>word_test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单词测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>identify_method</t>
+  </si>
+  <si>
+    <t>自测方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -21562,355 +21585,37 @@
       <sz val="11"/>
       <color rgb="FFCE9178"/>
       <name val="Consolas"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -21918,321 +21623,32 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -22554,20 +21970,20 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O530"/>
-  <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="15.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O533"/>
+  <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="21.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22614,7 +22030,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -22661,7 +22077,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -22708,7 +22124,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -22755,7 +22171,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -22802,7 +22218,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -22849,7 +22265,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -22896,7 +22312,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -22943,7 +22359,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -22990,7 +22406,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -23037,7 +22453,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -23084,7 +22500,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>150</v>
       </c>
@@ -23131,7 +22547,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>165</v>
       </c>
@@ -23178,7 +22594,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>180</v>
       </c>
@@ -23225,7 +22641,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>195</v>
       </c>
@@ -23272,7 +22688,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>210</v>
       </c>
@@ -23319,7 +22735,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>225</v>
       </c>
@@ -23366,7 +22782,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>240</v>
       </c>
@@ -23413,7 +22829,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>255</v>
       </c>
@@ -23460,7 +22876,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>270</v>
       </c>
@@ -23507,7 +22923,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>285</v>
       </c>
@@ -23554,7 +22970,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>300</v>
       </c>
@@ -23601,7 +23017,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>314</v>
       </c>
@@ -23648,7 +23064,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>328</v>
       </c>
@@ -23695,7 +23111,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>342</v>
       </c>
@@ -23742,7 +23158,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>357</v>
       </c>
@@ -23789,7 +23205,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>372</v>
       </c>
@@ -23836,7 +23252,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>387</v>
       </c>
@@ -23883,7 +23299,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>402</v>
       </c>
@@ -23930,7 +23346,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>417</v>
       </c>
@@ -23977,7 +23393,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>432</v>
       </c>
@@ -24024,7 +23440,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>447</v>
       </c>
@@ -24071,7 +23487,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>462</v>
       </c>
@@ -24118,7 +23534,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>477</v>
       </c>
@@ -24165,7 +23581,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>492</v>
       </c>
@@ -24212,7 +23628,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>507</v>
       </c>
@@ -24259,7 +23675,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>510</v>
       </c>
@@ -24306,7 +23722,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>513</v>
       </c>
@@ -24353,7 +23769,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>528</v>
       </c>
@@ -24400,7 +23816,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>541</v>
       </c>
@@ -24447,7 +23863,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>556</v>
       </c>
@@ -24494,7 +23910,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>569</v>
       </c>
@@ -24541,7 +23957,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>582</v>
       </c>
@@ -24588,7 +24004,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>595</v>
       </c>
@@ -24635,7 +24051,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>610</v>
       </c>
@@ -24682,7 +24098,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>624</v>
       </c>
@@ -24729,7 +24145,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>638</v>
       </c>
@@ -24776,7 +24192,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>653</v>
       </c>
@@ -24823,7 +24239,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>667</v>
       </c>
@@ -24870,7 +24286,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>681</v>
       </c>
@@ -24917,7 +24333,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
         <v>694</v>
       </c>
@@ -24964,7 +24380,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>706</v>
       </c>
@@ -25011,7 +24427,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
         <v>719</v>
       </c>
@@ -25058,7 +24474,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>732</v>
       </c>
@@ -25105,7 +24521,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>747</v>
       </c>
@@ -25152,7 +24568,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>760</v>
       </c>
@@ -25199,7 +24615,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>775</v>
       </c>
@@ -25246,7 +24662,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>790</v>
       </c>
@@ -25293,7 +24709,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>805</v>
       </c>
@@ -25340,7 +24756,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>820</v>
       </c>
@@ -25387,7 +24803,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>835</v>
       </c>
@@ -25434,7 +24850,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>850</v>
       </c>
@@ -25481,7 +24897,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>865</v>
       </c>
@@ -25528,7 +24944,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>880</v>
       </c>
@@ -25575,7 +24991,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>895</v>
       </c>
@@ -25622,7 +25038,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>910</v>
       </c>
@@ -25669,7 +25085,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>925</v>
       </c>
@@ -25716,7 +25132,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>940</v>
       </c>
@@ -25763,7 +25179,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>955</v>
       </c>
@@ -25810,7 +25226,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
         <v>970</v>
       </c>
@@ -25857,7 +25273,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
         <v>985</v>
       </c>
@@ -25904,7 +25320,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A72" t="s">
         <v>1000</v>
       </c>
@@ -25951,7 +25367,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
         <v>1015</v>
       </c>
@@ -25998,7 +25414,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A74" t="s">
         <v>1030</v>
       </c>
@@ -26045,7 +25461,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A75" t="s">
         <v>1045</v>
       </c>
@@ -26092,7 +25508,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
         <v>1060</v>
       </c>
@@ -26139,7 +25555,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
         <v>1075</v>
       </c>
@@ -26186,7 +25602,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
         <v>1090</v>
       </c>
@@ -26233,7 +25649,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A79" t="s">
         <v>1105</v>
       </c>
@@ -26280,7 +25696,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A80" t="s">
         <v>1120</v>
       </c>
@@ -26327,7 +25743,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
         <v>1135</v>
       </c>
@@ -26374,7 +25790,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A82" t="s">
         <v>1149</v>
       </c>
@@ -26421,7 +25837,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
         <v>1162</v>
       </c>
@@ -26468,7 +25884,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="84" spans="1:15">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A84" t="s">
         <v>1173</v>
       </c>
@@ -26515,7 +25931,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="85" spans="1:15">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A85" t="s">
         <v>1188</v>
       </c>
@@ -26562,7 +25978,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="86" spans="1:15">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A86" t="s">
         <v>1202</v>
       </c>
@@ -26609,7 +26025,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="87" spans="1:15">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A87" t="s">
         <v>1217</v>
       </c>
@@ -26656,7 +26072,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="88" spans="1:15">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
         <v>1232</v>
       </c>
@@ -26703,7 +26119,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="89" spans="1:15">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A89" t="s">
         <v>1247</v>
       </c>
@@ -26750,7 +26166,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="90" spans="1:15">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
         <v>1262</v>
       </c>
@@ -26797,7 +26213,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="91" spans="1:15">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
         <v>1277</v>
       </c>
@@ -26844,7 +26260,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="92" spans="1:15">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
         <v>1292</v>
       </c>
@@ -26891,7 +26307,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="93" spans="1:15">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
         <v>1307</v>
       </c>
@@ -26938,7 +26354,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="94" spans="1:15">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
         <v>1321</v>
       </c>
@@ -26985,7 +26401,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="95" spans="1:15">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A95" t="s">
         <v>1336</v>
       </c>
@@ -27032,7 +26448,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="96" spans="1:15">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
         <v>1351</v>
       </c>
@@ -27079,7 +26495,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="97" spans="1:15">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
         <v>1366</v>
       </c>
@@ -27126,7 +26542,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="98" spans="1:15">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
         <v>1381</v>
       </c>
@@ -27173,7 +26589,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="99" spans="1:15">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
         <v>1396</v>
       </c>
@@ -27220,7 +26636,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A100" t="s">
         <v>1411</v>
       </c>
@@ -27267,7 +26683,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="101" spans="1:15">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
         <v>1426</v>
       </c>
@@ -27314,7 +26730,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
         <v>1441</v>
       </c>
@@ -27361,7 +26777,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
         <v>1456</v>
       </c>
@@ -27408,7 +26824,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
         <v>1470</v>
       </c>
@@ -27455,7 +26871,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
         <v>1485</v>
       </c>
@@ -27502,7 +26918,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A106" t="s">
         <v>1500</v>
       </c>
@@ -27549,7 +26965,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A107" t="s">
         <v>1515</v>
       </c>
@@ -27596,7 +27012,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A108" t="s">
         <v>1530</v>
       </c>
@@ -27643,7 +27059,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
         <v>1545</v>
       </c>
@@ -27690,7 +27106,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="110" spans="1:15">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
         <v>1560</v>
       </c>
@@ -27737,7 +27153,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="111" spans="1:15">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
         <v>1574</v>
       </c>
@@ -27784,7 +27200,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="112" spans="1:15">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
         <v>1589</v>
       </c>
@@ -27831,7 +27247,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="113" spans="1:15">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
         <v>1604</v>
       </c>
@@ -27878,7 +27294,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="114" spans="1:15">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
         <v>1619</v>
       </c>
@@ -27925,7 +27341,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="115" spans="1:15">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
         <v>1634</v>
       </c>
@@ -27972,7 +27388,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="116" spans="1:15">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
         <v>1649</v>
       </c>
@@ -28019,7 +27435,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="117" spans="1:15">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
         <v>1660</v>
       </c>
@@ -28066,7 +27482,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="118" spans="1:15">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
         <v>1673</v>
       </c>
@@ -28113,7 +27529,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="119" spans="1:15">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
         <v>1688</v>
       </c>
@@ -28160,7 +27576,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="120" spans="1:15">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
         <v>1703</v>
       </c>
@@ -28207,7 +27623,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="121" spans="1:15">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
         <v>1718</v>
       </c>
@@ -28254,7 +27670,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="122" spans="1:15">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
         <v>1732</v>
       </c>
@@ -28301,7 +27717,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="123" spans="1:15">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A123" t="s">
         <v>1747</v>
       </c>
@@ -28348,7 +27764,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="124" spans="1:15">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
         <v>1762</v>
       </c>
@@ -28395,7 +27811,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="125" spans="1:15">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
         <v>1777</v>
       </c>
@@ -28442,7 +27858,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="126" spans="1:15">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
         <v>1792</v>
       </c>
@@ -28489,7 +27905,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="127" spans="1:15">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A127" t="s">
         <v>1807</v>
       </c>
@@ -28536,7 +27952,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="128" spans="1:15">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A128" t="s">
         <v>1822</v>
       </c>
@@ -28583,7 +27999,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="129" spans="1:15">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A129" t="s">
         <v>1837</v>
       </c>
@@ -28630,7 +28046,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="130" spans="1:15">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A130" t="s">
         <v>1850</v>
       </c>
@@ -28677,7 +28093,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="131" spans="1:15">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A131" t="s">
         <v>1862</v>
       </c>
@@ -28724,7 +28140,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="132" spans="1:15">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A132" t="s">
         <v>1877</v>
       </c>
@@ -28771,7 +28187,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="133" spans="1:15">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A133" t="s">
         <v>1882</v>
       </c>
@@ -28818,7 +28234,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="134" spans="1:15">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A134" t="s">
         <v>1897</v>
       </c>
@@ -28865,7 +28281,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="135" spans="1:15">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A135" t="s">
         <v>1912</v>
       </c>
@@ -28912,7 +28328,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="136" spans="1:15">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A136" t="s">
         <v>1927</v>
       </c>
@@ -28959,7 +28375,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="137" spans="1:15">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A137" t="s">
         <v>1942</v>
       </c>
@@ -29006,7 +28422,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="138" spans="1:15">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A138" t="s">
         <v>1957</v>
       </c>
@@ -29053,7 +28469,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="139" spans="1:15">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A139" t="s">
         <v>1972</v>
       </c>
@@ -29100,7 +28516,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="140" spans="1:15">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A140" t="s">
         <v>1986</v>
       </c>
@@ -29147,7 +28563,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="141" spans="1:15">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A141" t="s">
         <v>2001</v>
       </c>
@@ -29194,7 +28610,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="142" spans="1:15">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A142" t="s">
         <v>2016</v>
       </c>
@@ -29241,7 +28657,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="143" spans="1:15">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A143" t="s">
         <v>2031</v>
       </c>
@@ -29288,7 +28704,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="144" spans="1:15">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A144" t="s">
         <v>2046</v>
       </c>
@@ -29335,7 +28751,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="145" spans="1:15">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A145" t="s">
         <v>2061</v>
       </c>
@@ -29382,7 +28798,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="146" spans="1:15">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A146" t="s">
         <v>2075</v>
       </c>
@@ -29429,7 +28845,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="147" spans="1:15">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A147" t="s">
         <v>2090</v>
       </c>
@@ -29476,7 +28892,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="148" spans="1:15">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A148" t="s">
         <v>2105</v>
       </c>
@@ -29523,7 +28939,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="149" spans="1:15">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A149" t="s">
         <v>2120</v>
       </c>
@@ -29570,7 +28986,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="150" spans="1:15">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A150" t="s">
         <v>2135</v>
       </c>
@@ -29617,7 +29033,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="151" spans="1:15">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A151" t="s">
         <v>2150</v>
       </c>
@@ -29664,7 +29080,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="152" spans="1:15">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A152" t="s">
         <v>2164</v>
       </c>
@@ -29711,7 +29127,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="153" spans="1:15">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A153" t="s">
         <v>2170</v>
       </c>
@@ -29758,7 +29174,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="154" spans="1:15">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A154" t="s">
         <v>2183</v>
       </c>
@@ -29805,7 +29221,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="155" spans="1:15">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A155" t="s">
         <v>2198</v>
       </c>
@@ -29852,7 +29268,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="156" spans="1:15">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A156" t="s">
         <v>2212</v>
       </c>
@@ -29899,7 +29315,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="157" spans="1:15">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A157" t="s">
         <v>2223</v>
       </c>
@@ -29946,7 +29362,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="158" spans="1:15">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A158" t="s">
         <v>2237</v>
       </c>
@@ -29993,7 +29409,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="159" spans="1:15">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A159" t="s">
         <v>2252</v>
       </c>
@@ -30040,7 +29456,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="160" spans="1:15">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A160" t="s">
         <v>2267</v>
       </c>
@@ -30087,7 +29503,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="161" spans="1:15">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A161" t="s">
         <v>2282</v>
       </c>
@@ -30134,7 +29550,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="162" spans="1:15">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A162" t="s">
         <v>2297</v>
       </c>
@@ -30181,7 +29597,7 @@
         <v>2311</v>
       </c>
     </row>
-    <row r="163" spans="1:15">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A163" t="s">
         <v>2312</v>
       </c>
@@ -30228,7 +29644,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="164" spans="1:15">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A164" t="s">
         <v>2327</v>
       </c>
@@ -30275,7 +29691,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="165" spans="1:15">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A165" t="s">
         <v>2341</v>
       </c>
@@ -30322,7 +29738,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="166" spans="1:15">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A166" t="s">
         <v>2355</v>
       </c>
@@ -30369,7 +29785,7 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="167" spans="1:15">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A167" t="s">
         <v>2367</v>
       </c>
@@ -30416,7 +29832,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="168" spans="1:15">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A168" t="s">
         <v>2382</v>
       </c>
@@ -30463,7 +29879,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="169" spans="1:15">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A169" t="s">
         <v>2397</v>
       </c>
@@ -30510,7 +29926,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="170" spans="1:15">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A170" t="s">
         <v>2412</v>
       </c>
@@ -30557,7 +29973,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="171" spans="1:15">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A171" t="s">
         <v>2427</v>
       </c>
@@ -30604,7 +30020,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="172" spans="1:15">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A172" t="s">
         <v>2442</v>
       </c>
@@ -30651,7 +30067,7 @@
         <v>2445</v>
       </c>
     </row>
-    <row r="173" spans="1:15">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A173" t="s">
         <v>2454</v>
       </c>
@@ -30698,7 +30114,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="174" spans="1:15">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A174" t="s">
         <v>2467</v>
       </c>
@@ -30745,7 +30161,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="175" spans="1:15">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A175" t="s">
         <v>2482</v>
       </c>
@@ -30792,7 +30208,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="176" spans="1:15">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A176" t="s">
         <v>2497</v>
       </c>
@@ -30839,7 +30255,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="177" spans="1:15">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A177" t="s">
         <v>2512</v>
       </c>
@@ -30886,7 +30302,7 @@
         <v>2526</v>
       </c>
     </row>
-    <row r="178" spans="1:15">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A178" t="s">
         <v>2527</v>
       </c>
@@ -30933,7 +30349,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="179" spans="1:15">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A179" t="s">
         <v>2542</v>
       </c>
@@ -30980,7 +30396,7 @@
         <v>2545</v>
       </c>
     </row>
-    <row r="180" spans="1:15">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A180" t="s">
         <v>2556</v>
       </c>
@@ -31027,7 +30443,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="181" spans="1:15">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A181" t="s">
         <v>2571</v>
       </c>
@@ -31074,7 +30490,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="182" spans="1:15">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A182" t="s">
         <v>2585</v>
       </c>
@@ -31121,7 +30537,7 @@
         <v>2586</v>
       </c>
     </row>
-    <row r="183" spans="1:15">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A183" t="s">
         <v>2597</v>
       </c>
@@ -31168,7 +30584,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="184" spans="1:15">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A184" t="s">
         <v>2612</v>
       </c>
@@ -31215,7 +30631,7 @@
         <v>2626</v>
       </c>
     </row>
-    <row r="185" spans="1:15">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A185" t="s">
         <v>2627</v>
       </c>
@@ -31262,7 +30678,7 @@
         <v>2641</v>
       </c>
     </row>
-    <row r="186" spans="1:15">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A186" t="s">
         <v>2642</v>
       </c>
@@ -31309,7 +30725,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="187" spans="1:15">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A187" t="s">
         <v>2657</v>
       </c>
@@ -31356,7 +30772,7 @@
         <v>2671</v>
       </c>
     </row>
-    <row r="188" spans="1:15">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A188" t="s">
         <v>2672</v>
       </c>
@@ -31403,7 +30819,7 @@
         <v>2686</v>
       </c>
     </row>
-    <row r="189" spans="1:15">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A189" t="s">
         <v>2687</v>
       </c>
@@ -31450,7 +30866,7 @@
         <v>2701</v>
       </c>
     </row>
-    <row r="190" spans="1:15">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A190" t="s">
         <v>2702</v>
       </c>
@@ -31497,7 +30913,7 @@
         <v>2716</v>
       </c>
     </row>
-    <row r="191" spans="1:15">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A191" t="s">
         <v>2717</v>
       </c>
@@ -31544,7 +30960,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="192" spans="1:15">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A192" t="s">
         <v>2732</v>
       </c>
@@ -31591,7 +31007,7 @@
         <v>2745</v>
       </c>
     </row>
-    <row r="193" spans="1:15">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A193" t="s">
         <v>2746</v>
       </c>
@@ -31638,7 +31054,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="194" spans="1:15">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A194" t="s">
         <v>2759</v>
       </c>
@@ -31685,7 +31101,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="195" spans="1:15">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A195" t="s">
         <v>2771</v>
       </c>
@@ -31732,7 +31148,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="196" spans="1:15">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A196" t="s">
         <v>2785</v>
       </c>
@@ -31779,7 +31195,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="197" spans="1:15">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A197" t="s">
         <v>2799</v>
       </c>
@@ -31826,7 +31242,7 @@
         <v>2812</v>
       </c>
     </row>
-    <row r="198" spans="1:15">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A198" t="s">
         <v>2813</v>
       </c>
@@ -31873,7 +31289,7 @@
         <v>2827</v>
       </c>
     </row>
-    <row r="199" spans="1:15">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A199" t="s">
         <v>2828</v>
       </c>
@@ -31920,7 +31336,7 @@
         <v>2829</v>
       </c>
     </row>
-    <row r="200" spans="1:15">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A200" t="s">
         <v>2832</v>
       </c>
@@ -31967,7 +31383,7 @@
         <v>2833</v>
       </c>
     </row>
-    <row r="201" spans="1:15">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A201" t="s">
         <v>2846</v>
       </c>
@@ -32014,7 +31430,7 @@
         <v>2860</v>
       </c>
     </row>
-    <row r="202" spans="1:15">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A202" t="s">
         <v>2861</v>
       </c>
@@ -32061,7 +31477,7 @@
         <v>2862</v>
       </c>
     </row>
-    <row r="203" spans="1:15">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A203" t="s">
         <v>2875</v>
       </c>
@@ -32108,7 +31524,7 @@
         <v>2889</v>
       </c>
     </row>
-    <row r="204" spans="1:15">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A204" t="s">
         <v>2890</v>
       </c>
@@ -32155,7 +31571,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="205" spans="1:15">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A205" t="s">
         <v>2905</v>
       </c>
@@ -32202,7 +31618,7 @@
         <v>2919</v>
       </c>
     </row>
-    <row r="206" spans="1:15">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A206" t="s">
         <v>2920</v>
       </c>
@@ -32249,7 +31665,7 @@
         <v>2934</v>
       </c>
     </row>
-    <row r="207" spans="1:15">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A207" t="s">
         <v>2935</v>
       </c>
@@ -32296,7 +31712,7 @@
         <v>2949</v>
       </c>
     </row>
-    <row r="208" spans="1:15">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A208" t="s">
         <v>2950</v>
       </c>
@@ -32343,7 +31759,7 @@
         <v>2951</v>
       </c>
     </row>
-    <row r="209" spans="1:15">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A209" t="s">
         <v>2961</v>
       </c>
@@ -32390,7 +31806,7 @@
         <v>2962</v>
       </c>
     </row>
-    <row r="210" spans="1:15">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A210" t="s">
         <v>2975</v>
       </c>
@@ -32437,7 +31853,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="211" spans="1:15">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A211" t="s">
         <v>2989</v>
       </c>
@@ -32484,7 +31900,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="212" spans="1:15">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A212" t="s">
         <v>3004</v>
       </c>
@@ -32531,7 +31947,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="213" spans="1:15">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A213" t="s">
         <v>3017</v>
       </c>
@@ -32578,7 +31994,7 @@
         <v>3020</v>
       </c>
     </row>
-    <row r="214" spans="1:15">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A214" t="s">
         <v>3021</v>
       </c>
@@ -32625,7 +32041,7 @@
         <v>3035</v>
       </c>
     </row>
-    <row r="215" spans="1:15">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A215" t="s">
         <v>3036</v>
       </c>
@@ -32672,7 +32088,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="216" spans="1:15">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A216" t="s">
         <v>3040</v>
       </c>
@@ -32719,7 +32135,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="217" spans="1:15">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A217" t="s">
         <v>3055</v>
       </c>
@@ -32766,7 +32182,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="218" spans="1:15">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A218" t="s">
         <v>3065</v>
       </c>
@@ -32813,7 +32229,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="219" spans="1:15">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A219" t="s">
         <v>3080</v>
       </c>
@@ -32860,7 +32276,7 @@
         <v>3093</v>
       </c>
     </row>
-    <row r="220" spans="1:15">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A220" t="s">
         <v>3094</v>
       </c>
@@ -32907,7 +32323,7 @@
         <v>3108</v>
       </c>
     </row>
-    <row r="221" spans="1:15">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A221" t="s">
         <v>3109</v>
       </c>
@@ -32954,7 +32370,7 @@
         <v>3123</v>
       </c>
     </row>
-    <row r="222" spans="1:15">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A222" t="s">
         <v>3124</v>
       </c>
@@ -33001,7 +32417,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="223" spans="1:15">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A223" t="s">
         <v>3137</v>
       </c>
@@ -33048,7 +32464,7 @@
         <v>3151</v>
       </c>
     </row>
-    <row r="224" spans="1:15">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A224" t="s">
         <v>3152</v>
       </c>
@@ -33095,7 +32511,7 @@
         <v>3153</v>
       </c>
     </row>
-    <row r="225" spans="1:15">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A225" t="s">
         <v>3165</v>
       </c>
@@ -33142,7 +32558,7 @@
         <v>3179</v>
       </c>
     </row>
-    <row r="226" spans="1:15">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A226" t="s">
         <v>3180</v>
       </c>
@@ -33189,7 +32605,7 @@
         <v>3194</v>
       </c>
     </row>
-    <row r="227" spans="1:15">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A227" t="s">
         <v>3195</v>
       </c>
@@ -33236,7 +32652,7 @@
         <v>3209</v>
       </c>
     </row>
-    <row r="228" spans="1:15">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A228" t="s">
         <v>3210</v>
       </c>
@@ -33283,7 +32699,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="229" spans="1:15">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A229" t="s">
         <v>3224</v>
       </c>
@@ -33330,7 +32746,7 @@
         <v>3238</v>
       </c>
     </row>
-    <row r="230" spans="1:15">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A230" t="s">
         <v>3239</v>
       </c>
@@ -33377,7 +32793,7 @@
         <v>3253</v>
       </c>
     </row>
-    <row r="231" spans="1:15">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A231" t="s">
         <v>3254</v>
       </c>
@@ -33424,7 +32840,7 @@
         <v>3268</v>
       </c>
     </row>
-    <row r="232" spans="1:15">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A232" t="s">
         <v>3269</v>
       </c>
@@ -33471,7 +32887,7 @@
         <v>3283</v>
       </c>
     </row>
-    <row r="233" spans="1:15">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A233" t="s">
         <v>3284</v>
       </c>
@@ -33518,7 +32934,7 @@
         <v>3298</v>
       </c>
     </row>
-    <row r="234" spans="1:15">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A234" t="s">
         <v>3299</v>
       </c>
@@ -33565,7 +32981,7 @@
         <v>3313</v>
       </c>
     </row>
-    <row r="235" spans="1:15">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A235" t="s">
         <v>3314</v>
       </c>
@@ -33612,7 +33028,7 @@
         <v>3328</v>
       </c>
     </row>
-    <row r="236" spans="1:15">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A236" t="s">
         <v>3329</v>
       </c>
@@ -33659,7 +33075,7 @@
         <v>3343</v>
       </c>
     </row>
-    <row r="237" spans="1:15">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A237" t="s">
         <v>3344</v>
       </c>
@@ -33706,7 +33122,7 @@
         <v>3345</v>
       </c>
     </row>
-    <row r="238" spans="1:15">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A238" t="s">
         <v>3358</v>
       </c>
@@ -33753,7 +33169,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="239" spans="1:15">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A239" t="s">
         <v>3373</v>
       </c>
@@ -33800,7 +33216,7 @@
         <v>3387</v>
       </c>
     </row>
-    <row r="240" spans="1:15">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A240" t="s">
         <v>3388</v>
       </c>
@@ -33847,7 +33263,7 @@
         <v>3402</v>
       </c>
     </row>
-    <row r="241" spans="1:15">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A241" t="s">
         <v>3403</v>
       </c>
@@ -33894,7 +33310,7 @@
         <v>3404</v>
       </c>
     </row>
-    <row r="242" spans="1:15">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A242" t="s">
         <v>3416</v>
       </c>
@@ -33941,7 +33357,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="243" spans="1:15">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A243" t="s">
         <v>3430</v>
       </c>
@@ -33988,7 +33404,7 @@
         <v>3444</v>
       </c>
     </row>
-    <row r="244" spans="1:15">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A244" t="s">
         <v>3445</v>
       </c>
@@ -34035,7 +33451,7 @@
         <v>3459</v>
       </c>
     </row>
-    <row r="245" spans="1:15">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A245" t="s">
         <v>3460</v>
       </c>
@@ -34082,7 +33498,7 @@
         <v>3461</v>
       </c>
     </row>
-    <row r="246" spans="1:15">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A246" t="s">
         <v>3470</v>
       </c>
@@ -34129,7 +33545,7 @@
         <v>3484</v>
       </c>
     </row>
-    <row r="247" spans="1:15">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A247" t="s">
         <v>3485</v>
       </c>
@@ -34176,7 +33592,7 @@
         <v>3499</v>
       </c>
     </row>
-    <row r="248" spans="1:15">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A248" t="s">
         <v>3500</v>
       </c>
@@ -34223,7 +33639,7 @@
         <v>3514</v>
       </c>
     </row>
-    <row r="249" spans="1:15">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A249" t="s">
         <v>3515</v>
       </c>
@@ -34270,7 +33686,7 @@
         <v>3529</v>
       </c>
     </row>
-    <row r="250" spans="1:15">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A250" t="s">
         <v>3530</v>
       </c>
@@ -34317,7 +33733,7 @@
         <v>3544</v>
       </c>
     </row>
-    <row r="251" spans="1:15">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A251" t="s">
         <v>3545</v>
       </c>
@@ -34364,7 +33780,7 @@
         <v>3559</v>
       </c>
     </row>
-    <row r="252" spans="1:15">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A252" t="s">
         <v>3560</v>
       </c>
@@ -34411,7 +33827,7 @@
         <v>3574</v>
       </c>
     </row>
-    <row r="253" spans="1:15">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A253" t="s">
         <v>3575</v>
       </c>
@@ -34458,7 +33874,7 @@
         <v>3589</v>
       </c>
     </row>
-    <row r="254" spans="1:15">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A254" t="s">
         <v>3590</v>
       </c>
@@ -34505,7 +33921,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="255" spans="1:15">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A255" t="s">
         <v>3604</v>
       </c>
@@ -34552,7 +33968,7 @@
         <v>3618</v>
       </c>
     </row>
-    <row r="256" spans="1:15">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A256" t="s">
         <v>3619</v>
       </c>
@@ -34599,7 +34015,7 @@
         <v>3633</v>
       </c>
     </row>
-    <row r="257" spans="1:15">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A257" t="s">
         <v>3634</v>
       </c>
@@ -34646,7 +34062,7 @@
         <v>3648</v>
       </c>
     </row>
-    <row r="258" spans="1:15">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A258" t="s">
         <v>3649</v>
       </c>
@@ -34693,7 +34109,7 @@
         <v>3663</v>
       </c>
     </row>
-    <row r="259" spans="1:15">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A259" t="s">
         <v>3664</v>
       </c>
@@ -34740,7 +34156,7 @@
         <v>3678</v>
       </c>
     </row>
-    <row r="260" spans="1:15">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A260" t="s">
         <v>3679</v>
       </c>
@@ -34787,7 +34203,7 @@
         <v>3693</v>
       </c>
     </row>
-    <row r="261" spans="1:15">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A261" t="s">
         <v>3694</v>
       </c>
@@ -34834,7 +34250,7 @@
         <v>3695</v>
       </c>
     </row>
-    <row r="262" spans="1:15">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A262" t="s">
         <v>3703</v>
       </c>
@@ -34881,7 +34297,7 @@
         <v>3717</v>
       </c>
     </row>
-    <row r="263" spans="1:15">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A263" t="s">
         <v>3718</v>
       </c>
@@ -34928,7 +34344,7 @@
         <v>3719</v>
       </c>
     </row>
-    <row r="264" spans="1:15">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A264" t="s">
         <v>3732</v>
       </c>
@@ -34975,7 +34391,7 @@
         <v>3733</v>
       </c>
     </row>
-    <row r="265" spans="1:15">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A265" t="s">
         <v>3746</v>
       </c>
@@ -35022,7 +34438,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="266" spans="1:15">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A266" t="s">
         <v>3761</v>
       </c>
@@ -35069,7 +34485,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="267" spans="1:15">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A267" t="s">
         <v>3776</v>
       </c>
@@ -35116,7 +34532,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="268" spans="1:15">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A268" t="s">
         <v>3777</v>
       </c>
@@ -35163,7 +34579,7 @@
         <v>3791</v>
       </c>
     </row>
-    <row r="269" spans="1:15">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A269" t="s">
         <v>3792</v>
       </c>
@@ -35210,7 +34626,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="270" spans="1:15">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A270" t="s">
         <v>3807</v>
       </c>
@@ -35257,7 +34673,7 @@
         <v>3808</v>
       </c>
     </row>
-    <row r="271" spans="1:15">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A271" t="s">
         <v>3817</v>
       </c>
@@ -35304,7 +34720,7 @@
         <v>3818</v>
       </c>
     </row>
-    <row r="272" spans="1:15">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A272" t="s">
         <v>3830</v>
       </c>
@@ -35351,7 +34767,7 @@
         <v>3831</v>
       </c>
     </row>
-    <row r="273" spans="1:15">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A273" t="s">
         <v>3844</v>
       </c>
@@ -35398,7 +34814,7 @@
         <v>3845</v>
       </c>
     </row>
-    <row r="274" spans="1:15">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A274" t="s">
         <v>3858</v>
       </c>
@@ -35445,7 +34861,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="275" spans="1:15">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A275" t="s">
         <v>3872</v>
       </c>
@@ -35492,7 +34908,7 @@
         <v>3875</v>
       </c>
     </row>
-    <row r="276" spans="1:15">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A276" t="s">
         <v>3876</v>
       </c>
@@ -35539,7 +34955,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="277" spans="1:15">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A277" t="s">
         <v>3889</v>
       </c>
@@ -35586,7 +35002,7 @@
         <v>3903</v>
       </c>
     </row>
-    <row r="278" spans="1:15">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A278" t="s">
         <v>3904</v>
       </c>
@@ -35633,7 +35049,7 @@
         <v>3918</v>
       </c>
     </row>
-    <row r="279" spans="1:15">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A279" t="s">
         <v>3919</v>
       </c>
@@ -35680,7 +35096,7 @@
         <v>3933</v>
       </c>
     </row>
-    <row r="280" spans="1:15">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A280" t="s">
         <v>3934</v>
       </c>
@@ -35727,7 +35143,7 @@
         <v>3948</v>
       </c>
     </row>
-    <row r="281" spans="1:15">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A281" t="s">
         <v>3949</v>
       </c>
@@ -35774,7 +35190,7 @@
         <v>3963</v>
       </c>
     </row>
-    <row r="282" spans="1:15">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A282" t="s">
         <v>3964</v>
       </c>
@@ -35821,7 +35237,7 @@
         <v>3978</v>
       </c>
     </row>
-    <row r="283" spans="1:15">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A283" t="s">
         <v>3979</v>
       </c>
@@ -35868,7 +35284,7 @@
         <v>3993</v>
       </c>
     </row>
-    <row r="284" spans="1:15">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A284" t="s">
         <v>3994</v>
       </c>
@@ -35915,7 +35331,7 @@
         <v>4008</v>
       </c>
     </row>
-    <row r="285" spans="1:15">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A285" t="s">
         <v>4009</v>
       </c>
@@ -35962,7 +35378,7 @@
         <v>4023</v>
       </c>
     </row>
-    <row r="286" spans="1:15">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A286" t="s">
         <v>4024</v>
       </c>
@@ -36009,7 +35425,7 @@
         <v>4025</v>
       </c>
     </row>
-    <row r="287" spans="1:15">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A287" t="s">
         <v>4038</v>
       </c>
@@ -36056,7 +35472,7 @@
         <v>4052</v>
       </c>
     </row>
-    <row r="288" spans="1:15">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A288" t="s">
         <v>4053</v>
       </c>
@@ -36103,7 +35519,7 @@
         <v>4054</v>
       </c>
     </row>
-    <row r="289" spans="1:15">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A289" t="s">
         <v>4067</v>
       </c>
@@ -36150,7 +35566,7 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="290" spans="1:15">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A290" t="s">
         <v>4081</v>
       </c>
@@ -36197,7 +35613,7 @@
         <v>4088</v>
       </c>
     </row>
-    <row r="291" spans="1:15">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A291" t="s">
         <v>4089</v>
       </c>
@@ -36244,7 +35660,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="292" spans="1:15">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A292" t="s">
         <v>4104</v>
       </c>
@@ -36291,7 +35707,7 @@
         <v>4118</v>
       </c>
     </row>
-    <row r="293" spans="1:15">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A293" t="s">
         <v>4119</v>
       </c>
@@ -36338,7 +35754,7 @@
         <v>4120</v>
       </c>
     </row>
-    <row r="294" spans="1:15">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A294" t="s">
         <v>4133</v>
       </c>
@@ -36385,7 +35801,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="295" spans="1:15">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A295" t="s">
         <v>4148</v>
       </c>
@@ -36432,7 +35848,7 @@
         <v>4162</v>
       </c>
     </row>
-    <row r="296" spans="1:15">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A296" t="s">
         <v>4163</v>
       </c>
@@ -36479,7 +35895,7 @@
         <v>4177</v>
       </c>
     </row>
-    <row r="297" spans="1:15">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A297" t="s">
         <v>4178</v>
       </c>
@@ -36526,7 +35942,7 @@
         <v>4192</v>
       </c>
     </row>
-    <row r="298" spans="1:15">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A298" t="s">
         <v>4193</v>
       </c>
@@ -36573,7 +35989,7 @@
         <v>4207</v>
       </c>
     </row>
-    <row r="299" spans="1:15">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A299" t="s">
         <v>4208</v>
       </c>
@@ -36620,7 +36036,7 @@
         <v>4222</v>
       </c>
     </row>
-    <row r="300" spans="1:15">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A300" t="s">
         <v>4223</v>
       </c>
@@ -36667,7 +36083,7 @@
         <v>4237</v>
       </c>
     </row>
-    <row r="301" spans="1:15">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A301" t="s">
         <v>4238</v>
       </c>
@@ -36714,7 +36130,7 @@
         <v>4250</v>
       </c>
     </row>
-    <row r="302" spans="1:15">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A302" t="s">
         <v>4251</v>
       </c>
@@ -36761,7 +36177,7 @@
         <v>4252</v>
       </c>
     </row>
-    <row r="303" spans="1:15">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A303" t="s">
         <v>4263</v>
       </c>
@@ -36808,7 +36224,7 @@
         <v>4277</v>
       </c>
     </row>
-    <row r="304" spans="1:15">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A304" t="s">
         <v>4278</v>
       </c>
@@ -36855,7 +36271,7 @@
         <v>4279</v>
       </c>
     </row>
-    <row r="305" spans="1:15">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A305" t="s">
         <v>4292</v>
       </c>
@@ -36902,7 +36318,7 @@
         <v>4306</v>
       </c>
     </row>
-    <row r="306" spans="1:15">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A306" t="s">
         <v>4307</v>
       </c>
@@ -36949,7 +36365,7 @@
         <v>4321</v>
       </c>
     </row>
-    <row r="307" spans="1:15">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A307" t="s">
         <v>4322</v>
       </c>
@@ -36996,7 +36412,7 @@
         <v>4336</v>
       </c>
     </row>
-    <row r="308" spans="1:15">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A308" t="s">
         <v>4337</v>
       </c>
@@ -37043,7 +36459,7 @@
         <v>4351</v>
       </c>
     </row>
-    <row r="309" spans="1:15">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A309" t="s">
         <v>4352</v>
       </c>
@@ -37090,7 +36506,7 @@
         <v>4366</v>
       </c>
     </row>
-    <row r="310" spans="1:15">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A310" t="s">
         <v>4367</v>
       </c>
@@ -37137,7 +36553,7 @@
         <v>4381</v>
       </c>
     </row>
-    <row r="311" spans="1:15">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A311" t="s">
         <v>4382</v>
       </c>
@@ -37184,7 +36600,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="312" spans="1:15">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A312" t="s">
         <v>4397</v>
       </c>
@@ -37231,7 +36647,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="313" spans="1:15">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A313" t="s">
         <v>4412</v>
       </c>
@@ -37278,7 +36694,7 @@
         <v>4426</v>
       </c>
     </row>
-    <row r="314" spans="1:15">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A314" t="s">
         <v>4427</v>
       </c>
@@ -37325,7 +36741,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="315" spans="1:15">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A315" t="s">
         <v>4442</v>
       </c>
@@ -37372,7 +36788,7 @@
         <v>4443</v>
       </c>
     </row>
-    <row r="316" spans="1:15">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A316" t="s">
         <v>4456</v>
       </c>
@@ -37419,7 +36835,7 @@
         <v>4457</v>
       </c>
     </row>
-    <row r="317" spans="1:15">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A317" t="s">
         <v>4470</v>
       </c>
@@ -37466,7 +36882,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="318" spans="1:15">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A318" t="s">
         <v>4485</v>
       </c>
@@ -37513,7 +36929,7 @@
         <v>4499</v>
       </c>
     </row>
-    <row r="319" spans="1:15">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A319" t="s">
         <v>4500</v>
       </c>
@@ -37560,7 +36976,7 @@
         <v>4501</v>
       </c>
     </row>
-    <row r="320" spans="1:15">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A320" t="s">
         <v>4514</v>
       </c>
@@ -37607,7 +37023,7 @@
         <v>4515</v>
       </c>
     </row>
-    <row r="321" spans="1:15">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A321" t="s">
         <v>4528</v>
       </c>
@@ -37654,7 +37070,7 @@
         <v>4529</v>
       </c>
     </row>
-    <row r="322" spans="1:15">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A322" t="s">
         <v>4542</v>
       </c>
@@ -37701,7 +37117,7 @@
         <v>4543</v>
       </c>
     </row>
-    <row r="323" spans="1:15">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A323" t="s">
         <v>4556</v>
       </c>
@@ -37748,7 +37164,7 @@
         <v>4570</v>
       </c>
     </row>
-    <row r="324" spans="1:15">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A324" t="s">
         <v>4571</v>
       </c>
@@ -37795,7 +37211,7 @@
         <v>4585</v>
       </c>
     </row>
-    <row r="325" spans="1:15">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A325" t="s">
         <v>4586</v>
       </c>
@@ -37842,7 +37258,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="326" spans="1:15">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A326" t="s">
         <v>4601</v>
       </c>
@@ -37889,7 +37305,7 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="327" spans="1:15">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A327" t="s">
         <v>4616</v>
       </c>
@@ -37936,7 +37352,7 @@
         <v>4630</v>
       </c>
     </row>
-    <row r="328" spans="1:15">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A328" t="s">
         <v>4631</v>
       </c>
@@ -37983,7 +37399,7 @@
         <v>4645</v>
       </c>
     </row>
-    <row r="329" spans="1:15">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A329" t="s">
         <v>4646</v>
       </c>
@@ -38030,7 +37446,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="330" spans="1:15">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A330" t="s">
         <v>4660</v>
       </c>
@@ -38077,7 +37493,7 @@
         <v>4661</v>
       </c>
     </row>
-    <row r="331" spans="1:15">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A331" t="s">
         <v>4674</v>
       </c>
@@ -38124,7 +37540,7 @@
         <v>4688</v>
       </c>
     </row>
-    <row r="332" spans="1:15">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A332" t="s">
         <v>4689</v>
       </c>
@@ -38171,7 +37587,7 @@
         <v>4703</v>
       </c>
     </row>
-    <row r="333" spans="1:15">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A333" t="s">
         <v>4704</v>
       </c>
@@ -38218,7 +37634,7 @@
         <v>4717</v>
       </c>
     </row>
-    <row r="334" spans="1:15">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A334" t="s">
         <v>4718</v>
       </c>
@@ -38265,7 +37681,7 @@
         <v>4719</v>
       </c>
     </row>
-    <row r="335" spans="1:15">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A335" t="s">
         <v>4731</v>
       </c>
@@ -38312,7 +37728,7 @@
         <v>4745</v>
       </c>
     </row>
-    <row r="336" spans="1:15">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A336" t="s">
         <v>4746</v>
       </c>
@@ -38359,7 +37775,7 @@
         <v>4759</v>
       </c>
     </row>
-    <row r="337" spans="1:15">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A337" t="s">
         <v>4760</v>
       </c>
@@ -38406,7 +37822,7 @@
         <v>4763</v>
       </c>
     </row>
-    <row r="338" spans="1:15">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A338" t="s">
         <v>4772</v>
       </c>
@@ -38453,7 +37869,7 @@
         <v>4786</v>
       </c>
     </row>
-    <row r="339" spans="1:15">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A339" t="s">
         <v>4787</v>
       </c>
@@ -38500,7 +37916,7 @@
         <v>4801</v>
       </c>
     </row>
-    <row r="340" spans="1:15">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A340" t="s">
         <v>4802</v>
       </c>
@@ -38547,7 +37963,7 @@
         <v>4803</v>
       </c>
     </row>
-    <row r="341" spans="1:15">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A341" t="s">
         <v>4812</v>
       </c>
@@ -38594,7 +38010,7 @@
         <v>4813</v>
       </c>
     </row>
-    <row r="342" spans="1:15">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A342" t="s">
         <v>4826</v>
       </c>
@@ -38641,7 +38057,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="343" spans="1:15">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A343" t="s">
         <v>4840</v>
       </c>
@@ -38688,7 +38104,7 @@
         <v>4841</v>
       </c>
     </row>
-    <row r="344" spans="1:15">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A344" t="s">
         <v>4854</v>
       </c>
@@ -38735,7 +38151,7 @@
         <v>4867</v>
       </c>
     </row>
-    <row r="345" spans="1:15">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A345" t="s">
         <v>4868</v>
       </c>
@@ -38782,7 +38198,7 @@
         <v>4869</v>
       </c>
     </row>
-    <row r="346" spans="1:15">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A346" t="s">
         <v>4878</v>
       </c>
@@ -38829,7 +38245,7 @@
         <v>4892</v>
       </c>
     </row>
-    <row r="347" spans="1:15">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A347" t="s">
         <v>4893</v>
       </c>
@@ -38876,7 +38292,7 @@
         <v>4907</v>
       </c>
     </row>
-    <row r="348" spans="1:15">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A348" t="s">
         <v>4908</v>
       </c>
@@ -38923,7 +38339,7 @@
         <v>4922</v>
       </c>
     </row>
-    <row r="349" spans="1:15">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A349" t="s">
         <v>4923</v>
       </c>
@@ -38970,7 +38386,7 @@
         <v>4924</v>
       </c>
     </row>
-    <row r="350" spans="1:15">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A350" t="s">
         <v>4937</v>
       </c>
@@ -39017,7 +38433,7 @@
         <v>4950</v>
       </c>
     </row>
-    <row r="351" spans="1:15">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A351" t="s">
         <v>4951</v>
       </c>
@@ -39064,7 +38480,7 @@
         <v>4965</v>
       </c>
     </row>
-    <row r="352" spans="1:15">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A352" t="s">
         <v>4966</v>
       </c>
@@ -39111,7 +38527,7 @@
         <v>4980</v>
       </c>
     </row>
-    <row r="353" spans="1:15">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A353" t="s">
         <v>4981</v>
       </c>
@@ -39158,7 +38574,7 @@
         <v>4995</v>
       </c>
     </row>
-    <row r="354" spans="1:15">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A354" t="s">
         <v>4996</v>
       </c>
@@ -39205,7 +38621,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="355" spans="1:15">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A355" t="s">
         <v>5011</v>
       </c>
@@ -39252,7 +38668,7 @@
         <v>5012</v>
       </c>
     </row>
-    <row r="356" spans="1:15">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A356" t="s">
         <v>5025</v>
       </c>
@@ -39299,7 +38715,7 @@
         <v>5026</v>
       </c>
     </row>
-    <row r="357" spans="1:15">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A357" t="s">
         <v>5037</v>
       </c>
@@ -39346,7 +38762,7 @@
         <v>5049</v>
       </c>
     </row>
-    <row r="358" spans="1:15">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A358" t="s">
         <v>5050</v>
       </c>
@@ -39393,7 +38809,7 @@
         <v>5064</v>
       </c>
     </row>
-    <row r="359" spans="1:15">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A359" t="s">
         <v>5065</v>
       </c>
@@ -39440,7 +38856,7 @@
         <v>5066</v>
       </c>
     </row>
-    <row r="360" spans="1:15">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A360" t="s">
         <v>5079</v>
       </c>
@@ -39487,7 +38903,7 @@
         <v>5093</v>
       </c>
     </row>
-    <row r="361" spans="1:15">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A361" t="s">
         <v>5094</v>
       </c>
@@ -39534,7 +38950,7 @@
         <v>5108</v>
       </c>
     </row>
-    <row r="362" spans="1:15">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A362" t="s">
         <v>5109</v>
       </c>
@@ -39581,7 +38997,7 @@
         <v>5110</v>
       </c>
     </row>
-    <row r="363" spans="1:15">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A363" t="s">
         <v>5123</v>
       </c>
@@ -39628,7 +39044,7 @@
         <v>5137</v>
       </c>
     </row>
-    <row r="364" spans="1:15">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A364" t="s">
         <v>5138</v>
       </c>
@@ -39675,7 +39091,7 @@
         <v>5139</v>
       </c>
     </row>
-    <row r="365" spans="1:15">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A365" t="s">
         <v>5152</v>
       </c>
@@ -39722,7 +39138,7 @@
         <v>5166</v>
       </c>
     </row>
-    <row r="366" spans="1:15">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A366" t="s">
         <v>5167</v>
       </c>
@@ -39769,7 +39185,7 @@
         <v>5168</v>
       </c>
     </row>
-    <row r="367" spans="1:15">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A367" t="s">
         <v>5181</v>
       </c>
@@ -39816,7 +39232,7 @@
         <v>5182</v>
       </c>
     </row>
-    <row r="368" spans="1:15">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A368" t="s">
         <v>5195</v>
       </c>
@@ -39863,7 +39279,7 @@
         <v>5196</v>
       </c>
     </row>
-    <row r="369" spans="1:15">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A369" t="s">
         <v>5209</v>
       </c>
@@ -39910,7 +39326,7 @@
         <v>5210</v>
       </c>
     </row>
-    <row r="370" spans="1:15">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A370" t="s">
         <v>5221</v>
       </c>
@@ -39957,7 +39373,7 @@
         <v>5234</v>
       </c>
     </row>
-    <row r="371" spans="1:15">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A371" t="s">
         <v>5235</v>
       </c>
@@ -40004,7 +39420,7 @@
         <v>5249</v>
       </c>
     </row>
-    <row r="372" spans="1:15">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A372" t="s">
         <v>5250</v>
       </c>
@@ -40051,7 +39467,7 @@
         <v>5251</v>
       </c>
     </row>
-    <row r="373" spans="1:15">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A373" t="s">
         <v>5264</v>
       </c>
@@ -40098,7 +39514,7 @@
         <v>5278</v>
       </c>
     </row>
-    <row r="374" spans="1:15">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A374" t="s">
         <v>5279</v>
       </c>
@@ -40145,7 +39561,7 @@
         <v>5293</v>
       </c>
     </row>
-    <row r="375" spans="1:15">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A375" t="s">
         <v>5294</v>
       </c>
@@ -40192,7 +39608,7 @@
         <v>5308</v>
       </c>
     </row>
-    <row r="376" spans="1:15">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A376" t="s">
         <v>5309</v>
       </c>
@@ -40239,7 +39655,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="377" spans="1:15">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A377" t="s">
         <v>5311</v>
       </c>
@@ -40286,7 +39702,7 @@
         <v>5325</v>
       </c>
     </row>
-    <row r="378" spans="1:15">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A378" t="s">
         <v>5326</v>
       </c>
@@ -40333,7 +39749,7 @@
         <v>5329</v>
       </c>
     </row>
-    <row r="379" spans="1:15">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A379" t="s">
         <v>5338</v>
       </c>
@@ -40380,7 +39796,7 @@
         <v>5352</v>
       </c>
     </row>
-    <row r="380" spans="1:15">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A380" t="s">
         <v>5353</v>
       </c>
@@ -40427,7 +39843,7 @@
         <v>5363</v>
       </c>
     </row>
-    <row r="381" spans="1:15">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A381" t="s">
         <v>5364</v>
       </c>
@@ -40474,7 +39890,7 @@
         <v>5378</v>
       </c>
     </row>
-    <row r="382" spans="1:15">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A382" t="s">
         <v>5379</v>
       </c>
@@ -40521,7 +39937,7 @@
         <v>5380</v>
       </c>
     </row>
-    <row r="383" spans="1:15">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A383" t="s">
         <v>5391</v>
       </c>
@@ -40568,7 +39984,7 @@
         <v>5405</v>
       </c>
     </row>
-    <row r="384" spans="1:15">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A384" t="s">
         <v>5406</v>
       </c>
@@ -40615,7 +40031,7 @@
         <v>5420</v>
       </c>
     </row>
-    <row r="385" spans="1:15">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A385" t="s">
         <v>5421</v>
       </c>
@@ -40662,7 +40078,7 @@
         <v>5422</v>
       </c>
     </row>
-    <row r="386" spans="1:15">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A386" t="s">
         <v>5434</v>
       </c>
@@ -40709,7 +40125,7 @@
         <v>5447</v>
       </c>
     </row>
-    <row r="387" spans="1:15">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A387" t="s">
         <v>5448</v>
       </c>
@@ -40756,7 +40172,7 @@
         <v>5462</v>
       </c>
     </row>
-    <row r="388" spans="1:15">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A388" t="s">
         <v>5463</v>
       </c>
@@ -40803,7 +40219,7 @@
         <v>5477</v>
       </c>
     </row>
-    <row r="389" spans="1:15">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A389" t="s">
         <v>5478</v>
       </c>
@@ -40850,7 +40266,7 @@
         <v>5479</v>
       </c>
     </row>
-    <row r="390" spans="1:15">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A390" t="s">
         <v>5492</v>
       </c>
@@ -40897,7 +40313,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="391" spans="1:15">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A391" t="s">
         <v>5502</v>
       </c>
@@ -40944,7 +40360,7 @@
         <v>5516</v>
       </c>
     </row>
-    <row r="392" spans="1:15">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A392" t="s">
         <v>5517</v>
       </c>
@@ -40991,7 +40407,7 @@
         <v>5531</v>
       </c>
     </row>
-    <row r="393" spans="1:15">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A393" t="s">
         <v>5532</v>
       </c>
@@ -41038,7 +40454,7 @@
         <v>5533</v>
       </c>
     </row>
-    <row r="394" spans="1:15">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A394" t="s">
         <v>5546</v>
       </c>
@@ -41085,7 +40501,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="395" spans="1:15">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A395" t="s">
         <v>5561</v>
       </c>
@@ -41132,7 +40548,7 @@
         <v>5575</v>
       </c>
     </row>
-    <row r="396" spans="1:15">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A396" t="s">
         <v>5576</v>
       </c>
@@ -41179,7 +40595,7 @@
         <v>5590</v>
       </c>
     </row>
-    <row r="397" spans="1:15">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A397" t="s">
         <v>5591</v>
       </c>
@@ -41226,7 +40642,7 @@
         <v>5605</v>
       </c>
     </row>
-    <row r="398" spans="1:15">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A398" t="s">
         <v>5606</v>
       </c>
@@ -41273,7 +40689,7 @@
         <v>5607</v>
       </c>
     </row>
-    <row r="399" spans="1:15">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A399" t="s">
         <v>5620</v>
       </c>
@@ -41320,7 +40736,7 @@
         <v>5634</v>
       </c>
     </row>
-    <row r="400" spans="1:15">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A400" t="s">
         <v>5635</v>
       </c>
@@ -41367,7 +40783,7 @@
         <v>5636</v>
       </c>
     </row>
-    <row r="401" spans="1:15">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A401" t="s">
         <v>5647</v>
       </c>
@@ -41414,7 +40830,7 @@
         <v>5648</v>
       </c>
     </row>
-    <row r="402" spans="1:15">
+    <row r="402" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A402" t="s">
         <v>5660</v>
       </c>
@@ -41461,7 +40877,7 @@
         <v>5672</v>
       </c>
     </row>
-    <row r="403" spans="1:15">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A403" t="s">
         <v>5673</v>
       </c>
@@ -41508,7 +40924,7 @@
         <v>5687</v>
       </c>
     </row>
-    <row r="404" spans="1:15">
+    <row r="404" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A404" t="s">
         <v>5688</v>
       </c>
@@ -41555,7 +40971,7 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="405" spans="1:15">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A405" t="s">
         <v>5703</v>
       </c>
@@ -41602,7 +41018,7 @@
         <v>5717</v>
       </c>
     </row>
-    <row r="406" spans="1:15">
+    <row r="406" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A406" t="s">
         <v>5718</v>
       </c>
@@ -41649,7 +41065,7 @@
         <v>5719</v>
       </c>
     </row>
-    <row r="407" spans="1:15">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A407" t="s">
         <v>5732</v>
       </c>
@@ -41696,7 +41112,7 @@
         <v>5733</v>
       </c>
     </row>
-    <row r="408" spans="1:15">
+    <row r="408" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A408" t="s">
         <v>5745</v>
       </c>
@@ -41743,7 +41159,7 @@
         <v>5759</v>
       </c>
     </row>
-    <row r="409" spans="1:15">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A409" t="s">
         <v>5760</v>
       </c>
@@ -41790,7 +41206,7 @@
         <v>5774</v>
       </c>
     </row>
-    <row r="410" spans="1:15">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A410" t="s">
         <v>5775</v>
       </c>
@@ -41837,7 +41253,7 @@
         <v>5789</v>
       </c>
     </row>
-    <row r="411" spans="1:15">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A411" t="s">
         <v>5790</v>
       </c>
@@ -41884,7 +41300,7 @@
         <v>5804</v>
       </c>
     </row>
-    <row r="412" spans="1:15">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A412" t="s">
         <v>5805</v>
       </c>
@@ -41931,7 +41347,7 @@
         <v>5818</v>
       </c>
     </row>
-    <row r="413" spans="1:15">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A413" t="s">
         <v>5819</v>
       </c>
@@ -41978,7 +41394,7 @@
         <v>5833</v>
       </c>
     </row>
-    <row r="414" spans="1:15">
+    <row r="414" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A414" t="s">
         <v>5834</v>
       </c>
@@ -42025,7 +41441,7 @@
         <v>5847</v>
       </c>
     </row>
-    <row r="415" spans="1:15">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A415" t="s">
         <v>5848</v>
       </c>
@@ -42072,7 +41488,7 @@
         <v>5862</v>
       </c>
     </row>
-    <row r="416" spans="1:15">
+    <row r="416" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A416" t="s">
         <v>5863</v>
       </c>
@@ -42119,7 +41535,7 @@
         <v>5864</v>
       </c>
     </row>
-    <row r="417" spans="1:15">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A417" t="s">
         <v>5877</v>
       </c>
@@ -42166,7 +41582,7 @@
         <v>5878</v>
       </c>
     </row>
-    <row r="418" spans="1:15">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A418" t="s">
         <v>5891</v>
       </c>
@@ -42213,7 +41629,7 @@
         <v>5905</v>
       </c>
     </row>
-    <row r="419" spans="1:15">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A419" t="s">
         <v>5906</v>
       </c>
@@ -42260,7 +41676,7 @@
         <v>5920</v>
       </c>
     </row>
-    <row r="420" spans="1:15">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A420" t="s">
         <v>5921</v>
       </c>
@@ -42307,7 +41723,7 @@
         <v>5935</v>
       </c>
     </row>
-    <row r="421" spans="1:15">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A421" t="s">
         <v>5936</v>
       </c>
@@ -42354,7 +41770,7 @@
         <v>5950</v>
       </c>
     </row>
-    <row r="422" spans="1:15">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A422" t="s">
         <v>5951</v>
       </c>
@@ -42401,7 +41817,7 @@
         <v>5965</v>
       </c>
     </row>
-    <row r="423" spans="1:15">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A423" t="s">
         <v>5966</v>
       </c>
@@ -42448,7 +41864,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="424" spans="1:15">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A424" t="s">
         <v>5981</v>
       </c>
@@ -42495,7 +41911,7 @@
         <v>5982</v>
       </c>
     </row>
-    <row r="425" spans="1:15">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A425" t="s">
         <v>5995</v>
       </c>
@@ -42542,7 +41958,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="426" spans="1:15">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A426" t="s">
         <v>6004</v>
       </c>
@@ -42589,7 +42005,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="427" spans="1:15">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A427" t="s">
         <v>6011</v>
       </c>
@@ -42636,7 +42052,7 @@
         <v>6012</v>
       </c>
     </row>
-    <row r="428" spans="1:15">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A428" t="s">
         <v>6025</v>
       </c>
@@ -42683,7 +42099,7 @@
         <v>6039</v>
       </c>
     </row>
-    <row r="429" spans="1:15">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A429" t="s">
         <v>6040</v>
       </c>
@@ -42730,7 +42146,7 @@
         <v>6041</v>
       </c>
     </row>
-    <row r="430" spans="1:15">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A430" t="s">
         <v>6053</v>
       </c>
@@ -42777,7 +42193,7 @@
         <v>6067</v>
       </c>
     </row>
-    <row r="431" spans="1:15">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A431" t="s">
         <v>6068</v>
       </c>
@@ -42824,7 +42240,7 @@
         <v>6082</v>
       </c>
     </row>
-    <row r="432" spans="1:15">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A432" t="s">
         <v>6083</v>
       </c>
@@ -42871,7 +42287,7 @@
         <v>6097</v>
       </c>
     </row>
-    <row r="433" spans="1:15">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A433" t="s">
         <v>6098</v>
       </c>
@@ -42918,7 +42334,7 @@
         <v>6112</v>
       </c>
     </row>
-    <row r="434" spans="1:15">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A434" t="s">
         <v>6113</v>
       </c>
@@ -42965,7 +42381,7 @@
         <v>4025</v>
       </c>
     </row>
-    <row r="435" spans="1:15">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A435" t="s">
         <v>6126</v>
       </c>
@@ -43012,7 +42428,7 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="436" spans="1:15">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A436" t="s">
         <v>6132</v>
       </c>
@@ -43059,7 +42475,7 @@
         <v>3963</v>
       </c>
     </row>
-    <row r="437" spans="1:15">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A437" t="s">
         <v>6140</v>
       </c>
@@ -43106,7 +42522,7 @@
         <v>4118</v>
       </c>
     </row>
-    <row r="438" spans="1:15">
+    <row r="438" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A438" t="s">
         <v>6152</v>
       </c>
@@ -43153,7 +42569,7 @@
         <v>6165</v>
       </c>
     </row>
-    <row r="439" spans="1:15">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A439" t="s">
         <v>6166</v>
       </c>
@@ -43200,7 +42616,7 @@
         <v>4120</v>
       </c>
     </row>
-    <row r="440" spans="1:15">
+    <row r="440" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A440" t="s">
         <v>6179</v>
       </c>
@@ -43247,7 +42663,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="441" spans="1:15">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A441" t="s">
         <v>6184</v>
       </c>
@@ -43294,7 +42710,7 @@
         <v>6198</v>
       </c>
     </row>
-    <row r="442" spans="1:15">
+    <row r="442" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A442" t="s">
         <v>6199</v>
       </c>
@@ -43341,7 +42757,7 @@
         <v>6213</v>
       </c>
     </row>
-    <row r="443" spans="1:15">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A443" t="s">
         <v>6214</v>
       </c>
@@ -43388,7 +42804,7 @@
         <v>6228</v>
       </c>
     </row>
-    <row r="444" spans="1:15">
+    <row r="444" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A444" t="s">
         <v>6229</v>
       </c>
@@ -43435,7 +42851,7 @@
         <v>6243</v>
       </c>
     </row>
-    <row r="445" spans="1:15">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A445" t="s">
         <v>6244</v>
       </c>
@@ -43482,7 +42898,7 @@
         <v>6257</v>
       </c>
     </row>
-    <row r="446" spans="1:15">
+    <row r="446" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A446" t="s">
         <v>6258</v>
       </c>
@@ -43529,7 +42945,7 @@
         <v>6271</v>
       </c>
     </row>
-    <row r="447" spans="1:15">
+    <row r="447" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A447" t="s">
         <v>6272</v>
       </c>
@@ -43576,7 +42992,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="448" spans="1:15">
+    <row r="448" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A448" t="s">
         <v>6278</v>
       </c>
@@ -43623,7 +43039,7 @@
         <v>6285</v>
       </c>
     </row>
-    <row r="449" spans="1:15">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A449" t="s">
         <v>6286</v>
       </c>
@@ -43670,7 +43086,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="450" spans="1:15">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A450" t="s">
         <v>6301</v>
       </c>
@@ -43717,7 +43133,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="451" spans="1:15">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A451" t="s">
         <v>6316</v>
       </c>
@@ -43764,7 +43180,7 @@
         <v>6317</v>
       </c>
     </row>
-    <row r="452" spans="1:15">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A452" t="s">
         <v>6330</v>
       </c>
@@ -43811,7 +43227,7 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="453" spans="1:15">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A453" t="s">
         <v>6343</v>
       </c>
@@ -43858,7 +43274,7 @@
         <v>6344</v>
       </c>
     </row>
-    <row r="454" spans="1:15">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A454" t="s">
         <v>6355</v>
       </c>
@@ -43905,7 +43321,7 @@
         <v>6358</v>
       </c>
     </row>
-    <row r="455" spans="1:15">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A455" t="s">
         <v>6369</v>
       </c>
@@ -43952,7 +43368,7 @@
         <v>6383</v>
       </c>
     </row>
-    <row r="456" spans="1:15">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A456" t="s">
         <v>6384</v>
       </c>
@@ -43999,7 +43415,7 @@
         <v>6398</v>
       </c>
     </row>
-    <row r="457" spans="1:15">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A457" t="s">
         <v>6399</v>
       </c>
@@ -44046,7 +43462,7 @@
         <v>6413</v>
       </c>
     </row>
-    <row r="458" spans="1:15">
+    <row r="458" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A458" t="s">
         <v>6414</v>
       </c>
@@ -44093,7 +43509,7 @@
         <v>6428</v>
       </c>
     </row>
-    <row r="459" spans="1:15">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A459" t="s">
         <v>6429</v>
       </c>
@@ -44140,7 +43556,7 @@
         <v>6443</v>
       </c>
     </row>
-    <row r="460" spans="1:15">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A460" t="s">
         <v>6444</v>
       </c>
@@ -44187,7 +43603,7 @@
         <v>6458</v>
       </c>
     </row>
-    <row r="461" spans="1:15">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A461" t="s">
         <v>6459</v>
       </c>
@@ -44234,7 +43650,7 @@
         <v>6472</v>
       </c>
     </row>
-    <row r="462" spans="1:15">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A462" t="s">
         <v>6473</v>
       </c>
@@ -44281,7 +43697,7 @@
         <v>6486</v>
       </c>
     </row>
-    <row r="463" spans="1:15">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A463" t="s">
         <v>6487</v>
       </c>
@@ -44328,7 +43744,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="464" spans="1:15">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A464" t="s">
         <v>6502</v>
       </c>
@@ -44375,7 +43791,7 @@
         <v>6516</v>
       </c>
     </row>
-    <row r="465" spans="1:15">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A465" t="s">
         <v>6517</v>
       </c>
@@ -44422,7 +43838,7 @@
         <v>6530</v>
       </c>
     </row>
-    <row r="466" spans="1:15">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A466" t="s">
         <v>6531</v>
       </c>
@@ -44469,7 +43885,7 @@
         <v>6545</v>
       </c>
     </row>
-    <row r="467" spans="1:15">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A467" t="s">
         <v>6546</v>
       </c>
@@ -44516,7 +43932,7 @@
         <v>6547</v>
       </c>
     </row>
-    <row r="468" spans="1:15">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A468" t="s">
         <v>6559</v>
       </c>
@@ -44563,7 +43979,7 @@
         <v>6560</v>
       </c>
     </row>
-    <row r="469" spans="1:15">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A469" t="s">
         <v>6561</v>
       </c>
@@ -44610,7 +44026,7 @@
         <v>6562</v>
       </c>
     </row>
-    <row r="470" spans="1:15">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A470" t="s">
         <v>6574</v>
       </c>
@@ -44657,7 +44073,7 @@
         <v>6579</v>
       </c>
     </row>
-    <row r="471" spans="1:15">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A471" t="s">
         <v>6580</v>
       </c>
@@ -44704,7 +44120,7 @@
         <v>6594</v>
       </c>
     </row>
-    <row r="472" spans="1:15">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A472" t="s">
         <v>6595</v>
       </c>
@@ -44751,7 +44167,7 @@
         <v>6609</v>
       </c>
     </row>
-    <row r="473" spans="1:15">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A473" t="s">
         <v>6610</v>
       </c>
@@ -44798,7 +44214,7 @@
         <v>6619</v>
       </c>
     </row>
-    <row r="474" spans="1:15">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A474" t="s">
         <v>6620</v>
       </c>
@@ -44845,7 +44261,7 @@
         <v>6633</v>
       </c>
     </row>
-    <row r="475" spans="1:15">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A475" t="s">
         <v>6634</v>
       </c>
@@ -44892,7 +44308,7 @@
         <v>6648</v>
       </c>
     </row>
-    <row r="476" spans="1:15">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A476" t="s">
         <v>6649</v>
       </c>
@@ -44939,7 +44355,7 @@
         <v>6663</v>
       </c>
     </row>
-    <row r="477" spans="1:15">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A477" t="s">
         <v>6664</v>
       </c>
@@ -44986,7 +44402,7 @@
         <v>6678</v>
       </c>
     </row>
-    <row r="478" spans="1:15">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A478" t="s">
         <v>6679</v>
       </c>
@@ -45033,7 +44449,7 @@
         <v>6693</v>
       </c>
     </row>
-    <row r="479" spans="1:15">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A479" t="s">
         <v>6694</v>
       </c>
@@ -45080,7 +44496,7 @@
         <v>6708</v>
       </c>
     </row>
-    <row r="480" spans="1:15">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A480" t="s">
         <v>6709</v>
       </c>
@@ -45127,7 +44543,7 @@
         <v>6723</v>
       </c>
     </row>
-    <row r="481" spans="1:15">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A481" t="s">
         <v>6724</v>
       </c>
@@ -45174,7 +44590,7 @@
         <v>6738</v>
       </c>
     </row>
-    <row r="482" spans="1:15">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A482" t="s">
         <v>6739</v>
       </c>
@@ -45221,7 +44637,7 @@
         <v>6753</v>
       </c>
     </row>
-    <row r="483" spans="1:15">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A483" t="s">
         <v>6754</v>
       </c>
@@ -45268,7 +44684,7 @@
         <v>6768</v>
       </c>
     </row>
-    <row r="484" spans="1:15">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A484" t="s">
         <v>6769</v>
       </c>
@@ -45315,7 +44731,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="485" spans="1:15">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A485" t="s">
         <v>6784</v>
       </c>
@@ -45362,7 +44778,7 @@
         <v>6798</v>
       </c>
     </row>
-    <row r="486" spans="1:15">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A486" t="s">
         <v>6799</v>
       </c>
@@ -45409,7 +44825,7 @@
         <v>6813</v>
       </c>
     </row>
-    <row r="487" spans="1:15">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A487" t="s">
         <v>6814</v>
       </c>
@@ -45456,7 +44872,7 @@
         <v>6828</v>
       </c>
     </row>
-    <row r="488" spans="1:15">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A488" t="s">
         <v>6829</v>
       </c>
@@ -45503,7 +44919,7 @@
         <v>6843</v>
       </c>
     </row>
-    <row r="489" spans="1:15">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A489" t="s">
         <v>6844</v>
       </c>
@@ -45550,7 +44966,7 @@
         <v>6858</v>
       </c>
     </row>
-    <row r="490" spans="1:15">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A490" t="s">
         <v>6859</v>
       </c>
@@ -45597,7 +45013,7 @@
         <v>6873</v>
       </c>
     </row>
-    <row r="491" spans="1:15">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A491" t="s">
         <v>6874</v>
       </c>
@@ -45644,7 +45060,7 @@
         <v>6888</v>
       </c>
     </row>
-    <row r="492" spans="1:15">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A492" t="s">
         <v>6889</v>
       </c>
@@ -45691,7 +45107,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="493" spans="1:15">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A493" t="s">
         <v>6904</v>
       </c>
@@ -45738,7 +45154,7 @@
         <v>6918</v>
       </c>
     </row>
-    <row r="494" spans="1:15">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A494" t="s">
         <v>6919</v>
       </c>
@@ -45785,7 +45201,7 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="495" spans="1:15">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A495" t="s">
         <v>6934</v>
       </c>
@@ -45832,7 +45248,7 @@
         <v>6948</v>
       </c>
     </row>
-    <row r="496" spans="1:15">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A496" t="s">
         <v>6949</v>
       </c>
@@ -45879,7 +45295,7 @@
         <v>6963</v>
       </c>
     </row>
-    <row r="497" spans="1:15">
+    <row r="497" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A497" t="s">
         <v>6964</v>
       </c>
@@ -45926,7 +45342,7 @@
         <v>6965</v>
       </c>
     </row>
-    <row r="498" spans="1:15">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A498" t="s">
         <v>6978</v>
       </c>
@@ -45973,7 +45389,7 @@
         <v>6980</v>
       </c>
     </row>
-    <row r="499" spans="1:15">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A499" t="s">
         <v>6981</v>
       </c>
@@ -46020,7 +45436,7 @@
         <v>6995</v>
       </c>
     </row>
-    <row r="500" spans="1:15">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A500" t="s">
         <v>6996</v>
       </c>
@@ -46067,7 +45483,7 @@
         <v>7010</v>
       </c>
     </row>
-    <row r="501" spans="1:15">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A501" t="s">
         <v>7011</v>
       </c>
@@ -46114,7 +45530,7 @@
         <v>7013</v>
       </c>
     </row>
-    <row r="502" spans="1:15">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A502" t="s">
         <v>7014</v>
       </c>
@@ -46161,7 +45577,7 @@
         <v>7015</v>
       </c>
     </row>
-    <row r="503" spans="1:15">
+    <row r="503" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A503" t="s">
         <v>7028</v>
       </c>
@@ -46208,7 +45624,7 @@
         <v>7042</v>
       </c>
     </row>
-    <row r="504" spans="1:15">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A504" t="s">
         <v>7043</v>
       </c>
@@ -46255,7 +45671,7 @@
         <v>7057</v>
       </c>
     </row>
-    <row r="505" spans="1:15">
+    <row r="505" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A505" t="s">
         <v>7058</v>
       </c>
@@ -46302,7 +45718,7 @@
         <v>7072</v>
       </c>
     </row>
-    <row r="506" spans="1:15">
+    <row r="506" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A506" t="s">
         <v>7073</v>
       </c>
@@ -46349,7 +45765,7 @@
         <v>7087</v>
       </c>
     </row>
-    <row r="507" spans="1:15">
+    <row r="507" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A507" t="s">
         <v>7088</v>
       </c>
@@ -46396,7 +45812,7 @@
         <v>7102</v>
       </c>
     </row>
-    <row r="508" spans="1:15">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A508" t="s">
         <v>7103</v>
       </c>
@@ -46443,7 +45859,7 @@
         <v>7104</v>
       </c>
     </row>
-    <row r="509" spans="1:15">
+    <row r="509" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A509" t="s">
         <v>7117</v>
       </c>
@@ -46490,7 +45906,7 @@
         <v>7118</v>
       </c>
     </row>
-    <row r="510" spans="1:15">
+    <row r="510" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A510" t="s">
         <v>7120</v>
       </c>
@@ -46537,7 +45953,7 @@
         <v>7121</v>
       </c>
     </row>
-    <row r="511" ht="374.4" spans="1:15">
+    <row r="511" spans="1:15" ht="342" x14ac:dyDescent="0.15">
       <c r="A511" t="s">
         <v>7122</v>
       </c>
@@ -46584,665 +46000,665 @@
         <v>7123</v>
       </c>
     </row>
-    <row r="512" spans="1:15">
-      <c r="A512" s="2" t="s">
+    <row r="512" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A512" t="s">
         <v>7124</v>
       </c>
-      <c r="B512" s="2" t="s">
+      <c r="B512" t="s">
         <v>7125</v>
       </c>
-      <c r="C512" s="2" t="s">
+      <c r="C512" t="s">
         <v>7126</v>
       </c>
-      <c r="D512" s="2" t="s">
+      <c r="D512" t="s">
         <v>7125</v>
       </c>
-      <c r="E512" s="2" t="s">
+      <c r="E512" t="s">
         <v>7125</v>
       </c>
-      <c r="F512" s="2" t="s">
+      <c r="F512" t="s">
         <v>7125</v>
       </c>
-      <c r="G512" s="2" t="s">
+      <c r="G512" t="s">
         <v>7125</v>
       </c>
-      <c r="H512" s="2" t="s">
+      <c r="H512" t="s">
         <v>7125</v>
       </c>
-      <c r="I512" s="2" t="s">
+      <c r="I512" t="s">
         <v>7125</v>
       </c>
-      <c r="J512" s="2" t="s">
+      <c r="J512" t="s">
         <v>7125</v>
       </c>
-      <c r="K512" s="2" t="s">
+      <c r="K512" t="s">
         <v>7125</v>
       </c>
-      <c r="L512" s="2" t="s">
+      <c r="L512" t="s">
         <v>7125</v>
       </c>
-      <c r="M512" s="2" t="s">
+      <c r="M512" t="s">
         <v>7125</v>
       </c>
-      <c r="N512" s="2" t="s">
+      <c r="N512" t="s">
         <v>7125</v>
       </c>
-      <c r="O512" s="2" t="s">
+      <c r="O512" t="s">
         <v>7125</v>
       </c>
     </row>
-    <row r="513" spans="1:15">
-      <c r="A513" s="2" t="s">
+    <row r="513" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A513" t="s">
         <v>7127</v>
       </c>
-      <c r="B513" s="3" t="s">
+      <c r="B513" t="s">
         <v>7128</v>
       </c>
-      <c r="C513" s="3" t="s">
+      <c r="C513" t="s">
         <v>7129</v>
       </c>
-      <c r="D513" s="3" t="s">
+      <c r="D513" t="s">
         <v>7128</v>
       </c>
-      <c r="E513" s="3" t="s">
+      <c r="E513" t="s">
         <v>7128</v>
       </c>
-      <c r="F513" s="3" t="s">
+      <c r="F513" t="s">
         <v>7128</v>
       </c>
-      <c r="G513" s="3" t="s">
+      <c r="G513" t="s">
         <v>7128</v>
       </c>
-      <c r="H513" s="3" t="s">
+      <c r="H513" t="s">
         <v>7128</v>
       </c>
-      <c r="I513" s="3" t="s">
+      <c r="I513" t="s">
         <v>7128</v>
       </c>
-      <c r="J513" s="3" t="s">
+      <c r="J513" t="s">
         <v>7128</v>
       </c>
-      <c r="K513" s="3" t="s">
+      <c r="K513" t="s">
         <v>7128</v>
       </c>
-      <c r="L513" s="3" t="s">
+      <c r="L513" t="s">
         <v>7128</v>
       </c>
-      <c r="M513" s="3" t="s">
+      <c r="M513" t="s">
         <v>7128</v>
       </c>
-      <c r="N513" s="3" t="s">
+      <c r="N513" t="s">
         <v>7128</v>
       </c>
-      <c r="O513" s="3" t="s">
+      <c r="O513" t="s">
         <v>7128</v>
       </c>
     </row>
-    <row r="514" spans="1:15">
-      <c r="A514" s="4" t="s">
+    <row r="514" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A514" s="1" t="s">
         <v>7130</v>
       </c>
-      <c r="B514" s="2" t="s">
+      <c r="B514" t="s">
         <v>7131</v>
       </c>
-      <c r="C514" s="2" t="s">
+      <c r="C514" t="s">
         <v>7131</v>
       </c>
-      <c r="D514" s="2" t="s">
+      <c r="D514" t="s">
         <v>7131</v>
       </c>
-      <c r="E514" s="2" t="s">
+      <c r="E514" t="s">
         <v>7131</v>
       </c>
-      <c r="F514" s="2" t="s">
+      <c r="F514" t="s">
         <v>7131</v>
       </c>
-      <c r="G514" s="2" t="s">
+      <c r="G514" t="s">
         <v>7131</v>
       </c>
-      <c r="H514" s="2" t="s">
+      <c r="H514" t="s">
         <v>7131</v>
       </c>
-      <c r="I514" s="2" t="s">
+      <c r="I514" t="s">
         <v>7131</v>
       </c>
-      <c r="J514" s="2" t="s">
+      <c r="J514" t="s">
         <v>7131</v>
       </c>
-      <c r="K514" s="2" t="s">
+      <c r="K514" t="s">
         <v>7131</v>
       </c>
-      <c r="L514" s="2" t="s">
+      <c r="L514" t="s">
         <v>7131</v>
       </c>
-      <c r="M514" s="2" t="s">
+      <c r="M514" t="s">
         <v>7131</v>
       </c>
-      <c r="N514" s="2" t="s">
+      <c r="N514" t="s">
         <v>7131</v>
       </c>
-      <c r="O514" s="2" t="s">
+      <c r="O514" t="s">
         <v>7131</v>
       </c>
     </row>
-    <row r="515" spans="1:15">
-      <c r="A515" s="2" t="s">
+    <row r="515" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A515" t="s">
         <v>7132</v>
       </c>
-      <c r="B515" s="2" t="s">
+      <c r="B515" t="s">
         <v>7133</v>
       </c>
-      <c r="C515" s="2" t="s">
+      <c r="C515" t="s">
         <v>7133</v>
       </c>
-      <c r="D515" s="2" t="s">
+      <c r="D515" t="s">
         <v>7133</v>
       </c>
-      <c r="E515" s="2" t="s">
+      <c r="E515" t="s">
         <v>7133</v>
       </c>
-      <c r="F515" s="2" t="s">
+      <c r="F515" t="s">
         <v>7133</v>
       </c>
-      <c r="G515" s="2" t="s">
+      <c r="G515" t="s">
         <v>7133</v>
       </c>
-      <c r="H515" s="2" t="s">
+      <c r="H515" t="s">
         <v>7133</v>
       </c>
-      <c r="I515" s="2" t="s">
+      <c r="I515" t="s">
         <v>7133</v>
       </c>
-      <c r="J515" s="2" t="s">
+      <c r="J515" t="s">
         <v>7133</v>
       </c>
-      <c r="K515" s="2" t="s">
+      <c r="K515" t="s">
         <v>7133</v>
       </c>
-      <c r="L515" s="2" t="s">
+      <c r="L515" t="s">
         <v>7133</v>
       </c>
-      <c r="M515" s="2" t="s">
+      <c r="M515" t="s">
         <v>7133</v>
       </c>
-      <c r="N515" s="2" t="s">
+      <c r="N515" t="s">
         <v>7133</v>
       </c>
-      <c r="O515" s="2" t="s">
+      <c r="O515" t="s">
         <v>7133</v>
       </c>
     </row>
-    <row r="516" spans="1:15">
-      <c r="A516" s="2" t="s">
+    <row r="516" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A516" t="s">
         <v>7134</v>
       </c>
-      <c r="B516" s="2" t="s">
+      <c r="B516" t="s">
         <v>7135</v>
       </c>
-      <c r="C516" s="2" t="s">
+      <c r="C516" t="s">
         <v>7135</v>
       </c>
-      <c r="D516" s="2" t="s">
+      <c r="D516" t="s">
         <v>7135</v>
       </c>
-      <c r="E516" s="2" t="s">
+      <c r="E516" t="s">
         <v>7135</v>
       </c>
-      <c r="F516" s="2" t="s">
+      <c r="F516" t="s">
         <v>7135</v>
       </c>
-      <c r="G516" s="2" t="s">
+      <c r="G516" t="s">
         <v>7135</v>
       </c>
-      <c r="H516" s="2" t="s">
+      <c r="H516" t="s">
         <v>7135</v>
       </c>
-      <c r="I516" s="2" t="s">
+      <c r="I516" t="s">
         <v>7135</v>
       </c>
-      <c r="J516" s="2" t="s">
+      <c r="J516" t="s">
         <v>7135</v>
       </c>
-      <c r="K516" s="2" t="s">
+      <c r="K516" t="s">
         <v>7135</v>
       </c>
-      <c r="L516" s="2" t="s">
+      <c r="L516" t="s">
         <v>7135</v>
       </c>
-      <c r="M516" s="2" t="s">
+      <c r="M516" t="s">
         <v>7135</v>
       </c>
-      <c r="N516" s="2" t="s">
+      <c r="N516" t="s">
         <v>7135</v>
       </c>
-      <c r="O516" s="2" t="s">
+      <c r="O516" t="s">
         <v>7135</v>
       </c>
     </row>
-    <row r="517" spans="1:15">
-      <c r="A517" s="2" t="s">
+    <row r="517" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A517" t="s">
         <v>7136</v>
       </c>
-      <c r="B517" s="2" t="s">
+      <c r="B517" t="s">
         <v>7137</v>
       </c>
-      <c r="C517" s="2" t="s">
+      <c r="C517" t="s">
         <v>7137</v>
       </c>
-      <c r="D517" s="2" t="s">
+      <c r="D517" t="s">
         <v>7137</v>
       </c>
-      <c r="E517" s="2" t="s">
+      <c r="E517" t="s">
         <v>7137</v>
       </c>
-      <c r="F517" s="2" t="s">
+      <c r="F517" t="s">
         <v>7137</v>
       </c>
-      <c r="G517" s="2" t="s">
+      <c r="G517" t="s">
         <v>7137</v>
       </c>
-      <c r="H517" s="2" t="s">
+      <c r="H517" t="s">
         <v>7137</v>
       </c>
-      <c r="I517" s="2" t="s">
+      <c r="I517" t="s">
         <v>7137</v>
       </c>
-      <c r="J517" s="2" t="s">
+      <c r="J517" t="s">
         <v>7137</v>
       </c>
-      <c r="K517" s="2" t="s">
+      <c r="K517" t="s">
         <v>7137</v>
       </c>
-      <c r="L517" s="2" t="s">
+      <c r="L517" t="s">
         <v>7137</v>
       </c>
-      <c r="M517" s="2" t="s">
+      <c r="M517" t="s">
         <v>7137</v>
       </c>
-      <c r="N517" s="2" t="s">
+      <c r="N517" t="s">
         <v>7137</v>
       </c>
-      <c r="O517" s="2" t="s">
+      <c r="O517" t="s">
         <v>7137</v>
       </c>
     </row>
-    <row r="518" spans="1:15">
-      <c r="A518" s="2" t="s">
+    <row r="518" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A518" t="s">
         <v>7138</v>
       </c>
-      <c r="B518" s="2" t="s">
+      <c r="B518" t="s">
         <v>7139</v>
       </c>
-      <c r="C518" s="2" t="s">
+      <c r="C518" t="s">
         <v>7139</v>
       </c>
-      <c r="D518" s="2" t="s">
+      <c r="D518" t="s">
         <v>7139</v>
       </c>
-      <c r="E518" s="2" t="s">
+      <c r="E518" t="s">
         <v>7139</v>
       </c>
-      <c r="F518" s="2" t="s">
+      <c r="F518" t="s">
         <v>7139</v>
       </c>
-      <c r="G518" s="2" t="s">
+      <c r="G518" t="s">
         <v>7139</v>
       </c>
-      <c r="H518" s="2" t="s">
+      <c r="H518" t="s">
         <v>7139</v>
       </c>
-      <c r="I518" s="2" t="s">
+      <c r="I518" t="s">
         <v>7139</v>
       </c>
-      <c r="J518" s="2" t="s">
+      <c r="J518" t="s">
         <v>7139</v>
       </c>
-      <c r="K518" s="2" t="s">
+      <c r="K518" t="s">
         <v>7139</v>
       </c>
-      <c r="L518" s="2" t="s">
+      <c r="L518" t="s">
         <v>7139</v>
       </c>
-      <c r="M518" s="2" t="s">
+      <c r="M518" t="s">
         <v>7139</v>
       </c>
-      <c r="N518" s="2" t="s">
+      <c r="N518" t="s">
         <v>7139</v>
       </c>
-      <c r="O518" s="2" t="s">
+      <c r="O518" t="s">
         <v>7139</v>
       </c>
     </row>
-    <row r="519" spans="1:15">
-      <c r="A519" s="2" t="s">
+    <row r="519" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A519" t="s">
         <v>7140</v>
       </c>
-      <c r="B519" s="2" t="s">
+      <c r="B519" t="s">
         <v>7141</v>
       </c>
-      <c r="C519" s="2" t="s">
+      <c r="C519" t="s">
         <v>7141</v>
       </c>
-      <c r="D519" s="2" t="s">
+      <c r="D519" t="s">
         <v>7141</v>
       </c>
-      <c r="E519" s="2" t="s">
+      <c r="E519" t="s">
         <v>7141</v>
       </c>
-      <c r="F519" s="2" t="s">
+      <c r="F519" t="s">
         <v>7141</v>
       </c>
-      <c r="G519" s="2" t="s">
+      <c r="G519" t="s">
         <v>7141</v>
       </c>
-      <c r="H519" s="2" t="s">
+      <c r="H519" t="s">
         <v>7141</v>
       </c>
-      <c r="I519" s="2" t="s">
+      <c r="I519" t="s">
         <v>7141</v>
       </c>
-      <c r="J519" s="2" t="s">
+      <c r="J519" t="s">
         <v>7141</v>
       </c>
-      <c r="K519" s="2" t="s">
+      <c r="K519" t="s">
         <v>7141</v>
       </c>
-      <c r="L519" s="2" t="s">
+      <c r="L519" t="s">
         <v>7141</v>
       </c>
-      <c r="M519" s="2" t="s">
+      <c r="M519" t="s">
         <v>7141</v>
       </c>
-      <c r="N519" s="2" t="s">
+      <c r="N519" t="s">
         <v>7141</v>
       </c>
-      <c r="O519" s="2" t="s">
+      <c r="O519" t="s">
         <v>7141</v>
       </c>
     </row>
-    <row r="520" spans="1:15">
-      <c r="A520" s="2" t="s">
+    <row r="520" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A520" t="s">
         <v>7142</v>
       </c>
-      <c r="B520" s="2" t="s">
+      <c r="B520" t="s">
         <v>7143</v>
       </c>
-      <c r="C520" s="2" t="s">
+      <c r="C520" t="s">
         <v>7143</v>
       </c>
-      <c r="D520" s="2" t="s">
+      <c r="D520" t="s">
         <v>7143</v>
       </c>
-      <c r="E520" s="2" t="s">
+      <c r="E520" t="s">
         <v>7143</v>
       </c>
-      <c r="F520" s="2" t="s">
+      <c r="F520" t="s">
         <v>7143</v>
       </c>
-      <c r="G520" s="2" t="s">
+      <c r="G520" t="s">
         <v>7143</v>
       </c>
-      <c r="H520" s="2" t="s">
+      <c r="H520" t="s">
         <v>7143</v>
       </c>
-      <c r="I520" s="2" t="s">
+      <c r="I520" t="s">
         <v>7143</v>
       </c>
-      <c r="J520" s="2" t="s">
+      <c r="J520" t="s">
         <v>7143</v>
       </c>
-      <c r="K520" s="2" t="s">
+      <c r="K520" t="s">
         <v>7143</v>
       </c>
-      <c r="L520" s="2" t="s">
+      <c r="L520" t="s">
         <v>7143</v>
       </c>
-      <c r="M520" s="2" t="s">
+      <c r="M520" t="s">
         <v>7143</v>
       </c>
-      <c r="N520" s="2" t="s">
+      <c r="N520" t="s">
         <v>7143</v>
       </c>
-      <c r="O520" s="2" t="s">
+      <c r="O520" t="s">
         <v>7143</v>
       </c>
     </row>
-    <row r="521" spans="1:15">
-      <c r="A521" s="5" t="s">
+    <row r="521" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="A521" s="2" t="s">
         <v>7144</v>
       </c>
-      <c r="B521" s="2" t="s">
+      <c r="B521" t="s">
         <v>7145</v>
       </c>
-      <c r="C521" s="2" t="s">
+      <c r="C521" t="s">
         <v>7145</v>
       </c>
-      <c r="D521" s="2" t="s">
+      <c r="D521" t="s">
         <v>7145</v>
       </c>
-      <c r="E521" s="2" t="s">
+      <c r="E521" t="s">
         <v>7145</v>
       </c>
-      <c r="F521" s="2" t="s">
+      <c r="F521" t="s">
         <v>7145</v>
       </c>
-      <c r="G521" s="2" t="s">
+      <c r="G521" t="s">
         <v>7145</v>
       </c>
-      <c r="H521" s="2" t="s">
+      <c r="H521" t="s">
         <v>7145</v>
       </c>
-      <c r="I521" s="2" t="s">
+      <c r="I521" t="s">
         <v>7145</v>
       </c>
-      <c r="J521" s="2" t="s">
+      <c r="J521" t="s">
         <v>7145</v>
       </c>
-      <c r="K521" s="2" t="s">
+      <c r="K521" t="s">
         <v>7145</v>
       </c>
-      <c r="L521" s="2" t="s">
+      <c r="L521" t="s">
         <v>7145</v>
       </c>
-      <c r="M521" s="2" t="s">
+      <c r="M521" t="s">
         <v>7145</v>
       </c>
-      <c r="N521" s="2" t="s">
+      <c r="N521" t="s">
         <v>7145</v>
       </c>
-      <c r="O521" s="2" t="s">
+      <c r="O521" t="s">
         <v>7145</v>
       </c>
     </row>
-    <row r="522" spans="1:15">
-      <c r="A522" s="2" t="s">
+    <row r="522" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A522" t="s">
         <v>7146</v>
       </c>
-      <c r="B522" s="2" t="s">
+      <c r="B522" t="s">
         <v>7147</v>
       </c>
-      <c r="C522" s="2" t="s">
+      <c r="C522" t="s">
         <v>7147</v>
       </c>
-      <c r="D522" s="2" t="s">
+      <c r="D522" t="s">
         <v>7147</v>
       </c>
-      <c r="E522" s="2" t="s">
+      <c r="E522" t="s">
         <v>7147</v>
       </c>
-      <c r="F522" s="2" t="s">
+      <c r="F522" t="s">
         <v>7147</v>
       </c>
-      <c r="G522" s="2" t="s">
+      <c r="G522" t="s">
         <v>7147</v>
       </c>
-      <c r="H522" s="2" t="s">
+      <c r="H522" t="s">
         <v>7147</v>
       </c>
-      <c r="I522" s="2" t="s">
+      <c r="I522" t="s">
         <v>7147</v>
       </c>
-      <c r="J522" s="2" t="s">
+      <c r="J522" t="s">
         <v>7147</v>
       </c>
-      <c r="K522" s="2" t="s">
+      <c r="K522" t="s">
         <v>7147</v>
       </c>
-      <c r="L522" s="2" t="s">
+      <c r="L522" t="s">
         <v>7147</v>
       </c>
-      <c r="M522" s="2" t="s">
+      <c r="M522" t="s">
         <v>7147</v>
       </c>
-      <c r="N522" s="2" t="s">
+      <c r="N522" t="s">
         <v>7147</v>
       </c>
-      <c r="O522" s="2" t="s">
+      <c r="O522" t="s">
         <v>7147</v>
       </c>
     </row>
-    <row r="523" spans="1:15">
-      <c r="A523" s="2" t="s">
+    <row r="523" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A523" t="s">
         <v>7148</v>
       </c>
-      <c r="B523" s="2" t="s">
+      <c r="B523" t="s">
         <v>7149</v>
       </c>
-      <c r="C523" s="2" t="s">
+      <c r="C523" t="s">
         <v>7149</v>
       </c>
-      <c r="D523" s="2" t="s">
+      <c r="D523" t="s">
         <v>7149</v>
       </c>
-      <c r="E523" s="2" t="s">
+      <c r="E523" t="s">
         <v>7149</v>
       </c>
-      <c r="F523" s="2" t="s">
+      <c r="F523" t="s">
         <v>7149</v>
       </c>
-      <c r="G523" s="2" t="s">
+      <c r="G523" t="s">
         <v>7149</v>
       </c>
-      <c r="H523" s="2" t="s">
+      <c r="H523" t="s">
         <v>7149</v>
       </c>
-      <c r="I523" s="2" t="s">
+      <c r="I523" t="s">
         <v>7149</v>
       </c>
-      <c r="J523" s="2" t="s">
+      <c r="J523" t="s">
         <v>7149</v>
       </c>
-      <c r="K523" s="2" t="s">
+      <c r="K523" t="s">
         <v>7149</v>
       </c>
-      <c r="L523" s="2" t="s">
+      <c r="L523" t="s">
         <v>7149</v>
       </c>
-      <c r="M523" s="2" t="s">
+      <c r="M523" t="s">
         <v>7149</v>
       </c>
-      <c r="N523" s="2" t="s">
+      <c r="N523" t="s">
         <v>7149</v>
       </c>
-      <c r="O523" s="2" t="s">
+      <c r="O523" t="s">
         <v>7149</v>
       </c>
     </row>
-    <row r="524" spans="1:15">
-      <c r="A524" s="2" t="s">
+    <row r="524" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A524" t="s">
         <v>7150</v>
       </c>
-      <c r="B524" s="2" t="s">
+      <c r="B524" t="s">
         <v>7151</v>
       </c>
-      <c r="C524" s="2" t="s">
+      <c r="C524" t="s">
         <v>7151</v>
       </c>
-      <c r="D524" s="2" t="s">
+      <c r="D524" t="s">
         <v>7151</v>
       </c>
-      <c r="E524" s="2" t="s">
+      <c r="E524" t="s">
         <v>7151</v>
       </c>
-      <c r="F524" s="2" t="s">
+      <c r="F524" t="s">
         <v>7151</v>
       </c>
-      <c r="G524" s="2" t="s">
+      <c r="G524" t="s">
         <v>7151</v>
       </c>
-      <c r="H524" s="2" t="s">
+      <c r="H524" t="s">
         <v>7151</v>
       </c>
-      <c r="I524" s="2" t="s">
+      <c r="I524" t="s">
         <v>7151</v>
       </c>
-      <c r="J524" s="2" t="s">
+      <c r="J524" t="s">
         <v>7151</v>
       </c>
-      <c r="K524" s="2" t="s">
+      <c r="K524" t="s">
         <v>7151</v>
       </c>
-      <c r="L524" s="2" t="s">
+      <c r="L524" t="s">
         <v>7151</v>
       </c>
-      <c r="M524" s="2" t="s">
+      <c r="M524" t="s">
         <v>7151</v>
       </c>
-      <c r="N524" s="2" t="s">
+      <c r="N524" t="s">
         <v>7151</v>
       </c>
-      <c r="O524" s="2" t="s">
+      <c r="O524" t="s">
         <v>7151</v>
       </c>
     </row>
-    <row r="525" spans="1:15">
-      <c r="A525" s="2" t="s">
+    <row r="525" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A525" t="s">
         <v>7152</v>
       </c>
-      <c r="B525" s="2" t="s">
+      <c r="B525" t="s">
         <v>7153</v>
       </c>
-      <c r="C525" s="2" t="s">
+      <c r="C525" t="s">
         <v>7154</v>
       </c>
-      <c r="D525" s="2" t="s">
+      <c r="D525" t="s">
         <v>7154</v>
       </c>
-      <c r="E525" s="2" t="s">
+      <c r="E525" t="s">
         <v>7154</v>
       </c>
-      <c r="F525" s="2" t="s">
+      <c r="F525" t="s">
         <v>7154</v>
       </c>
-      <c r="G525" s="2" t="s">
+      <c r="G525" t="s">
         <v>7154</v>
       </c>
-      <c r="H525" s="2" t="s">
+      <c r="H525" t="s">
         <v>7154</v>
       </c>
-      <c r="I525" s="2" t="s">
+      <c r="I525" t="s">
         <v>7154</v>
       </c>
-      <c r="J525" s="2" t="s">
+      <c r="J525" t="s">
         <v>7154</v>
       </c>
-      <c r="K525" s="2" t="s">
+      <c r="K525" t="s">
         <v>7154</v>
       </c>
-      <c r="L525" s="2" t="s">
+      <c r="L525" t="s">
         <v>7154</v>
       </c>
-      <c r="M525" s="2" t="s">
+      <c r="M525" t="s">
         <v>7154</v>
       </c>
-      <c r="N525" s="2" t="s">
+      <c r="N525" t="s">
         <v>7154</v>
       </c>
-      <c r="O525" s="2" t="s">
+      <c r="O525" t="s">
         <v>7154</v>
       </c>
     </row>
-    <row r="526" spans="1:15">
+    <row r="526" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A526" t="s">
         <v>7155</v>
       </c>
@@ -47289,7 +46705,7 @@
         <v>7156</v>
       </c>
     </row>
-    <row r="527" spans="1:15">
+    <row r="527" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A527" t="s">
         <v>7157</v>
       </c>
@@ -47336,7 +46752,7 @@
         <v>7158</v>
       </c>
     </row>
-    <row r="528" spans="1:15">
+    <row r="528" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A528" t="s">
         <v>7159</v>
       </c>
@@ -47383,7 +46799,7 @@
         <v>7160</v>
       </c>
     </row>
-    <row r="529" spans="1:15">
+    <row r="529" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A529" t="s">
         <v>7161</v>
       </c>
@@ -47430,7 +46846,7 @@
         <v>7162</v>
       </c>
     </row>
-    <row r="530" spans="1:15">
+    <row r="530" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A530" t="s">
         <v>7163</v>
       </c>
@@ -47477,10 +46893,151 @@
         <v>7164</v>
       </c>
     </row>
+    <row r="531" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A531" s="3" t="s">
+        <v>7165</v>
+      </c>
+      <c r="B531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="C531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="D531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="E531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="F531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="G531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="H531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="I531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="J531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="K531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="L531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="M531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="N531" s="3" t="s">
+        <v>7166</v>
+      </c>
+      <c r="O531" s="3" t="s">
+        <v>7166</v>
+      </c>
+    </row>
+    <row r="532" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A532" s="3" t="s">
+        <v>7167</v>
+      </c>
+      <c r="B532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="C532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="D532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="E532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="F532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="G532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="H532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="I532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="J532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="K532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="L532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="M532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="N532" s="3" t="s">
+        <v>7168</v>
+      </c>
+      <c r="O532" s="3" t="s">
+        <v>7168</v>
+      </c>
+    </row>
+    <row r="533" spans="1:15" ht="15" x14ac:dyDescent="0.2">
+      <c r="A533" s="4" t="s">
+        <v>7169</v>
+      </c>
+      <c r="B533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="C533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="D533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="E533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="F533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="G533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="H533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="I533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="J533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="K533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="L533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="M533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="N533" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="O533" s="3" t="s">
+        <v>7170</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <ignoredErrors>
     <ignoredError sqref="A249 A119:O248 A118 A1:O117 C275 A275 A250:O274 A498 A499:O500 A501 A502:O508 C118:O118 A469:O497 A449:O467 C448:O448 A448 A277:O447" numberStoredAsText="1"/>
   </ignoredErrors>
